--- a/1.Project-with_Monolithic_Architecture/requirements/requirements_specification.xlsx
+++ b/1.Project-with_Monolithic_Architecture/requirements/requirements_specification.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Ingeniería de sistemas- Unicauca\Ing. Sistemas\SofEng2\Class\Project-Piedrazul\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\SoftwareProjects\Piedrazul-Medical-Services-Network\1.Project-with_Monolithic_Architecture\requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0589426-1B64-4FEB-A1A7-2A6B782C7BC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84CD7D34-7751-49D0-A0FD-0078F6079AC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="308">
   <si>
     <t>Sistema de gestion y agendamiento de citas medicas para centro de salud Piedra azul</t>
   </si>
@@ -930,13 +930,28 @@
   </si>
   <si>
     <t>cuando  no diligencie todos los campos obligatorios válidamente</t>
+  </si>
+  <si>
+    <t>E1-HU4</t>
+  </si>
+  <si>
+    <t>Desactivar Usuario</t>
+  </si>
+  <si>
+    <t>Como administrador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Para tener control del acceso de los usuarios </t>
+  </si>
+  <si>
+    <t>Quiero desactivar usuarios</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1008,6 +1023,13 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1261,7 +1283,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1329,9 +1351,6 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1362,9 +1381,6 @@
     <xf numFmtId="0" fontId="13" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1374,17 +1390,8 @@
     <xf numFmtId="0" fontId="13" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1418,7 +1425,35 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1431,43 +1466,33 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1476,35 +1501,43 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1746,22 +1779,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="36" customHeight="1">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="63"/>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="68"/>
     </row>
     <row r="2" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A2" s="64" t="s">
+      <c r="A2" s="69" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="65"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="66"/>
+      <c r="B2" s="70"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="71"/>
       <c r="F2" s="1"/>
     </row>
     <row r="3" spans="1:6" ht="14.25" customHeight="1">
@@ -1816,7 +1849,7 @@
       <c r="D6" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="100" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1824,7 +1857,12 @@
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
-      <c r="E7" s="9"/>
+      <c r="D7" s="14" t="s">
+        <v>303</v>
+      </c>
+      <c r="E7" s="99" t="s">
+        <v>304</v>
+      </c>
       <c r="F7" s="10"/>
     </row>
     <row r="8" spans="1:6" ht="14.25" customHeight="1">
@@ -1859,7 +1897,7 @@
       <c r="E10" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F10" s="36"/>
+      <c r="F10" s="35"/>
     </row>
     <row r="11" spans="1:6" ht="14.25" customHeight="1">
       <c r="A11" s="7"/>
@@ -1899,7 +1937,7 @@
       <c r="B15" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="36" t="s">
+      <c r="C15" s="35" t="s">
         <v>195</v>
       </c>
       <c r="D15" s="7" t="s">
@@ -1952,7 +1990,7 @@
       <c r="B20" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="36" t="s">
+      <c r="C20" s="35" t="s">
         <v>196</v>
       </c>
       <c r="D20" s="7" t="s">
@@ -2098,63 +2136,63 @@
       <c r="E33" s="13"/>
     </row>
     <row r="34" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A34" s="49">
+      <c r="A34" s="44">
         <v>7</v>
       </c>
-      <c r="B34" s="50" t="s">
+      <c r="B34" s="45" t="s">
         <v>241</v>
       </c>
-      <c r="C34" s="51" t="s">
+      <c r="C34" s="46" t="s">
         <v>242</v>
       </c>
-      <c r="D34" s="51" t="s">
+      <c r="D34" s="46" t="s">
         <v>243</v>
       </c>
-      <c r="E34" s="52" t="s">
+      <c r="E34" s="47" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A35" s="53"/>
-      <c r="B35" s="54"/>
-      <c r="C35" s="54"/>
-      <c r="D35" s="55" t="s">
+      <c r="A35" s="48"/>
+      <c r="B35" s="49"/>
+      <c r="C35" s="49"/>
+      <c r="D35" s="50" t="s">
         <v>245</v>
       </c>
-      <c r="E35" s="56" t="s">
+      <c r="E35" s="51" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="36" spans="1:5" s="43" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A36" s="53"/>
-      <c r="B36" s="54"/>
-      <c r="C36" s="54"/>
-      <c r="D36" s="55" t="s">
+    <row r="36" spans="1:5" s="40" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A36" s="48"/>
+      <c r="B36" s="49"/>
+      <c r="C36" s="49"/>
+      <c r="D36" s="50" t="s">
         <v>247</v>
       </c>
-      <c r="E36" s="56" t="s">
+      <c r="E36" s="51" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A37" s="53"/>
-      <c r="B37" s="54"/>
-      <c r="C37" s="54"/>
-      <c r="D37" s="55" t="s">
+      <c r="A37" s="48"/>
+      <c r="B37" s="49"/>
+      <c r="C37" s="49"/>
+      <c r="D37" s="50" t="s">
         <v>267</v>
       </c>
-      <c r="E37" s="56" t="s">
+      <c r="E37" s="51" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="14.25" customHeight="1" thickBot="1">
-      <c r="A38" s="57"/>
-      <c r="B38" s="57"/>
-      <c r="C38" s="57"/>
-      <c r="D38" s="58" t="s">
+      <c r="A38" s="52"/>
+      <c r="B38" s="52"/>
+      <c r="C38" s="52"/>
+      <c r="D38" s="53" t="s">
         <v>269</v>
       </c>
-      <c r="E38" s="59" t="s">
+      <c r="E38" s="54" t="s">
         <v>270</v>
       </c>
     </row>
@@ -3126,7 +3164,7 @@
     <mergeCell ref="A2:E2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3152,20 +3190,20 @@
   <sheetData>
     <row r="1" spans="1:9" ht="72" customHeight="1">
       <c r="A1" s="21"/>
-      <c r="B1" s="67" t="s">
+      <c r="B1" s="76" t="s">
         <v>53</v>
       </c>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="67" t="s">
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="G1" s="70"/>
-      <c r="H1" s="70"/>
-      <c r="I1" s="71"/>
-    </row>
-    <row r="2" spans="1:9" ht="14.25" customHeight="1">
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="78"/>
+    </row>
+    <row r="2" spans="1:9" ht="45">
       <c r="A2" s="22" t="s">
         <v>55</v>
       </c>
@@ -3195,119 +3233,119 @@
       </c>
     </row>
     <row r="3" spans="1:9" ht="45">
-      <c r="A3" s="81" t="s">
+      <c r="A3" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="86" t="s">
+      <c r="B3" s="81" t="s">
         <v>99</v>
       </c>
-      <c r="C3" s="86" t="s">
+      <c r="C3" s="81" t="s">
         <v>142</v>
       </c>
-      <c r="D3" s="86" t="s">
+      <c r="D3" s="81" t="s">
         <v>143</v>
       </c>
       <c r="E3" s="23">
         <v>1</v>
       </c>
-      <c r="F3" s="35" t="s">
+      <c r="F3" s="34" t="s">
         <v>285</v>
       </c>
-      <c r="G3" s="35" t="s">
+      <c r="G3" s="34" t="s">
         <v>147</v>
       </c>
-      <c r="H3" s="35" t="s">
+      <c r="H3" s="34" t="s">
         <v>288</v>
       </c>
-      <c r="I3" s="35" t="s">
+      <c r="I3" s="34" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="4" spans="1:9" s="45" customFormat="1" ht="45">
-      <c r="A4" s="81"/>
-      <c r="B4" s="90"/>
-      <c r="C4" s="90"/>
-      <c r="D4" s="90"/>
-      <c r="E4" s="28">
+    <row r="4" spans="1:9" s="41" customFormat="1" ht="45">
+      <c r="A4" s="79"/>
+      <c r="B4" s="82"/>
+      <c r="C4" s="82"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="27">
         <v>2</v>
       </c>
-      <c r="F4" s="35" t="s">
+      <c r="F4" s="34" t="s">
         <v>286</v>
       </c>
-      <c r="G4" s="35" t="s">
+      <c r="G4" s="34" t="s">
         <v>287</v>
       </c>
-      <c r="H4" s="35" t="s">
+      <c r="H4" s="34" t="s">
         <v>288</v>
       </c>
-      <c r="I4" s="35" t="s">
+      <c r="I4" s="34" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="57.75" customHeight="1">
-      <c r="A5" s="82"/>
+    <row r="5" spans="1:9" ht="30">
+      <c r="A5" s="80"/>
       <c r="B5" s="73"/>
       <c r="C5" s="73"/>
       <c r="D5" s="73"/>
       <c r="E5" s="23">
         <v>3</v>
       </c>
-      <c r="F5" s="35" t="s">
+      <c r="F5" s="34" t="s">
         <v>144</v>
       </c>
-      <c r="G5" s="35" t="s">
+      <c r="G5" s="34" t="s">
         <v>148</v>
       </c>
-      <c r="H5" s="35" t="s">
+      <c r="H5" s="34" t="s">
         <v>149</v>
       </c>
-      <c r="I5" s="35" t="s">
+      <c r="I5" s="34" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="45" customHeight="1">
-      <c r="A6" s="82"/>
+    <row r="6" spans="1:9" ht="45">
+      <c r="A6" s="80"/>
       <c r="B6" s="73"/>
       <c r="C6" s="73"/>
       <c r="D6" s="73"/>
       <c r="E6" s="23">
         <v>4</v>
       </c>
-      <c r="F6" s="35" t="s">
+      <c r="F6" s="34" t="s">
         <v>145</v>
       </c>
-      <c r="G6" s="35" t="s">
+      <c r="G6" s="34" t="s">
         <v>152</v>
       </c>
-      <c r="H6" s="35" t="s">
+      <c r="H6" s="34" t="s">
         <v>153</v>
       </c>
-      <c r="I6" s="35" t="s">
+      <c r="I6" s="34" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="30">
-      <c r="A7" s="82"/>
+      <c r="A7" s="80"/>
       <c r="B7" s="74"/>
       <c r="C7" s="74"/>
       <c r="D7" s="74"/>
       <c r="E7" s="23">
         <v>5</v>
       </c>
-      <c r="F7" s="35" t="s">
+      <c r="F7" s="34" t="s">
         <v>146</v>
       </c>
-      <c r="G7" s="35" t="s">
+      <c r="G7" s="34" t="s">
         <v>155</v>
       </c>
-      <c r="H7" s="35" t="s">
+      <c r="H7" s="34" t="s">
         <v>153</v>
       </c>
-      <c r="I7" s="35" t="s">
+      <c r="I7" s="34" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="14.25" customHeight="1">
+    <row r="8" spans="1:9">
       <c r="A8" s="25"/>
       <c r="B8" s="25"/>
       <c r="C8" s="25"/>
@@ -3318,78 +3356,78 @@
       <c r="H8" s="25"/>
       <c r="I8" s="25"/>
     </row>
-    <row r="9" spans="1:9" ht="43.5" customHeight="1">
-      <c r="A9" s="81" t="s">
+    <row r="9" spans="1:9" ht="30">
+      <c r="A9" s="79" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="86" t="s">
+      <c r="B9" s="81" t="s">
         <v>99</v>
       </c>
-      <c r="C9" s="86" t="s">
+      <c r="C9" s="81" t="s">
         <v>157</v>
       </c>
-      <c r="D9" s="86" t="s">
+      <c r="D9" s="81" t="s">
         <v>158</v>
       </c>
       <c r="E9" s="23">
         <v>1</v>
       </c>
-      <c r="F9" s="35" t="s">
+      <c r="F9" s="34" t="s">
         <v>290</v>
       </c>
-      <c r="G9" s="35" t="s">
+      <c r="G9" s="34" t="s">
         <v>160</v>
       </c>
-      <c r="H9" s="35" t="s">
+      <c r="H9" s="34" t="s">
         <v>161</v>
       </c>
-      <c r="I9" s="35" t="s">
+      <c r="I9" s="34" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="10" spans="1:9" s="45" customFormat="1" ht="43.5" customHeight="1">
-      <c r="A10" s="81"/>
-      <c r="B10" s="90"/>
-      <c r="C10" s="90"/>
-      <c r="D10" s="90"/>
-      <c r="E10" s="28">
+    <row r="10" spans="1:9" s="41" customFormat="1" ht="45">
+      <c r="A10" s="79"/>
+      <c r="B10" s="82"/>
+      <c r="C10" s="82"/>
+      <c r="D10" s="82"/>
+      <c r="E10" s="27">
         <v>2</v>
       </c>
-      <c r="F10" s="35" t="s">
+      <c r="F10" s="34" t="s">
         <v>291</v>
       </c>
-      <c r="G10" s="35" t="s">
+      <c r="G10" s="34" t="s">
         <v>292</v>
       </c>
-      <c r="H10" s="35" t="s">
+      <c r="H10" s="34" t="s">
         <v>293</v>
       </c>
-      <c r="I10" s="35" t="s">
+      <c r="I10" s="34" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="43.5" customHeight="1">
-      <c r="A11" s="82"/>
+    <row r="11" spans="1:9" ht="30">
+      <c r="A11" s="80"/>
       <c r="B11" s="73"/>
       <c r="C11" s="73"/>
       <c r="D11" s="73"/>
-      <c r="E11" s="28">
+      <c r="E11" s="27">
         <v>3</v>
       </c>
-      <c r="F11" s="35" t="s">
+      <c r="F11" s="34" t="s">
         <v>159</v>
       </c>
-      <c r="G11" s="35" t="s">
+      <c r="G11" s="34" t="s">
         <v>175</v>
       </c>
-      <c r="H11" s="35" t="s">
+      <c r="H11" s="34" t="s">
         <v>163</v>
       </c>
-      <c r="I11" s="35" t="s">
+      <c r="I11" s="34" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="14.25" customHeight="1">
+    <row r="12" spans="1:9">
       <c r="A12" s="25"/>
       <c r="B12" s="25"/>
       <c r="C12" s="25"/>
@@ -3401,35 +3439,35 @@
       <c r="I12" s="25"/>
     </row>
     <row r="13" spans="1:9" ht="30">
-      <c r="A13" s="37" t="s">
+      <c r="A13" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="37" t="s">
+      <c r="B13" s="36" t="s">
         <v>99</v>
       </c>
-      <c r="C13" s="37" t="s">
+      <c r="C13" s="36" t="s">
         <v>165</v>
       </c>
-      <c r="D13" s="37" t="s">
+      <c r="D13" s="36" t="s">
         <v>166</v>
       </c>
       <c r="E13" s="23">
         <v>1</v>
       </c>
-      <c r="F13" s="35" t="s">
+      <c r="F13" s="34" t="s">
         <v>81</v>
       </c>
-      <c r="G13" s="35" t="s">
+      <c r="G13" s="34" t="s">
         <v>176</v>
       </c>
-      <c r="H13" s="35" t="s">
+      <c r="H13" s="34" t="s">
         <v>167</v>
       </c>
-      <c r="I13" s="35" t="s">
+      <c r="I13" s="34" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="14.25" customHeight="1">
+    <row r="14" spans="1:9">
       <c r="A14" s="25"/>
       <c r="B14" s="25"/>
       <c r="C14" s="25"/>
@@ -3440,99 +3478,67 @@
       <c r="H14" s="25"/>
       <c r="I14" s="25"/>
     </row>
-    <row r="15" spans="1:9" ht="30">
+    <row r="15" spans="1:9">
       <c r="A15" s="83" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15" s="86" t="s">
-        <v>169</v>
-      </c>
-      <c r="C15" s="86" t="s">
-        <v>170</v>
-      </c>
-      <c r="D15" s="86" t="s">
-        <v>171</v>
-      </c>
-      <c r="E15" s="23">
+        <v>303</v>
+      </c>
+      <c r="B15" s="81" t="s">
+        <v>305</v>
+      </c>
+      <c r="C15" s="81" t="s">
+        <v>307</v>
+      </c>
+      <c r="D15" s="81" t="s">
+        <v>306</v>
+      </c>
+      <c r="E15" s="27">
         <v>1</v>
       </c>
-      <c r="F15" s="35" t="s">
-        <v>172</v>
-      </c>
-      <c r="G15" s="35" t="s">
-        <v>177</v>
-      </c>
-      <c r="H15" s="35" t="s">
-        <v>178</v>
-      </c>
-      <c r="I15" s="35" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" s="45" customFormat="1" ht="30">
-      <c r="A16" s="93"/>
-      <c r="B16" s="90"/>
-      <c r="C16" s="90"/>
-      <c r="D16" s="90"/>
-      <c r="E16" s="28">
+      <c r="F15" s="34"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="34"/>
+    </row>
+    <row r="16" spans="1:9" s="41" customFormat="1">
+      <c r="A16" s="84"/>
+      <c r="B16" s="82"/>
+      <c r="C16" s="82"/>
+      <c r="D16" s="82"/>
+      <c r="E16" s="27">
         <v>2</v>
       </c>
-      <c r="F16" s="35" t="s">
-        <v>295</v>
-      </c>
-      <c r="G16" s="35" t="s">
-        <v>296</v>
-      </c>
-      <c r="H16" s="35" t="s">
-        <v>297</v>
-      </c>
-      <c r="I16" s="35" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="90">
-      <c r="A17" s="84"/>
-      <c r="B17" s="78"/>
-      <c r="C17" s="78"/>
-      <c r="D17" s="78"/>
-      <c r="E17" s="23">
+      <c r="F16" s="34"/>
+      <c r="G16" s="34"/>
+      <c r="H16" s="34"/>
+      <c r="I16" s="34"/>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="85"/>
+      <c r="B17" s="87"/>
+      <c r="C17" s="87"/>
+      <c r="D17" s="87"/>
+      <c r="E17" s="27">
         <v>3</v>
       </c>
-      <c r="F17" s="35" t="s">
-        <v>173</v>
-      </c>
-      <c r="G17" s="35" t="s">
-        <v>180</v>
-      </c>
-      <c r="H17" s="35" t="s">
-        <v>182</v>
-      </c>
-      <c r="I17" s="35" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="30">
-      <c r="A18" s="85"/>
-      <c r="B18" s="87"/>
-      <c r="C18" s="87"/>
-      <c r="D18" s="87"/>
-      <c r="E18" s="23">
+      <c r="F17" s="34"/>
+      <c r="G17" s="34"/>
+      <c r="H17" s="34"/>
+      <c r="I17" s="34"/>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="86"/>
+      <c r="B18" s="88"/>
+      <c r="C18" s="88"/>
+      <c r="D18" s="88"/>
+      <c r="E18" s="27">
         <v>4</v>
       </c>
-      <c r="F18" s="35" t="s">
-        <v>174</v>
-      </c>
-      <c r="G18" s="35" t="s">
-        <v>181</v>
-      </c>
-      <c r="H18" s="35" t="s">
-        <v>183</v>
-      </c>
-      <c r="I18" s="35" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="14.25" customHeight="1">
+      <c r="F18" s="34"/>
+      <c r="G18" s="34"/>
+      <c r="H18" s="34"/>
+      <c r="I18" s="34"/>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" s="25"/>
       <c r="B19" s="25"/>
       <c r="C19" s="25"/>
@@ -3544,1009 +3550,1011 @@
       <c r="I19" s="25"/>
     </row>
     <row r="20" spans="1:9" ht="30">
-      <c r="A20" s="88" t="s">
+      <c r="A20" s="83" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="81" t="s">
+        <v>169</v>
+      </c>
+      <c r="C20" s="81" t="s">
+        <v>170</v>
+      </c>
+      <c r="D20" s="81" t="s">
+        <v>171</v>
+      </c>
+      <c r="E20" s="27">
+        <v>1</v>
+      </c>
+      <c r="F20" s="34" t="s">
+        <v>172</v>
+      </c>
+      <c r="G20" s="34" t="s">
+        <v>177</v>
+      </c>
+      <c r="H20" s="34" t="s">
+        <v>178</v>
+      </c>
+      <c r="I20" s="34" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="30">
+      <c r="A21" s="84"/>
+      <c r="B21" s="82"/>
+      <c r="C21" s="82"/>
+      <c r="D21" s="82"/>
+      <c r="E21" s="27">
+        <v>2</v>
+      </c>
+      <c r="F21" s="34" t="s">
+        <v>295</v>
+      </c>
+      <c r="G21" s="34" t="s">
+        <v>296</v>
+      </c>
+      <c r="H21" s="34" t="s">
+        <v>297</v>
+      </c>
+      <c r="I21" s="34" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="90">
+      <c r="A22" s="85"/>
+      <c r="B22" s="87"/>
+      <c r="C22" s="87"/>
+      <c r="D22" s="87"/>
+      <c r="E22" s="27">
+        <v>3</v>
+      </c>
+      <c r="F22" s="34" t="s">
+        <v>173</v>
+      </c>
+      <c r="G22" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="H22" s="34" t="s">
+        <v>182</v>
+      </c>
+      <c r="I22" s="34" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="30">
+      <c r="A23" s="86"/>
+      <c r="B23" s="88"/>
+      <c r="C23" s="88"/>
+      <c r="D23" s="88"/>
+      <c r="E23" s="27">
+        <v>4</v>
+      </c>
+      <c r="F23" s="34" t="s">
+        <v>174</v>
+      </c>
+      <c r="G23" s="34" t="s">
+        <v>181</v>
+      </c>
+      <c r="H23" s="34" t="s">
+        <v>183</v>
+      </c>
+      <c r="I23" s="34" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="25"/>
+      <c r="B24" s="25"/>
+      <c r="C24" s="25"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="25"/>
+      <c r="I24" s="25"/>
+    </row>
+    <row r="25" spans="1:9" ht="30">
+      <c r="A25" s="90" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="86" t="s">
+      <c r="B25" s="81" t="s">
         <v>169</v>
       </c>
-      <c r="C20" s="86" t="s">
+      <c r="C25" s="81" t="s">
         <v>185</v>
       </c>
-      <c r="D20" s="86" t="s">
+      <c r="D25" s="81" t="s">
         <v>186</v>
       </c>
-      <c r="E20" s="23">
+      <c r="E25" s="27">
         <v>1</v>
       </c>
-      <c r="F20" s="35" t="s">
+      <c r="F25" s="34" t="s">
         <v>187</v>
       </c>
-      <c r="G20" s="35" t="s">
+      <c r="G25" s="34" t="s">
         <v>189</v>
       </c>
-      <c r="H20" s="35" t="s">
+      <c r="H25" s="34" t="s">
         <v>190</v>
       </c>
-      <c r="I20" s="35" t="s">
+      <c r="I25" s="34" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="21" spans="1:9">
-      <c r="A21" s="73"/>
-      <c r="B21" s="73"/>
-      <c r="C21" s="73"/>
-      <c r="D21" s="73"/>
-      <c r="E21" s="23">
+    <row r="26" spans="1:9">
+      <c r="A26" s="73"/>
+      <c r="B26" s="73"/>
+      <c r="C26" s="73"/>
+      <c r="D26" s="73"/>
+      <c r="E26" s="27">
         <v>2</v>
       </c>
-      <c r="F21" s="35" t="s">
+      <c r="F26" s="34" t="s">
         <v>188</v>
       </c>
-      <c r="G21" s="35" t="s">
+      <c r="G26" s="34" t="s">
         <v>193</v>
       </c>
-      <c r="H21" s="35" t="s">
+      <c r="H26" s="34" t="s">
         <v>190</v>
       </c>
-      <c r="I21" s="35" t="s">
+      <c r="I26" s="34" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A22" s="25"/>
-      <c r="B22" s="25"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="26"/>
-      <c r="F22" s="25"/>
-      <c r="G22" s="25"/>
-      <c r="H22" s="25"/>
-      <c r="I22" s="25"/>
-    </row>
-    <row r="23" spans="1:9" ht="30">
-      <c r="A23" s="88" t="s">
+    <row r="27" spans="1:9">
+      <c r="A27" s="25"/>
+      <c r="B27" s="25"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25"/>
+      <c r="I27" s="25"/>
+    </row>
+    <row r="28" spans="1:9" ht="30">
+      <c r="A28" s="90" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="86" t="s">
+      <c r="B28" s="81" t="s">
         <v>211</v>
       </c>
-      <c r="C23" s="86" t="s">
+      <c r="C28" s="81" t="s">
         <v>197</v>
       </c>
-      <c r="D23" s="86" t="s">
+      <c r="D28" s="81" t="s">
         <v>198</v>
       </c>
-      <c r="E23" s="28">
+      <c r="E28" s="27">
         <v>1</v>
       </c>
-      <c r="F23" s="35" t="s">
+      <c r="F28" s="34" t="s">
         <v>199</v>
       </c>
-      <c r="G23" s="35" t="s">
+      <c r="G28" s="34" t="s">
         <v>202</v>
       </c>
-      <c r="H23" s="35" t="s">
+      <c r="H28" s="34" t="s">
         <v>203</v>
       </c>
-      <c r="I23" s="35" t="s">
+      <c r="I28" s="34" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="30">
-      <c r="A24" s="89"/>
-      <c r="B24" s="90"/>
-      <c r="C24" s="90"/>
-      <c r="D24" s="90"/>
-      <c r="E24" s="28">
+    <row r="29" spans="1:9" ht="30">
+      <c r="A29" s="92"/>
+      <c r="B29" s="82"/>
+      <c r="C29" s="82"/>
+      <c r="D29" s="82"/>
+      <c r="E29" s="27">
         <v>2</v>
       </c>
-      <c r="F24" s="35" t="s">
+      <c r="F29" s="34" t="s">
         <v>200</v>
       </c>
-      <c r="G24" s="35" t="s">
+      <c r="G29" s="34" t="s">
         <v>205</v>
       </c>
-      <c r="H24" s="35" t="s">
+      <c r="H29" s="34" t="s">
         <v>206</v>
       </c>
-      <c r="I24" s="35" t="s">
+      <c r="I29" s="34" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="30">
-      <c r="A25" s="73"/>
-      <c r="B25" s="73"/>
-      <c r="C25" s="73"/>
-      <c r="D25" s="73"/>
-      <c r="E25" s="28">
+    <row r="30" spans="1:9" ht="30">
+      <c r="A30" s="73"/>
+      <c r="B30" s="73"/>
+      <c r="C30" s="73"/>
+      <c r="D30" s="73"/>
+      <c r="E30" s="27">
         <v>3</v>
       </c>
-      <c r="F25" s="35" t="s">
+      <c r="F30" s="34" t="s">
         <v>201</v>
       </c>
-      <c r="G25" s="35" t="s">
+      <c r="G30" s="34" t="s">
         <v>208</v>
       </c>
-      <c r="H25" s="35" t="s">
+      <c r="H30" s="34" t="s">
         <v>209</v>
       </c>
-      <c r="I25" s="35" t="s">
+      <c r="I30" s="34" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="26" spans="1:9">
-      <c r="A26" s="25"/>
-      <c r="B26" s="25"/>
-      <c r="C26" s="25"/>
-      <c r="D26" s="25"/>
-      <c r="E26" s="26"/>
-      <c r="F26" s="25"/>
-      <c r="G26" s="25"/>
-      <c r="H26" s="25"/>
-      <c r="I26" s="25"/>
-    </row>
-    <row r="27" spans="1:9" ht="30">
-      <c r="A27" s="38" t="s">
+    <row r="31" spans="1:9">
+      <c r="A31" s="25"/>
+      <c r="B31" s="25"/>
+      <c r="C31" s="25"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="25"/>
+      <c r="G31" s="25"/>
+      <c r="H31" s="25"/>
+      <c r="I31" s="25"/>
+    </row>
+    <row r="32" spans="1:9" ht="30">
+      <c r="A32" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="B27" s="37" t="s">
+      <c r="B32" s="64" t="s">
         <v>211</v>
       </c>
-      <c r="C27" s="37" t="s">
+      <c r="C32" s="64" t="s">
         <v>212</v>
       </c>
-      <c r="D27" s="37" t="s">
+      <c r="D32" s="64" t="s">
         <v>213</v>
       </c>
-      <c r="E27" s="28">
+      <c r="E32" s="27">
         <v>1</v>
       </c>
-      <c r="F27" s="35" t="s">
+      <c r="F32" s="34" t="s">
         <v>81</v>
       </c>
-      <c r="G27" s="35" t="s">
+      <c r="G32" s="34" t="s">
         <v>214</v>
       </c>
-      <c r="H27" s="35" t="s">
+      <c r="H32" s="34" t="s">
         <v>215</v>
       </c>
-      <c r="I27" s="35" t="s">
+      <c r="I32" s="34" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A28" s="25"/>
-      <c r="B28" s="25"/>
-      <c r="C28" s="25"/>
-      <c r="D28" s="25"/>
-      <c r="E28" s="26"/>
-      <c r="F28" s="25"/>
-      <c r="G28" s="25"/>
-      <c r="H28" s="25"/>
-      <c r="I28" s="25"/>
-    </row>
-    <row r="29" spans="1:9" ht="30">
-      <c r="A29" s="38" t="s">
+    <row r="33" spans="1:9">
+      <c r="A33" s="25"/>
+      <c r="B33" s="25"/>
+      <c r="C33" s="25"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="25"/>
+      <c r="H33" s="25"/>
+      <c r="I33" s="25"/>
+    </row>
+    <row r="34" spans="1:9" ht="30">
+      <c r="A34" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="B29" s="37" t="s">
+      <c r="B34" s="64" t="s">
         <v>211</v>
       </c>
-      <c r="C29" s="37" t="s">
+      <c r="C34" s="64" t="s">
         <v>217</v>
       </c>
-      <c r="D29" s="37" t="s">
+      <c r="D34" s="64" t="s">
         <v>218</v>
       </c>
-      <c r="E29" s="28">
+      <c r="E34" s="27">
         <v>1</v>
       </c>
-      <c r="F29" s="35" t="s">
+      <c r="F34" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="G29" s="35" t="s">
+      <c r="G34" s="34" t="s">
         <v>220</v>
       </c>
-      <c r="H29" s="35" t="s">
+      <c r="H34" s="34" t="s">
         <v>221</v>
       </c>
-      <c r="I29" s="35" t="s">
+      <c r="I34" s="34" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="30" spans="1:9">
-      <c r="A30" s="25"/>
-      <c r="B30" s="25"/>
-      <c r="C30" s="25"/>
-      <c r="D30" s="25"/>
-      <c r="E30" s="26"/>
-      <c r="F30" s="25"/>
-      <c r="G30" s="25"/>
-      <c r="H30" s="25"/>
-      <c r="I30" s="25"/>
-    </row>
-    <row r="31" spans="1:9" ht="30">
-      <c r="A31" s="39" t="s">
+    <row r="35" spans="1:9">
+      <c r="A35" s="25"/>
+      <c r="B35" s="25"/>
+      <c r="C35" s="25"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="26"/>
+      <c r="F35" s="25"/>
+      <c r="G35" s="25"/>
+      <c r="H35" s="25"/>
+      <c r="I35" s="25"/>
+    </row>
+    <row r="36" spans="1:9" ht="30">
+      <c r="A36" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="B31" s="39" t="s">
+      <c r="B36" s="37" t="s">
         <v>223</v>
       </c>
-      <c r="C31" s="37" t="s">
+      <c r="C36" s="64" t="s">
         <v>224</v>
       </c>
-      <c r="D31" s="39" t="s">
+      <c r="D36" s="37" t="s">
         <v>225</v>
       </c>
-      <c r="E31" s="31">
+      <c r="E36" s="30">
         <v>1</v>
       </c>
-      <c r="F31" s="40" t="s">
+      <c r="F36" s="38" t="s">
         <v>199</v>
       </c>
-      <c r="G31" s="40" t="s">
+      <c r="G36" s="38" t="s">
         <v>226</v>
       </c>
-      <c r="H31" s="40" t="s">
+      <c r="H36" s="38" t="s">
         <v>233</v>
       </c>
-      <c r="I31" s="40" t="s">
+      <c r="I36" s="38" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A32" s="33"/>
-      <c r="B32" s="33"/>
-      <c r="C32" s="34"/>
-      <c r="D32" s="33"/>
-      <c r="E32" s="33"/>
-      <c r="F32" s="33"/>
-      <c r="G32" s="33"/>
-      <c r="H32" s="33"/>
-      <c r="I32" s="33"/>
-    </row>
-    <row r="33" spans="1:9" ht="30">
-      <c r="A33" s="38" t="s">
+    <row r="37" spans="1:9">
+      <c r="A37" s="32"/>
+      <c r="B37" s="32"/>
+      <c r="C37" s="33"/>
+      <c r="D37" s="32"/>
+      <c r="E37" s="32"/>
+      <c r="F37" s="32"/>
+      <c r="G37" s="32"/>
+      <c r="H37" s="32"/>
+      <c r="I37" s="32"/>
+    </row>
+    <row r="38" spans="1:9" ht="30">
+      <c r="A38" s="65" t="s">
         <v>31</v>
       </c>
-      <c r="B33" s="37" t="s">
+      <c r="B38" s="64" t="s">
         <v>228</v>
       </c>
-      <c r="C33" s="37" t="s">
+      <c r="C38" s="64" t="s">
         <v>229</v>
       </c>
-      <c r="D33" s="37" t="s">
+      <c r="D38" s="64" t="s">
         <v>230</v>
       </c>
-      <c r="E33" s="28">
+      <c r="E38" s="27">
         <v>1</v>
       </c>
-      <c r="F33" s="35" t="s">
+      <c r="F38" s="34" t="s">
         <v>231</v>
       </c>
-      <c r="G33" s="35" t="s">
+      <c r="G38" s="34" t="s">
         <v>202</v>
       </c>
-      <c r="H33" s="35" t="s">
+      <c r="H38" s="34" t="s">
         <v>232</v>
       </c>
-      <c r="I33" s="35" t="s">
+      <c r="I38" s="34" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A34" s="25"/>
-      <c r="B34" s="25"/>
-      <c r="C34" s="25"/>
-      <c r="D34" s="25"/>
-      <c r="E34" s="26"/>
-      <c r="F34" s="25"/>
-      <c r="G34" s="25"/>
-      <c r="H34" s="25"/>
-      <c r="I34" s="25"/>
-    </row>
-    <row r="35" spans="1:9" ht="30">
-      <c r="A35" s="38" t="s">
+    <row r="39" spans="1:9">
+      <c r="A39" s="25"/>
+      <c r="B39" s="25"/>
+      <c r="C39" s="25"/>
+      <c r="D39" s="25"/>
+      <c r="E39" s="26"/>
+      <c r="F39" s="25"/>
+      <c r="G39" s="25"/>
+      <c r="H39" s="25"/>
+      <c r="I39" s="25"/>
+    </row>
+    <row r="40" spans="1:9" ht="30">
+      <c r="A40" s="65" t="s">
         <v>33</v>
       </c>
-      <c r="B35" s="37" t="s">
+      <c r="B40" s="64" t="s">
         <v>228</v>
       </c>
-      <c r="C35" s="37" t="s">
+      <c r="C40" s="64" t="s">
         <v>235</v>
       </c>
-      <c r="D35" s="37" t="s">
+      <c r="D40" s="64" t="s">
         <v>236</v>
       </c>
-      <c r="E35" s="28">
+      <c r="E40" s="27">
         <v>1</v>
       </c>
-      <c r="F35" s="35" t="s">
+      <c r="F40" s="34" t="s">
         <v>237</v>
       </c>
-      <c r="G35" s="35" t="s">
+      <c r="G40" s="34" t="s">
         <v>238</v>
       </c>
-      <c r="H35" s="35" t="s">
+      <c r="H40" s="34" t="s">
         <v>239</v>
       </c>
-      <c r="I35" s="35" t="s">
+      <c r="I40" s="34" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A36" s="25"/>
-      <c r="B36" s="25"/>
-      <c r="C36" s="41"/>
-      <c r="D36" s="25"/>
-      <c r="E36" s="26"/>
-      <c r="F36" s="25"/>
-      <c r="G36" s="25"/>
-      <c r="H36" s="25"/>
-      <c r="I36" s="25"/>
-    </row>
-    <row r="37" spans="1:9" ht="30">
-      <c r="A37" s="79" t="s">
+    <row r="41" spans="1:9">
+      <c r="A41" s="25"/>
+      <c r="B41" s="25"/>
+      <c r="C41" s="39"/>
+      <c r="D41" s="25"/>
+      <c r="E41" s="26"/>
+      <c r="F41" s="25"/>
+      <c r="G41" s="25"/>
+      <c r="H41" s="25"/>
+      <c r="I41" s="25"/>
+    </row>
+    <row r="42" spans="1:9" ht="30">
+      <c r="A42" s="91" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="72" t="s">
+      <c r="B42" s="89" t="s">
         <v>64</v>
       </c>
-      <c r="C37" s="72" t="s">
+      <c r="C42" s="89" t="s">
         <v>65</v>
       </c>
-      <c r="D37" s="72" t="s">
+      <c r="D42" s="89" t="s">
         <v>66</v>
       </c>
-      <c r="E37" s="23">
+      <c r="E42" s="27">
         <v>1</v>
       </c>
-      <c r="F37" s="24" t="s">
+      <c r="F42" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="G37" s="35" t="s">
+      <c r="G42" s="34" t="s">
         <v>68</v>
       </c>
-      <c r="H37" s="24" t="s">
+      <c r="H42" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="I37" s="24" t="s">
+      <c r="I42" s="24" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="30">
-      <c r="A38" s="73"/>
-      <c r="B38" s="73"/>
-      <c r="C38" s="73"/>
-      <c r="D38" s="73"/>
-      <c r="E38" s="23">
+    <row r="43" spans="1:9" ht="30">
+      <c r="A43" s="73"/>
+      <c r="B43" s="73"/>
+      <c r="C43" s="73"/>
+      <c r="D43" s="73"/>
+      <c r="E43" s="27">
         <v>2</v>
       </c>
-      <c r="F38" s="24" t="s">
+      <c r="F43" s="24" t="s">
         <v>71</v>
       </c>
-      <c r="G38" s="24" t="s">
+      <c r="G43" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="H38" s="24" t="s">
+      <c r="H43" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="I38" s="24" t="s">
+      <c r="I43" s="24" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="30">
-      <c r="A39" s="74"/>
-      <c r="B39" s="74"/>
-      <c r="C39" s="74"/>
-      <c r="D39" s="74"/>
-      <c r="E39" s="23">
+    <row r="44" spans="1:9" ht="30">
+      <c r="A44" s="74"/>
+      <c r="B44" s="74"/>
+      <c r="C44" s="74"/>
+      <c r="D44" s="74"/>
+      <c r="E44" s="27">
         <v>3</v>
       </c>
-      <c r="F39" s="24" t="s">
+      <c r="F44" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="G39" s="24" t="s">
+      <c r="G44" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="H39" s="24" t="s">
+      <c r="H44" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="I39" s="24" t="s">
+      <c r="I44" s="24" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="40" spans="1:9">
-      <c r="A40" s="25"/>
-      <c r="B40" s="25"/>
-      <c r="C40" s="25"/>
-      <c r="D40" s="25"/>
-      <c r="E40" s="26"/>
-      <c r="F40" s="25"/>
-      <c r="G40" s="25"/>
-      <c r="H40" s="25"/>
-      <c r="I40" s="25"/>
-    </row>
-    <row r="41" spans="1:9" ht="30">
-      <c r="A41" s="81" t="s">
+    <row r="45" spans="1:9">
+      <c r="A45" s="25"/>
+      <c r="B45" s="25"/>
+      <c r="C45" s="25"/>
+      <c r="D45" s="25"/>
+      <c r="E45" s="26"/>
+      <c r="F45" s="25"/>
+      <c r="G45" s="25"/>
+      <c r="H45" s="25"/>
+      <c r="I45" s="25"/>
+    </row>
+    <row r="46" spans="1:9" ht="30">
+      <c r="A46" s="79" t="s">
         <v>39</v>
       </c>
-      <c r="B41" s="72" t="s">
+      <c r="B46" s="89" t="s">
         <v>64</v>
       </c>
-      <c r="C41" s="72" t="s">
+      <c r="C46" s="89" t="s">
         <v>79</v>
       </c>
-      <c r="D41" s="72" t="s">
+      <c r="D46" s="89" t="s">
         <v>80</v>
       </c>
-      <c r="E41" s="23">
+      <c r="E46" s="27">
         <v>1</v>
       </c>
-      <c r="F41" s="24" t="s">
+      <c r="F46" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="G41" s="24" t="s">
+      <c r="G46" s="24" t="s">
         <v>82</v>
       </c>
-      <c r="H41" s="24" t="s">
+      <c r="H46" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="I41" s="24" t="s">
+      <c r="I46" s="24" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="30">
-      <c r="A42" s="82"/>
-      <c r="B42" s="74"/>
-      <c r="C42" s="74"/>
-      <c r="D42" s="74"/>
-      <c r="E42" s="23">
+    <row r="47" spans="1:9" ht="30">
+      <c r="A47" s="80"/>
+      <c r="B47" s="74"/>
+      <c r="C47" s="74"/>
+      <c r="D47" s="74"/>
+      <c r="E47" s="27">
         <v>2</v>
       </c>
-      <c r="F42" s="24" t="s">
+      <c r="F47" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="G42" s="24" t="s">
+      <c r="G47" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="H42" s="24" t="s">
+      <c r="H47" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="I42" s="24" t="s">
+      <c r="I47" s="24" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="43" spans="1:9">
-      <c r="A43" s="25"/>
-      <c r="B43" s="25"/>
-      <c r="C43" s="25"/>
-      <c r="D43" s="25"/>
-      <c r="E43" s="26"/>
-      <c r="F43" s="25"/>
-      <c r="G43" s="25"/>
-      <c r="H43" s="25"/>
-      <c r="I43" s="25"/>
-    </row>
-    <row r="44" spans="1:9" ht="30">
-      <c r="A44" s="81" t="s">
+    <row r="48" spans="1:9">
+      <c r="A48" s="25"/>
+      <c r="B48" s="25"/>
+      <c r="C48" s="25"/>
+      <c r="D48" s="25"/>
+      <c r="E48" s="26"/>
+      <c r="F48" s="25"/>
+      <c r="G48" s="25"/>
+      <c r="H48" s="25"/>
+      <c r="I48" s="25"/>
+    </row>
+    <row r="49" spans="1:9" ht="30">
+      <c r="A49" s="79" t="s">
         <v>41</v>
       </c>
-      <c r="B44" s="72" t="s">
+      <c r="B49" s="89" t="s">
         <v>64</v>
       </c>
-      <c r="C44" s="72" t="s">
+      <c r="C49" s="89" t="s">
         <v>89</v>
       </c>
-      <c r="D44" s="72" t="s">
+      <c r="D49" s="89" t="s">
         <v>90</v>
       </c>
-      <c r="E44" s="23">
+      <c r="E49" s="27">
         <v>1</v>
       </c>
-      <c r="F44" s="24" t="s">
+      <c r="F49" s="24" t="s">
         <v>91</v>
       </c>
-      <c r="G44" s="24" t="s">
+      <c r="G49" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="H44" s="24" t="s">
+      <c r="H49" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="I44" s="24" t="s">
+      <c r="I49" s="24" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="45" spans="1:9">
-      <c r="A45" s="82"/>
-      <c r="B45" s="74"/>
-      <c r="C45" s="74"/>
-      <c r="D45" s="74"/>
-      <c r="E45" s="23">
+    <row r="50" spans="1:9">
+      <c r="A50" s="80"/>
+      <c r="B50" s="74"/>
+      <c r="C50" s="74"/>
+      <c r="D50" s="74"/>
+      <c r="E50" s="27">
         <v>2</v>
       </c>
-      <c r="F45" s="24" t="s">
+      <c r="F50" s="24" t="s">
         <v>95</v>
       </c>
-      <c r="G45" s="24" t="s">
+      <c r="G50" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="H45" s="24" t="s">
+      <c r="H50" s="24" t="s">
         <v>97</v>
       </c>
-      <c r="I45" s="24" t="s">
+      <c r="I50" s="24" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="46" spans="1:9">
-      <c r="A46" s="25"/>
-      <c r="B46" s="25"/>
-      <c r="C46" s="25"/>
-      <c r="D46" s="25"/>
-      <c r="E46" s="26"/>
-      <c r="F46" s="25"/>
-      <c r="G46" s="25"/>
-      <c r="H46" s="25"/>
-      <c r="I46" s="25"/>
-    </row>
-    <row r="47" spans="1:9" ht="30">
-      <c r="A47" s="81" t="s">
+    <row r="51" spans="1:9">
+      <c r="A51" s="25"/>
+      <c r="B51" s="25"/>
+      <c r="C51" s="25"/>
+      <c r="D51" s="25"/>
+      <c r="E51" s="26"/>
+      <c r="F51" s="25"/>
+      <c r="G51" s="25"/>
+      <c r="H51" s="25"/>
+      <c r="I51" s="25"/>
+    </row>
+    <row r="52" spans="1:9" ht="30">
+      <c r="A52" s="79" t="s">
         <v>45</v>
       </c>
-      <c r="B47" s="72" t="s">
+      <c r="B52" s="89" t="s">
         <v>99</v>
       </c>
-      <c r="C47" s="72" t="s">
+      <c r="C52" s="89" t="s">
         <v>100</v>
       </c>
-      <c r="D47" s="72" t="s">
+      <c r="D52" s="89" t="s">
         <v>101</v>
       </c>
-      <c r="E47" s="23">
+      <c r="E52" s="27">
         <v>1</v>
       </c>
-      <c r="F47" s="24" t="s">
+      <c r="F52" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="G47" s="24" t="s">
+      <c r="G52" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="H47" s="24" t="s">
+      <c r="H52" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="I47" s="24" t="s">
+      <c r="I52" s="24" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="30">
-      <c r="A48" s="82"/>
-      <c r="B48" s="73"/>
-      <c r="C48" s="73"/>
-      <c r="D48" s="73"/>
-      <c r="E48" s="23">
+    <row r="53" spans="1:9" ht="30">
+      <c r="A53" s="80"/>
+      <c r="B53" s="73"/>
+      <c r="C53" s="73"/>
+      <c r="D53" s="73"/>
+      <c r="E53" s="27">
         <v>2</v>
       </c>
-      <c r="F48" s="24" t="s">
+      <c r="F53" s="24" t="s">
         <v>106</v>
       </c>
-      <c r="G48" s="24" t="s">
+      <c r="G53" s="24" t="s">
         <v>107</v>
       </c>
-      <c r="H48" s="24" t="s">
+      <c r="H53" s="24" t="s">
         <v>108</v>
       </c>
-      <c r="I48" s="24" t="s">
+      <c r="I53" s="24" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="49" spans="1:9">
-      <c r="A49" s="82"/>
-      <c r="B49" s="74"/>
-      <c r="C49" s="74"/>
-      <c r="D49" s="74"/>
-      <c r="E49" s="23">
+    <row r="54" spans="1:9">
+      <c r="A54" s="80"/>
+      <c r="B54" s="74"/>
+      <c r="C54" s="74"/>
+      <c r="D54" s="74"/>
+      <c r="E54" s="27">
         <v>3</v>
       </c>
-      <c r="F49" s="24" t="s">
+      <c r="F54" s="24" t="s">
         <v>110</v>
       </c>
-      <c r="G49" s="24" t="s">
+      <c r="G54" s="24" t="s">
         <v>111</v>
       </c>
-      <c r="H49" s="24" t="s">
+      <c r="H54" s="24" t="s">
         <v>112</v>
       </c>
-      <c r="I49" s="24" t="s">
+      <c r="I54" s="24" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="50" spans="1:9">
-      <c r="A50" s="25"/>
-      <c r="B50" s="25"/>
-      <c r="C50" s="25"/>
-      <c r="D50" s="25"/>
-      <c r="E50" s="26"/>
-      <c r="F50" s="25"/>
-      <c r="G50" s="25"/>
-      <c r="H50" s="25"/>
-      <c r="I50" s="25"/>
-    </row>
-    <row r="51" spans="1:9" ht="45">
-      <c r="A51" s="27" t="s">
+    <row r="55" spans="1:9">
+      <c r="A55" s="25"/>
+      <c r="B55" s="25"/>
+      <c r="C55" s="25"/>
+      <c r="D55" s="25"/>
+      <c r="E55" s="26"/>
+      <c r="F55" s="25"/>
+      <c r="G55" s="25"/>
+      <c r="H55" s="25"/>
+      <c r="I55" s="25"/>
+    </row>
+    <row r="56" spans="1:9" ht="45">
+      <c r="A56" s="62" t="s">
         <v>47</v>
       </c>
-      <c r="B51" s="24" t="s">
+      <c r="B56" s="24" t="s">
         <v>99</v>
       </c>
-      <c r="C51" s="24" t="s">
+      <c r="C56" s="24" t="s">
         <v>114</v>
       </c>
-      <c r="D51" s="24" t="s">
+      <c r="D56" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="E51" s="23">
+      <c r="E56" s="27">
         <v>1</v>
       </c>
-      <c r="F51" s="24" t="s">
+      <c r="F56" s="24" t="s">
         <v>116</v>
       </c>
-      <c r="G51" s="24" t="s">
+      <c r="G56" s="24" t="s">
         <v>117</v>
       </c>
-      <c r="H51" s="24" t="s">
+      <c r="H56" s="24" t="s">
         <v>118</v>
       </c>
-      <c r="I51" s="24" t="s">
+      <c r="I56" s="24" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="52" spans="1:9">
-      <c r="A52" s="25"/>
-      <c r="B52" s="25"/>
-      <c r="C52" s="25"/>
-      <c r="D52" s="25"/>
-      <c r="E52" s="26"/>
-      <c r="F52" s="25"/>
-      <c r="G52" s="25"/>
-      <c r="H52" s="25"/>
-      <c r="I52" s="25"/>
-    </row>
-    <row r="53" spans="1:9" ht="30">
-      <c r="A53" s="79" t="s">
+    <row r="57" spans="1:9">
+      <c r="A57" s="25"/>
+      <c r="B57" s="25"/>
+      <c r="C57" s="25"/>
+      <c r="D57" s="25"/>
+      <c r="E57" s="26"/>
+      <c r="F57" s="25"/>
+      <c r="G57" s="25"/>
+      <c r="H57" s="25"/>
+      <c r="I57" s="25"/>
+    </row>
+    <row r="58" spans="1:9" s="41" customFormat="1" ht="30">
+      <c r="A58" s="91" t="s">
         <v>51</v>
       </c>
-      <c r="B53" s="72" t="s">
+      <c r="B58" s="89" t="s">
         <v>99</v>
       </c>
-      <c r="C53" s="72" t="s">
+      <c r="C58" s="89" t="s">
         <v>120</v>
       </c>
-      <c r="D53" s="72" t="s">
+      <c r="D58" s="89" t="s">
         <v>121</v>
       </c>
-      <c r="E53" s="23">
+      <c r="E58" s="27">
         <v>1</v>
       </c>
-      <c r="F53" s="24" t="s">
+      <c r="F58" s="24" t="s">
         <v>122</v>
       </c>
-      <c r="G53" s="24" t="s">
+      <c r="G58" s="24" t="s">
         <v>123</v>
       </c>
-      <c r="H53" s="24" t="s">
+      <c r="H58" s="24" t="s">
         <v>124</v>
       </c>
-      <c r="I53" s="24" t="s">
+      <c r="I58" s="24" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="30">
-      <c r="A54" s="73"/>
-      <c r="B54" s="73"/>
-      <c r="C54" s="73"/>
-      <c r="D54" s="73"/>
-      <c r="E54" s="23">
+    <row r="59" spans="1:9" ht="30">
+      <c r="A59" s="73"/>
+      <c r="B59" s="73"/>
+      <c r="C59" s="73"/>
+      <c r="D59" s="73"/>
+      <c r="E59" s="27">
         <v>2</v>
       </c>
-      <c r="F54" s="24" t="s">
+      <c r="F59" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="G54" s="24" t="s">
+      <c r="G59" s="24" t="s">
         <v>127</v>
       </c>
-      <c r="H54" s="24" t="s">
+      <c r="H59" s="24" t="s">
         <v>128</v>
       </c>
-      <c r="I54" s="24" t="s">
+      <c r="I59" s="24" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="55" spans="1:9">
-      <c r="A55" s="74"/>
-      <c r="B55" s="74"/>
-      <c r="C55" s="74"/>
-      <c r="D55" s="74"/>
-      <c r="E55" s="23">
+    <row r="60" spans="1:9">
+      <c r="A60" s="74"/>
+      <c r="B60" s="74"/>
+      <c r="C60" s="74"/>
+      <c r="D60" s="74"/>
+      <c r="E60" s="27">
         <v>3</v>
       </c>
-      <c r="F55" s="24" t="s">
+      <c r="F60" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="G55" s="24" t="s">
+      <c r="G60" s="24" t="s">
         <v>131</v>
       </c>
-      <c r="H55" s="24" t="s">
+      <c r="H60" s="24" t="s">
         <v>132</v>
       </c>
-      <c r="I55" s="24" t="s">
+      <c r="I60" s="24" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A56" s="25"/>
-      <c r="B56" s="25"/>
-      <c r="C56" s="25"/>
-      <c r="D56" s="25"/>
-      <c r="E56" s="26"/>
-      <c r="F56" s="25"/>
-      <c r="G56" s="25"/>
-      <c r="H56" s="25"/>
-      <c r="I56" s="25"/>
-    </row>
-    <row r="57" spans="1:9" ht="30">
-      <c r="A57" s="75" t="s">
+    <row r="61" spans="1:9">
+      <c r="A61" s="25"/>
+      <c r="B61" s="25"/>
+      <c r="C61" s="25"/>
+      <c r="D61" s="25"/>
+      <c r="E61" s="26"/>
+      <c r="F61" s="25"/>
+      <c r="G61" s="25"/>
+      <c r="H61" s="25"/>
+      <c r="I61" s="25"/>
+    </row>
+    <row r="62" spans="1:9" ht="30">
+      <c r="A62" s="93" t="s">
         <v>243</v>
       </c>
-      <c r="B57" s="77" t="s">
+      <c r="B62" s="96" t="s">
         <v>99</v>
       </c>
-      <c r="C57" s="75" t="s">
+      <c r="C62" s="93" t="s">
         <v>249</v>
       </c>
-      <c r="D57" s="75" t="s">
+      <c r="D62" s="93" t="s">
         <v>250</v>
       </c>
-      <c r="E57" s="47">
+      <c r="E62" s="42">
         <v>1</v>
       </c>
-      <c r="F57" s="48" t="s">
+      <c r="F62" s="43" t="s">
         <v>285</v>
       </c>
-      <c r="G57" s="48" t="s">
+      <c r="G62" s="43" t="s">
         <v>252</v>
       </c>
-      <c r="H57" s="48" t="s">
+      <c r="H62" s="43" t="s">
         <v>300</v>
       </c>
-      <c r="I57" s="48" t="s">
+      <c r="I62" s="43" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="58" spans="1:9" s="45" customFormat="1" ht="30">
-      <c r="A58" s="94"/>
-      <c r="B58" s="95"/>
-      <c r="C58" s="94"/>
-      <c r="D58" s="94"/>
-      <c r="E58" s="47">
+    <row r="63" spans="1:9" ht="30">
+      <c r="A63" s="94"/>
+      <c r="B63" s="97"/>
+      <c r="C63" s="94"/>
+      <c r="D63" s="94"/>
+      <c r="E63" s="42">
         <v>2</v>
       </c>
-      <c r="F58" s="48" t="s">
+      <c r="F63" s="43" t="s">
         <v>299</v>
       </c>
-      <c r="G58" s="48" t="s">
+      <c r="G63" s="43" t="s">
         <v>176</v>
       </c>
-      <c r="H58" s="48" t="s">
+      <c r="H63" s="43" t="s">
         <v>302</v>
       </c>
-      <c r="I58" s="48" t="s">
+      <c r="I63" s="43" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="30">
-      <c r="A59" s="76"/>
-      <c r="B59" s="76"/>
-      <c r="C59" s="76"/>
-      <c r="D59" s="76"/>
-      <c r="E59" s="47">
+    <row r="64" spans="1:9" ht="30">
+      <c r="A64" s="95"/>
+      <c r="B64" s="95"/>
+      <c r="C64" s="95"/>
+      <c r="D64" s="95"/>
+      <c r="E64" s="42">
         <v>3</v>
       </c>
-      <c r="F59" s="48" t="s">
+      <c r="F64" s="43" t="s">
         <v>251</v>
       </c>
-      <c r="G59" s="48" t="s">
+      <c r="G64" s="43" t="s">
         <v>254</v>
       </c>
-      <c r="H59" s="48" t="s">
+      <c r="H64" s="43" t="s">
         <v>255</v>
       </c>
-      <c r="I59" s="48" t="s">
+      <c r="I64" s="43" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A60" s="25"/>
-      <c r="B60" s="25"/>
-      <c r="C60" s="25"/>
-      <c r="D60" s="25"/>
-      <c r="E60" s="26"/>
-      <c r="F60" s="25"/>
-      <c r="G60" s="25"/>
-      <c r="H60" s="25"/>
-      <c r="I60" s="25"/>
-    </row>
-    <row r="61" spans="1:9" ht="30">
-      <c r="A61" s="46" t="s">
+    <row r="65" spans="1:9">
+      <c r="A65" s="25"/>
+      <c r="B65" s="25"/>
+      <c r="C65" s="25"/>
+      <c r="D65" s="25"/>
+      <c r="E65" s="26"/>
+      <c r="F65" s="25"/>
+      <c r="G65" s="25"/>
+      <c r="H65" s="25"/>
+      <c r="I65" s="25"/>
+    </row>
+    <row r="66" spans="1:9" ht="30">
+      <c r="A66" s="59" t="s">
         <v>245</v>
       </c>
-      <c r="B61" s="60" t="s">
+      <c r="B66" s="60" t="s">
         <v>99</v>
       </c>
-      <c r="C61" s="46" t="s">
+      <c r="C66" s="59" t="s">
         <v>257</v>
       </c>
-      <c r="D61" s="46" t="s">
+      <c r="D66" s="59" t="s">
         <v>258</v>
       </c>
-      <c r="E61" s="47">
+      <c r="E66" s="42">
         <v>1</v>
       </c>
-      <c r="F61" s="48" t="s">
+      <c r="F66" s="43" t="s">
         <v>264</v>
       </c>
-      <c r="G61" s="48" t="s">
+      <c r="G66" s="43" t="s">
         <v>259</v>
       </c>
-      <c r="H61" s="48" t="s">
+      <c r="H66" s="43" t="s">
         <v>260</v>
       </c>
-      <c r="I61" s="48" t="s">
+      <c r="I66" s="43" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A62" s="25"/>
-      <c r="B62" s="25"/>
-      <c r="C62" s="25"/>
-      <c r="D62" s="25"/>
-      <c r="E62" s="26"/>
-      <c r="F62" s="25"/>
-      <c r="G62" s="25"/>
-      <c r="H62" s="25"/>
-      <c r="I62" s="25"/>
-    </row>
-    <row r="63" spans="1:9" ht="30">
-      <c r="A63" s="46" t="s">
+    <row r="67" spans="1:9">
+      <c r="A67" s="25"/>
+      <c r="B67" s="25"/>
+      <c r="C67" s="25"/>
+      <c r="D67" s="25"/>
+      <c r="E67" s="26"/>
+      <c r="F67" s="25"/>
+      <c r="G67" s="25"/>
+      <c r="H67" s="25"/>
+      <c r="I67" s="25"/>
+    </row>
+    <row r="68" spans="1:9" ht="30">
+      <c r="A68" s="59" t="s">
         <v>247</v>
       </c>
-      <c r="B63" s="60" t="s">
+      <c r="B68" s="60" t="s">
         <v>99</v>
       </c>
-      <c r="C63" s="46" t="s">
+      <c r="C68" s="59" t="s">
         <v>262</v>
       </c>
-      <c r="D63" s="46" t="s">
+      <c r="D68" s="59" t="s">
         <v>263</v>
       </c>
-      <c r="E63" s="47">
+      <c r="E68" s="42">
         <v>1</v>
       </c>
-      <c r="F63" s="48" t="s">
+      <c r="F68" s="43" t="s">
         <v>265</v>
       </c>
-      <c r="G63" s="48" t="s">
+      <c r="G68" s="43" t="s">
         <v>176</v>
       </c>
-      <c r="H63" s="48" t="s">
+      <c r="H68" s="43" t="s">
         <v>266</v>
       </c>
-      <c r="I63" s="48" t="s">
+      <c r="I68" s="43" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A64" s="25"/>
-      <c r="B64" s="25"/>
-      <c r="C64" s="25"/>
-      <c r="D64" s="25"/>
-      <c r="E64" s="26"/>
-      <c r="F64" s="25"/>
-      <c r="G64" s="25"/>
-      <c r="H64" s="25"/>
-      <c r="I64" s="25"/>
-    </row>
-    <row r="65" spans="1:9" ht="30">
-      <c r="A65" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="B65" s="42" t="s">
-        <v>99</v>
-      </c>
-      <c r="C65" s="42" t="s">
-        <v>271</v>
-      </c>
-      <c r="D65" s="42" t="s">
-        <v>272</v>
-      </c>
-      <c r="E65" s="28">
-        <v>1</v>
-      </c>
-      <c r="F65" s="24" t="s">
-        <v>81</v>
-      </c>
-      <c r="G65" s="24" t="s">
-        <v>273</v>
-      </c>
-      <c r="H65" s="24" t="s">
-        <v>274</v>
-      </c>
-      <c r="I65" s="24" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A66" s="25"/>
-      <c r="B66" s="25"/>
-      <c r="C66" s="25"/>
-      <c r="D66" s="25"/>
-      <c r="E66" s="26"/>
-      <c r="F66" s="25"/>
-      <c r="G66" s="25"/>
-      <c r="H66" s="25"/>
-      <c r="I66" s="25"/>
-    </row>
-    <row r="67" spans="1:9" ht="30">
-      <c r="A67" s="79" t="s">
-        <v>269</v>
-      </c>
-      <c r="B67" s="72" t="s">
-        <v>99</v>
-      </c>
-      <c r="C67" s="72" t="s">
-        <v>276</v>
-      </c>
-      <c r="D67" s="72" t="s">
-        <v>277</v>
-      </c>
-      <c r="E67" s="28">
-        <v>1</v>
-      </c>
-      <c r="F67" s="24" t="s">
-        <v>278</v>
-      </c>
-      <c r="G67" s="24" t="s">
-        <v>280</v>
-      </c>
-      <c r="H67" s="24" t="s">
-        <v>281</v>
-      </c>
-      <c r="I67" s="24" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" ht="30">
-      <c r="A68" s="80"/>
-      <c r="B68" s="78"/>
-      <c r="C68" s="78"/>
-      <c r="D68" s="78"/>
-      <c r="E68" s="28">
-        <v>2</v>
-      </c>
-      <c r="F68" s="24" t="s">
-        <v>279</v>
-      </c>
-      <c r="G68" s="24" t="s">
-        <v>283</v>
-      </c>
-      <c r="H68" s="24" t="s">
-        <v>281</v>
-      </c>
-      <c r="I68" s="24" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" ht="14.25" customHeight="1">
+    <row r="69" spans="1:9">
       <c r="A69" s="25"/>
       <c r="B69" s="25"/>
       <c r="C69" s="25"/>
@@ -4557,1005 +4565,1234 @@
       <c r="H69" s="25"/>
       <c r="I69" s="25"/>
     </row>
-    <row r="70" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A70" s="29"/>
-      <c r="E70" s="29"/>
-    </row>
-    <row r="71" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A71" s="29"/>
-      <c r="E71" s="29"/>
-    </row>
-    <row r="72" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A72" s="29"/>
-      <c r="E72" s="29"/>
-    </row>
-    <row r="73" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A73" s="29"/>
-      <c r="E73" s="29"/>
-    </row>
-    <row r="74" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A74" s="29"/>
-      <c r="E74" s="29"/>
-    </row>
-    <row r="75" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A75" s="29"/>
-      <c r="E75" s="29"/>
-    </row>
-    <row r="76" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A76" s="29"/>
-      <c r="E76" s="29"/>
-    </row>
-    <row r="77" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A77" s="29"/>
-      <c r="E77" s="29"/>
-    </row>
-    <row r="78" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A78" s="29"/>
-      <c r="E78" s="29"/>
-    </row>
-    <row r="79" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A79" s="29"/>
-      <c r="E79" s="29"/>
-    </row>
-    <row r="80" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A80" s="29"/>
-      <c r="E80" s="29"/>
-    </row>
-    <row r="81" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A81" s="29"/>
-      <c r="E81" s="29"/>
-    </row>
-    <row r="82" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A82" s="29"/>
-      <c r="E82" s="29"/>
-    </row>
-    <row r="83" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A83" s="29"/>
-      <c r="E83" s="29"/>
-    </row>
-    <row r="84" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A84" s="29"/>
-      <c r="E84" s="29"/>
-    </row>
-    <row r="85" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A85" s="29"/>
-      <c r="E85" s="29"/>
-    </row>
-    <row r="86" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A86" s="29"/>
-      <c r="E86" s="29"/>
-    </row>
-    <row r="87" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A87" s="29"/>
-      <c r="E87" s="29"/>
-    </row>
-    <row r="88" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A88" s="29"/>
-      <c r="E88" s="29"/>
-    </row>
-    <row r="89" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A89" s="29"/>
-      <c r="E89" s="29"/>
-    </row>
-    <row r="90" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A90" s="29"/>
-      <c r="E90" s="29"/>
-    </row>
-    <row r="91" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A91" s="29"/>
-      <c r="E91" s="29"/>
-    </row>
-    <row r="92" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A92" s="29"/>
-      <c r="E92" s="29"/>
-    </row>
-    <row r="93" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A93" s="29"/>
-      <c r="E93" s="29"/>
-    </row>
-    <row r="94" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A94" s="29"/>
-      <c r="E94" s="29"/>
-    </row>
-    <row r="95" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A95" s="29"/>
-      <c r="E95" s="29"/>
-    </row>
-    <row r="96" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A96" s="29"/>
-      <c r="E96" s="29"/>
-    </row>
-    <row r="97" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A97" s="29"/>
-      <c r="E97" s="29"/>
-    </row>
-    <row r="98" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A98" s="29"/>
-      <c r="E98" s="29"/>
-    </row>
-    <row r="99" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A99" s="29"/>
-      <c r="E99" s="29"/>
-    </row>
-    <row r="100" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A100" s="29"/>
-      <c r="E100" s="29"/>
-    </row>
-    <row r="101" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A101" s="29"/>
-      <c r="E101" s="29"/>
-    </row>
-    <row r="102" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A102" s="29"/>
-      <c r="E102" s="29"/>
-    </row>
-    <row r="103" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A103" s="29"/>
-      <c r="E103" s="29"/>
-    </row>
-    <row r="104" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A104" s="29"/>
-      <c r="E104" s="29"/>
-    </row>
-    <row r="105" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A105" s="29"/>
-      <c r="E105" s="29"/>
-    </row>
-    <row r="106" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A106" s="29"/>
-      <c r="E106" s="29"/>
-    </row>
-    <row r="107" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A107" s="29"/>
-      <c r="E107" s="29"/>
-    </row>
-    <row r="108" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A108" s="29"/>
-      <c r="E108" s="29"/>
-    </row>
-    <row r="109" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A109" s="29"/>
-      <c r="E109" s="29"/>
-    </row>
-    <row r="110" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A110" s="29"/>
-      <c r="E110" s="29"/>
-    </row>
-    <row r="111" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A111" s="29"/>
-      <c r="E111" s="29"/>
-    </row>
-    <row r="112" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A112" s="29"/>
-      <c r="E112" s="29"/>
-    </row>
-    <row r="113" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A113" s="29"/>
-      <c r="E113" s="29"/>
-    </row>
-    <row r="114" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A114" s="29"/>
-      <c r="E114" s="29"/>
-    </row>
-    <row r="115" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A115" s="29"/>
-      <c r="E115" s="29"/>
-    </row>
-    <row r="116" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A116" s="29"/>
-      <c r="E116" s="29"/>
-    </row>
-    <row r="117" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A117" s="29"/>
-      <c r="E117" s="29"/>
-    </row>
-    <row r="118" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A118" s="29"/>
-      <c r="E118" s="29"/>
-    </row>
-    <row r="119" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A119" s="29"/>
-      <c r="E119" s="29"/>
-    </row>
-    <row r="120" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A120" s="29"/>
-      <c r="E120" s="29"/>
-    </row>
-    <row r="121" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A121" s="29"/>
-      <c r="E121" s="29"/>
-    </row>
-    <row r="122" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A122" s="29"/>
-      <c r="E122" s="29"/>
-    </row>
-    <row r="123" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A123" s="29"/>
-      <c r="E123" s="29"/>
-    </row>
-    <row r="124" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A124" s="29"/>
-      <c r="E124" s="29"/>
-    </row>
-    <row r="125" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A125" s="29"/>
-      <c r="E125" s="29"/>
-    </row>
-    <row r="126" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A126" s="29"/>
-      <c r="E126" s="29"/>
-    </row>
-    <row r="127" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A127" s="29"/>
-      <c r="E127" s="29"/>
-    </row>
-    <row r="128" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A128" s="29"/>
-      <c r="E128" s="29"/>
-    </row>
-    <row r="129" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A129" s="29"/>
-      <c r="E129" s="29"/>
-    </row>
-    <row r="130" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A130" s="29"/>
-      <c r="E130" s="29"/>
-    </row>
-    <row r="131" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A131" s="29"/>
-      <c r="E131" s="29"/>
+    <row r="70" spans="1:9" ht="30">
+      <c r="A70" s="61" t="s">
+        <v>267</v>
+      </c>
+      <c r="B70" s="58" t="s">
+        <v>99</v>
+      </c>
+      <c r="C70" s="58" t="s">
+        <v>271</v>
+      </c>
+      <c r="D70" s="58" t="s">
+        <v>272</v>
+      </c>
+      <c r="E70" s="27">
+        <v>1</v>
+      </c>
+      <c r="F70" s="24" t="s">
+        <v>81</v>
+      </c>
+      <c r="G70" s="24" t="s">
+        <v>273</v>
+      </c>
+      <c r="H70" s="24" t="s">
+        <v>274</v>
+      </c>
+      <c r="I70" s="24" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9">
+      <c r="A71" s="25"/>
+      <c r="B71" s="25"/>
+      <c r="C71" s="25"/>
+      <c r="D71" s="25"/>
+      <c r="E71" s="26"/>
+      <c r="F71" s="25"/>
+      <c r="G71" s="25"/>
+      <c r="H71" s="25"/>
+      <c r="I71" s="25"/>
+    </row>
+    <row r="72" spans="1:9" ht="30">
+      <c r="A72" s="91" t="s">
+        <v>269</v>
+      </c>
+      <c r="B72" s="89" t="s">
+        <v>99</v>
+      </c>
+      <c r="C72" s="89" t="s">
+        <v>276</v>
+      </c>
+      <c r="D72" s="89" t="s">
+        <v>277</v>
+      </c>
+      <c r="E72" s="27">
+        <v>1</v>
+      </c>
+      <c r="F72" s="24" t="s">
+        <v>278</v>
+      </c>
+      <c r="G72" s="24" t="s">
+        <v>280</v>
+      </c>
+      <c r="H72" s="24" t="s">
+        <v>281</v>
+      </c>
+      <c r="I72" s="24" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" ht="30">
+      <c r="A73" s="98"/>
+      <c r="B73" s="87"/>
+      <c r="C73" s="87"/>
+      <c r="D73" s="87"/>
+      <c r="E73" s="27">
+        <v>2</v>
+      </c>
+      <c r="F73" s="24" t="s">
+        <v>279</v>
+      </c>
+      <c r="G73" s="24" t="s">
+        <v>283</v>
+      </c>
+      <c r="H73" s="24" t="s">
+        <v>281</v>
+      </c>
+      <c r="I73" s="24" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9">
+      <c r="A74" s="25"/>
+      <c r="B74" s="25"/>
+      <c r="C74" s="25"/>
+      <c r="D74" s="25"/>
+      <c r="E74" s="26"/>
+      <c r="F74" s="25"/>
+      <c r="G74" s="25"/>
+      <c r="H74" s="25"/>
+      <c r="I74" s="25"/>
+    </row>
+    <row r="75" spans="1:9" ht="14.25">
+      <c r="A75" s="28"/>
+      <c r="E75" s="28"/>
+    </row>
+    <row r="76" spans="1:9" ht="14.25">
+      <c r="A76" s="28"/>
+      <c r="E76" s="28"/>
+    </row>
+    <row r="77" spans="1:9" ht="14.25">
+      <c r="A77" s="28"/>
+      <c r="E77" s="28"/>
+    </row>
+    <row r="78" spans="1:9" ht="14.25">
+      <c r="A78" s="28"/>
+      <c r="E78" s="28"/>
+    </row>
+    <row r="79" spans="1:9" ht="14.25">
+      <c r="A79" s="28"/>
+      <c r="E79" s="28"/>
+    </row>
+    <row r="80" spans="1:9" ht="14.25">
+      <c r="A80" s="28"/>
+      <c r="E80" s="28"/>
+    </row>
+    <row r="81" spans="1:8" ht="14.25">
+      <c r="A81" s="28"/>
+      <c r="E81" s="28"/>
+    </row>
+    <row r="82" spans="1:8" ht="14.25">
+      <c r="A82" s="28"/>
+      <c r="E82" s="28"/>
+    </row>
+    <row r="83" spans="1:8" ht="14.25">
+      <c r="A83" s="28"/>
+      <c r="E83" s="28"/>
+    </row>
+    <row r="84" spans="1:8" ht="14.25">
+      <c r="A84" s="28"/>
+      <c r="E84" s="28"/>
+    </row>
+    <row r="85" spans="1:8" ht="14.25">
+      <c r="A85" s="28"/>
+      <c r="E85" s="28"/>
+    </row>
+    <row r="86" spans="1:8" ht="14.25">
+      <c r="A86" s="28"/>
+      <c r="E86" s="28"/>
+    </row>
+    <row r="87" spans="1:8" ht="14.25">
+      <c r="A87" s="28"/>
+      <c r="E87" s="28"/>
+      <c r="H87" s="63"/>
+    </row>
+    <row r="88" spans="1:8" ht="14.25">
+      <c r="A88" s="28"/>
+      <c r="E88" s="28"/>
+    </row>
+    <row r="89" spans="1:8" ht="14.25">
+      <c r="A89" s="28"/>
+      <c r="E89" s="28"/>
+    </row>
+    <row r="90" spans="1:8" ht="14.25">
+      <c r="A90" s="28"/>
+      <c r="E90" s="28"/>
+    </row>
+    <row r="91" spans="1:8" ht="14.25">
+      <c r="A91" s="28"/>
+      <c r="E91" s="28"/>
+    </row>
+    <row r="92" spans="1:8" ht="14.25">
+      <c r="A92" s="28"/>
+      <c r="E92" s="28"/>
+    </row>
+    <row r="93" spans="1:8" ht="14.25">
+      <c r="A93" s="28"/>
+      <c r="E93" s="28"/>
+    </row>
+    <row r="94" spans="1:8" ht="14.25">
+      <c r="A94" s="28"/>
+      <c r="E94" s="28"/>
+    </row>
+    <row r="95" spans="1:8" ht="14.25">
+      <c r="A95" s="28"/>
+      <c r="E95" s="28"/>
+    </row>
+    <row r="96" spans="1:8" ht="14.25">
+      <c r="A96" s="28"/>
+      <c r="E96" s="28"/>
+    </row>
+    <row r="97" spans="1:5" ht="14.25">
+      <c r="A97" s="28"/>
+      <c r="E97" s="28"/>
+    </row>
+    <row r="98" spans="1:5" ht="14.25">
+      <c r="A98" s="28"/>
+      <c r="E98" s="28"/>
+    </row>
+    <row r="99" spans="1:5" ht="14.25">
+      <c r="A99" s="28"/>
+      <c r="E99" s="28"/>
+    </row>
+    <row r="100" spans="1:5" ht="14.25">
+      <c r="A100" s="28"/>
+      <c r="E100" s="28"/>
+    </row>
+    <row r="101" spans="1:5" ht="14.25">
+      <c r="A101" s="28"/>
+      <c r="E101" s="28"/>
+    </row>
+    <row r="102" spans="1:5" ht="14.25">
+      <c r="A102" s="28"/>
+      <c r="E102" s="28"/>
+    </row>
+    <row r="103" spans="1:5" ht="14.25">
+      <c r="A103" s="28"/>
+      <c r="E103" s="28"/>
+    </row>
+    <row r="104" spans="1:5" ht="14.25">
+      <c r="A104" s="28"/>
+      <c r="E104" s="28"/>
+    </row>
+    <row r="105" spans="1:5" ht="14.25">
+      <c r="A105" s="28"/>
+      <c r="E105" s="28"/>
+    </row>
+    <row r="106" spans="1:5" ht="14.25">
+      <c r="A106" s="28"/>
+      <c r="E106" s="28"/>
+    </row>
+    <row r="107" spans="1:5" ht="14.25">
+      <c r="A107" s="28"/>
+      <c r="E107" s="28"/>
+    </row>
+    <row r="108" spans="1:5" ht="14.25">
+      <c r="A108" s="28"/>
+      <c r="E108" s="28"/>
+    </row>
+    <row r="109" spans="1:5" ht="14.25">
+      <c r="A109" s="28"/>
+      <c r="E109" s="28"/>
+    </row>
+    <row r="110" spans="1:5" ht="14.25">
+      <c r="A110" s="28"/>
+      <c r="E110" s="28"/>
+    </row>
+    <row r="111" spans="1:5" ht="14.25">
+      <c r="A111" s="28"/>
+      <c r="E111" s="28"/>
+    </row>
+    <row r="112" spans="1:5" ht="14.25">
+      <c r="A112" s="28"/>
+      <c r="E112" s="28"/>
+    </row>
+    <row r="113" spans="1:5" ht="14.25">
+      <c r="A113" s="28"/>
+      <c r="E113" s="28"/>
+    </row>
+    <row r="114" spans="1:5" ht="14.25">
+      <c r="A114" s="28"/>
+      <c r="E114" s="28"/>
+    </row>
+    <row r="115" spans="1:5" ht="14.25">
+      <c r="A115" s="28"/>
+      <c r="E115" s="28"/>
+    </row>
+    <row r="116" spans="1:5" ht="14.25">
+      <c r="A116" s="28"/>
+      <c r="E116" s="28"/>
+    </row>
+    <row r="117" spans="1:5" ht="14.25">
+      <c r="A117" s="28"/>
+      <c r="E117" s="28"/>
+    </row>
+    <row r="118" spans="1:5" ht="14.25">
+      <c r="A118" s="28"/>
+      <c r="E118" s="28"/>
+    </row>
+    <row r="119" spans="1:5" ht="14.25">
+      <c r="A119" s="28"/>
+      <c r="E119" s="28"/>
+    </row>
+    <row r="120" spans="1:5" ht="14.25">
+      <c r="A120" s="28"/>
+      <c r="E120" s="28"/>
+    </row>
+    <row r="121" spans="1:5" ht="14.25">
+      <c r="A121" s="28"/>
+      <c r="E121" s="28"/>
+    </row>
+    <row r="122" spans="1:5" ht="14.25">
+      <c r="A122" s="28"/>
+      <c r="E122" s="28"/>
+    </row>
+    <row r="123" spans="1:5" ht="14.25">
+      <c r="A123" s="28"/>
+      <c r="E123" s="28"/>
+    </row>
+    <row r="124" spans="1:5" ht="14.25">
+      <c r="A124" s="28"/>
+      <c r="E124" s="28"/>
+    </row>
+    <row r="125" spans="1:5" ht="14.25">
+      <c r="A125" s="28"/>
+      <c r="E125" s="28"/>
+    </row>
+    <row r="126" spans="1:5" ht="14.25">
+      <c r="A126" s="28"/>
+      <c r="E126" s="28"/>
+    </row>
+    <row r="127" spans="1:5" ht="14.25">
+      <c r="A127" s="28"/>
+      <c r="E127" s="28"/>
+    </row>
+    <row r="128" spans="1:5" ht="14.25">
+      <c r="A128" s="28"/>
+      <c r="E128" s="28"/>
+    </row>
+    <row r="129" spans="1:5" ht="14.25">
+      <c r="A129" s="28"/>
+      <c r="E129" s="28"/>
+    </row>
+    <row r="130" spans="1:5" ht="14.25">
+      <c r="A130" s="28"/>
+      <c r="E130" s="28"/>
+    </row>
+    <row r="131" spans="1:5" ht="14.25">
+      <c r="A131" s="28"/>
+      <c r="E131" s="28"/>
     </row>
     <row r="132" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A132" s="29"/>
-      <c r="E132" s="29"/>
+      <c r="A132" s="28"/>
+      <c r="E132" s="28"/>
     </row>
     <row r="133" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A133" s="29"/>
-      <c r="E133" s="29"/>
+      <c r="A133" s="28"/>
+      <c r="E133" s="28"/>
     </row>
     <row r="134" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A134" s="29"/>
-      <c r="E134" s="29"/>
+      <c r="A134" s="28"/>
+      <c r="E134" s="28"/>
     </row>
     <row r="135" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A135" s="29"/>
-      <c r="E135" s="29"/>
+      <c r="A135" s="28"/>
+      <c r="E135" s="28"/>
     </row>
     <row r="136" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A136" s="29"/>
-      <c r="E136" s="29"/>
+      <c r="A136" s="28"/>
+      <c r="E136" s="28"/>
     </row>
     <row r="137" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A137" s="29"/>
-      <c r="E137" s="29"/>
+      <c r="A137" s="28"/>
+      <c r="E137" s="28"/>
     </row>
     <row r="138" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A138" s="29"/>
-      <c r="E138" s="29"/>
+      <c r="A138" s="28"/>
+      <c r="E138" s="28"/>
     </row>
     <row r="139" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A139" s="29"/>
-      <c r="E139" s="29"/>
+      <c r="A139" s="28"/>
+      <c r="E139" s="28"/>
     </row>
     <row r="140" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A140" s="29"/>
-      <c r="E140" s="29"/>
+      <c r="A140" s="28"/>
+      <c r="E140" s="28"/>
     </row>
     <row r="141" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A141" s="29"/>
-      <c r="E141" s="29"/>
+      <c r="A141" s="28"/>
+      <c r="E141" s="28"/>
     </row>
     <row r="142" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A142" s="29"/>
-      <c r="E142" s="29"/>
+      <c r="A142" s="28"/>
+      <c r="E142" s="28"/>
     </row>
     <row r="143" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A143" s="29"/>
-      <c r="E143" s="29"/>
+      <c r="A143" s="28"/>
+      <c r="E143" s="28"/>
     </row>
     <row r="144" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A144" s="29"/>
-      <c r="E144" s="29"/>
+      <c r="A144" s="28"/>
+      <c r="E144" s="28"/>
     </row>
     <row r="145" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A145" s="29"/>
-      <c r="E145" s="29"/>
+      <c r="A145" s="28"/>
+      <c r="E145" s="28"/>
     </row>
     <row r="146" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A146" s="29"/>
-      <c r="E146" s="29"/>
+      <c r="A146" s="28"/>
+      <c r="E146" s="28"/>
     </row>
     <row r="147" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A147" s="29"/>
-      <c r="E147" s="29"/>
+      <c r="A147" s="28"/>
+      <c r="E147" s="28"/>
     </row>
     <row r="148" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A148" s="29"/>
-      <c r="E148" s="29"/>
+      <c r="A148" s="28"/>
+      <c r="E148" s="28"/>
     </row>
     <row r="149" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A149" s="29"/>
-      <c r="E149" s="29"/>
+      <c r="A149" s="28"/>
+      <c r="E149" s="28"/>
     </row>
     <row r="150" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A150" s="29"/>
-      <c r="E150" s="29"/>
+      <c r="A150" s="28"/>
+      <c r="E150" s="28"/>
     </row>
     <row r="151" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A151" s="29"/>
-      <c r="E151" s="29"/>
+      <c r="A151" s="28"/>
+      <c r="E151" s="28"/>
     </row>
     <row r="152" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A152" s="29"/>
-      <c r="E152" s="29"/>
+      <c r="A152" s="28"/>
+      <c r="E152" s="28"/>
     </row>
     <row r="153" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A153" s="29"/>
-      <c r="E153" s="29"/>
+      <c r="A153" s="28"/>
+      <c r="E153" s="28"/>
     </row>
     <row r="154" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A154" s="29"/>
-      <c r="E154" s="29"/>
+      <c r="A154" s="28"/>
+      <c r="E154" s="28"/>
     </row>
     <row r="155" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A155" s="29"/>
-      <c r="E155" s="29"/>
+      <c r="A155" s="28"/>
+      <c r="E155" s="28"/>
     </row>
     <row r="156" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A156" s="29"/>
-      <c r="E156" s="29"/>
+      <c r="A156" s="28"/>
+      <c r="E156" s="28"/>
     </row>
     <row r="157" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A157" s="29"/>
-      <c r="E157" s="29"/>
+      <c r="A157" s="28"/>
+      <c r="E157" s="28"/>
     </row>
     <row r="158" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A158" s="29"/>
-      <c r="E158" s="29"/>
+      <c r="A158" s="28"/>
+      <c r="E158" s="28"/>
     </row>
     <row r="159" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A159" s="29"/>
-      <c r="E159" s="29"/>
+      <c r="A159" s="28"/>
+      <c r="E159" s="28"/>
     </row>
     <row r="160" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A160" s="29"/>
-      <c r="E160" s="29"/>
+      <c r="A160" s="28"/>
+      <c r="E160" s="28"/>
     </row>
     <row r="161" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A161" s="29"/>
-      <c r="E161" s="29"/>
+      <c r="A161" s="28"/>
+      <c r="E161" s="28"/>
     </row>
     <row r="162" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A162" s="29"/>
-      <c r="E162" s="29"/>
+      <c r="A162" s="28"/>
+      <c r="E162" s="28"/>
     </row>
     <row r="163" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A163" s="29"/>
-      <c r="E163" s="29"/>
+      <c r="A163" s="28"/>
+      <c r="E163" s="28"/>
     </row>
     <row r="164" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A164" s="29"/>
-      <c r="E164" s="29"/>
+      <c r="A164" s="28"/>
+      <c r="E164" s="28"/>
     </row>
     <row r="165" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A165" s="29"/>
-      <c r="E165" s="29"/>
+      <c r="A165" s="28"/>
+      <c r="E165" s="28"/>
     </row>
     <row r="166" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A166" s="29"/>
-      <c r="E166" s="29"/>
+      <c r="A166" s="28"/>
+      <c r="E166" s="28"/>
     </row>
     <row r="167" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A167" s="29"/>
-      <c r="E167" s="29"/>
+      <c r="A167" s="28"/>
+      <c r="E167" s="28"/>
     </row>
     <row r="168" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A168" s="29"/>
-      <c r="E168" s="29"/>
+      <c r="A168" s="28"/>
+      <c r="E168" s="28"/>
     </row>
     <row r="169" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A169" s="29"/>
-      <c r="E169" s="29"/>
+      <c r="A169" s="28"/>
+      <c r="E169" s="28"/>
     </row>
     <row r="170" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A170" s="29"/>
-      <c r="E170" s="29"/>
+      <c r="A170" s="28"/>
+      <c r="E170" s="28"/>
     </row>
     <row r="171" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A171" s="29"/>
-      <c r="E171" s="29"/>
+      <c r="A171" s="28"/>
+      <c r="E171" s="28"/>
     </row>
     <row r="172" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A172" s="29"/>
-      <c r="E172" s="29"/>
+      <c r="A172" s="28"/>
+      <c r="E172" s="28"/>
     </row>
     <row r="173" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A173" s="29"/>
-      <c r="E173" s="29"/>
+      <c r="A173" s="28"/>
+      <c r="E173" s="28"/>
     </row>
     <row r="174" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A174" s="29"/>
-      <c r="E174" s="29"/>
+      <c r="A174" s="28"/>
+      <c r="E174" s="28"/>
     </row>
     <row r="175" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A175" s="29"/>
-      <c r="E175" s="29"/>
+      <c r="A175" s="28"/>
+      <c r="E175" s="28"/>
     </row>
     <row r="176" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A176" s="29"/>
-      <c r="E176" s="29"/>
+      <c r="A176" s="28"/>
+      <c r="E176" s="28"/>
     </row>
     <row r="177" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A177" s="29"/>
-      <c r="E177" s="29"/>
+      <c r="A177" s="28"/>
+      <c r="E177" s="28"/>
     </row>
     <row r="178" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A178" s="29"/>
-      <c r="E178" s="29"/>
+      <c r="A178" s="28"/>
+      <c r="E178" s="28"/>
     </row>
     <row r="179" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A179" s="29"/>
-      <c r="E179" s="29"/>
+      <c r="A179" s="28"/>
+      <c r="E179" s="28"/>
     </row>
     <row r="180" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A180" s="29"/>
-      <c r="E180" s="29"/>
+      <c r="A180" s="28"/>
+      <c r="E180" s="28"/>
     </row>
     <row r="181" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A181" s="29"/>
-      <c r="E181" s="29"/>
+      <c r="A181" s="28"/>
+      <c r="E181" s="28"/>
     </row>
     <row r="182" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A182" s="29"/>
-      <c r="E182" s="29"/>
+      <c r="A182" s="28"/>
+      <c r="E182" s="28"/>
     </row>
     <row r="183" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A183" s="29"/>
-      <c r="E183" s="29"/>
+      <c r="A183" s="28"/>
+      <c r="E183" s="28"/>
     </row>
     <row r="184" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A184" s="29"/>
-      <c r="E184" s="29"/>
+      <c r="A184" s="28"/>
+      <c r="E184" s="28"/>
     </row>
     <row r="185" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A185" s="29"/>
-      <c r="E185" s="29"/>
+      <c r="A185" s="28"/>
+      <c r="E185" s="28"/>
     </row>
     <row r="186" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A186" s="29"/>
-      <c r="E186" s="29"/>
+      <c r="A186" s="28"/>
+      <c r="E186" s="28"/>
     </row>
     <row r="187" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A187" s="29"/>
-      <c r="E187" s="29"/>
+      <c r="A187" s="28"/>
+      <c r="E187" s="28"/>
     </row>
     <row r="188" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A188" s="29"/>
-      <c r="E188" s="29"/>
+      <c r="A188" s="28"/>
+      <c r="E188" s="28"/>
     </row>
     <row r="189" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A189" s="29"/>
-      <c r="E189" s="29"/>
+      <c r="A189" s="28"/>
+      <c r="E189" s="28"/>
     </row>
     <row r="190" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A190" s="29"/>
-      <c r="E190" s="29"/>
+      <c r="A190" s="28"/>
+      <c r="E190" s="28"/>
     </row>
     <row r="191" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A191" s="29"/>
-      <c r="E191" s="29"/>
+      <c r="A191" s="28"/>
+      <c r="E191" s="28"/>
     </row>
     <row r="192" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A192" s="29"/>
-      <c r="E192" s="29"/>
+      <c r="A192" s="28"/>
+      <c r="E192" s="28"/>
     </row>
     <row r="193" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A193" s="29"/>
-      <c r="E193" s="29"/>
+      <c r="A193" s="28"/>
+      <c r="E193" s="28"/>
     </row>
     <row r="194" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A194" s="29"/>
-      <c r="E194" s="29"/>
+      <c r="A194" s="28"/>
+      <c r="E194" s="28"/>
     </row>
     <row r="195" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A195" s="29"/>
-      <c r="E195" s="29"/>
+      <c r="A195" s="28"/>
+      <c r="E195" s="28"/>
     </row>
     <row r="196" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A196" s="29"/>
-      <c r="E196" s="29"/>
+      <c r="A196" s="28"/>
+      <c r="E196" s="28"/>
     </row>
     <row r="197" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A197" s="29"/>
-      <c r="E197" s="29"/>
+      <c r="A197" s="28"/>
+      <c r="E197" s="28"/>
     </row>
     <row r="198" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A198" s="29"/>
-      <c r="E198" s="29"/>
+      <c r="A198" s="28"/>
+      <c r="E198" s="28"/>
     </row>
     <row r="199" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A199" s="29"/>
-      <c r="E199" s="29"/>
+      <c r="A199" s="28"/>
+      <c r="E199" s="28"/>
     </row>
     <row r="200" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A200" s="29"/>
-      <c r="E200" s="29"/>
+      <c r="A200" s="28"/>
+      <c r="E200" s="28"/>
     </row>
     <row r="201" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A201" s="29"/>
-      <c r="E201" s="29"/>
+      <c r="A201" s="28"/>
+      <c r="E201" s="28"/>
     </row>
     <row r="202" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A202" s="29"/>
-      <c r="E202" s="29"/>
+      <c r="A202" s="28"/>
+      <c r="E202" s="28"/>
     </row>
     <row r="203" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A203" s="29"/>
-      <c r="E203" s="29"/>
+      <c r="A203" s="28"/>
+      <c r="E203" s="28"/>
     </row>
     <row r="204" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A204" s="29"/>
-      <c r="E204" s="29"/>
+      <c r="A204" s="28"/>
+      <c r="E204" s="28"/>
     </row>
     <row r="205" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A205" s="29"/>
-      <c r="E205" s="29"/>
+      <c r="A205" s="28"/>
+      <c r="E205" s="28"/>
     </row>
     <row r="206" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A206" s="29"/>
-      <c r="E206" s="29"/>
+      <c r="A206" s="28"/>
+      <c r="E206" s="28"/>
     </row>
     <row r="207" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A207" s="29"/>
-      <c r="E207" s="29"/>
+      <c r="A207" s="28"/>
+      <c r="E207" s="28"/>
     </row>
     <row r="208" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A208" s="29"/>
-      <c r="E208" s="29"/>
+      <c r="A208" s="28"/>
+      <c r="E208" s="28"/>
     </row>
     <row r="209" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A209" s="29"/>
-      <c r="E209" s="29"/>
+      <c r="A209" s="28"/>
+      <c r="E209" s="28"/>
     </row>
     <row r="210" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A210" s="29"/>
-      <c r="E210" s="29"/>
+      <c r="A210" s="28"/>
+      <c r="E210" s="28"/>
     </row>
     <row r="211" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A211" s="29"/>
-      <c r="E211" s="29"/>
+      <c r="A211" s="28"/>
+      <c r="E211" s="28"/>
     </row>
     <row r="212" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A212" s="29"/>
-      <c r="E212" s="29"/>
+      <c r="A212" s="28"/>
+      <c r="E212" s="28"/>
     </row>
     <row r="213" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A213" s="29"/>
-      <c r="E213" s="29"/>
+      <c r="A213" s="28"/>
+      <c r="E213" s="28"/>
     </row>
     <row r="214" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A214" s="29"/>
-      <c r="E214" s="29"/>
-    </row>
-    <row r="215" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A215" s="29"/>
-      <c r="E215" s="29"/>
-    </row>
-    <row r="216" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A216" s="29"/>
-      <c r="E216" s="29"/>
-    </row>
-    <row r="217" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A217" s="29"/>
-      <c r="E217" s="29"/>
-    </row>
-    <row r="218" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A218" s="29"/>
-      <c r="E218" s="29"/>
-    </row>
-    <row r="219" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A219" s="29"/>
-      <c r="E219" s="29"/>
-    </row>
-    <row r="220" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A220" s="29"/>
-      <c r="E220" s="29"/>
-    </row>
-    <row r="221" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A221" s="29"/>
-      <c r="E221" s="29"/>
-    </row>
-    <row r="222" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A222" s="29"/>
-      <c r="E222" s="29"/>
-    </row>
-    <row r="223" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A223" s="29"/>
-      <c r="E223" s="29"/>
-    </row>
-    <row r="224" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A224" s="29"/>
-      <c r="E224" s="29"/>
-    </row>
-    <row r="225" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A225" s="29"/>
-      <c r="E225" s="29"/>
-    </row>
-    <row r="226" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A226" s="29"/>
-      <c r="E226" s="29"/>
-    </row>
-    <row r="227" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A227" s="29"/>
-      <c r="E227" s="29"/>
-    </row>
-    <row r="228" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A228" s="29"/>
-      <c r="E228" s="29"/>
-    </row>
-    <row r="229" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A229" s="29"/>
-      <c r="E229" s="29"/>
-    </row>
-    <row r="230" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A230" s="29"/>
-      <c r="E230" s="29"/>
-    </row>
-    <row r="231" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A231" s="29"/>
-      <c r="E231" s="29"/>
-    </row>
-    <row r="232" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A232" s="29"/>
-      <c r="E232" s="29"/>
-    </row>
-    <row r="233" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A233" s="29"/>
-      <c r="E233" s="29"/>
-    </row>
+      <c r="A214" s="28"/>
+      <c r="E214" s="28"/>
+    </row>
+    <row r="215" spans="1:5" ht="14.25" customHeight="1"/>
+    <row r="216" spans="1:5" ht="14.25" customHeight="1"/>
+    <row r="217" spans="1:5" ht="14.25" customHeight="1"/>
+    <row r="218" spans="1:5" ht="14.25" customHeight="1"/>
+    <row r="219" spans="1:5" ht="14.25" customHeight="1"/>
+    <row r="220" spans="1:5" ht="14.25" customHeight="1"/>
+    <row r="221" spans="1:5" ht="14.25" customHeight="1"/>
+    <row r="222" spans="1:5" ht="14.25" customHeight="1"/>
+    <row r="223" spans="1:5" ht="14.25" customHeight="1"/>
+    <row r="224" spans="1:5" ht="14.25" customHeight="1"/>
+    <row r="225" spans="1:5" ht="14.25" customHeight="1"/>
+    <row r="226" spans="1:5" ht="14.25" customHeight="1"/>
+    <row r="227" spans="1:5" ht="14.25" customHeight="1"/>
+    <row r="228" spans="1:5" ht="14.25" customHeight="1"/>
+    <row r="229" spans="1:5" ht="14.25" customHeight="1"/>
+    <row r="230" spans="1:5" ht="14.25" customHeight="1"/>
+    <row r="231" spans="1:5" ht="14.25" customHeight="1"/>
+    <row r="232" spans="1:5" ht="14.25" customHeight="1"/>
+    <row r="233" spans="1:5" ht="14.25" customHeight="1"/>
     <row r="234" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A234" s="29"/>
-      <c r="E234" s="29"/>
+      <c r="A234" s="28"/>
+      <c r="E234" s="28"/>
     </row>
     <row r="235" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A235" s="29"/>
-      <c r="E235" s="29"/>
+      <c r="A235" s="28"/>
+      <c r="E235" s="28"/>
     </row>
     <row r="236" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A236" s="29"/>
-      <c r="E236" s="29"/>
+      <c r="A236" s="28"/>
+      <c r="E236" s="28"/>
     </row>
     <row r="237" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A237" s="29"/>
-      <c r="E237" s="29"/>
+      <c r="A237" s="28"/>
+      <c r="E237" s="28"/>
     </row>
     <row r="238" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A238" s="29"/>
-      <c r="E238" s="29"/>
+      <c r="A238" s="28"/>
+      <c r="E238" s="28"/>
     </row>
     <row r="239" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A239" s="29"/>
-      <c r="E239" s="29"/>
+      <c r="A239" s="28"/>
+      <c r="E239" s="28"/>
     </row>
     <row r="240" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A240" s="29"/>
-      <c r="E240" s="29"/>
+      <c r="A240" s="28"/>
+      <c r="E240" s="28"/>
     </row>
     <row r="241" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A241" s="29"/>
-      <c r="E241" s="29"/>
+      <c r="A241" s="28"/>
+      <c r="E241" s="28"/>
     </row>
     <row r="242" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A242" s="29"/>
-      <c r="E242" s="29"/>
+      <c r="A242" s="28"/>
+      <c r="E242" s="28"/>
     </row>
     <row r="243" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A243" s="29"/>
-      <c r="E243" s="29"/>
+      <c r="A243" s="28"/>
+      <c r="E243" s="28"/>
     </row>
     <row r="244" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A244" s="29"/>
-      <c r="E244" s="29"/>
+      <c r="A244" s="28"/>
+      <c r="E244" s="28"/>
     </row>
     <row r="245" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A245" s="29"/>
-      <c r="E245" s="29"/>
+      <c r="A245" s="28"/>
+      <c r="E245" s="28"/>
     </row>
     <row r="246" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A246" s="29"/>
-      <c r="E246" s="29"/>
+      <c r="A246" s="28"/>
+      <c r="E246" s="28"/>
     </row>
     <row r="247" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A247" s="29"/>
-      <c r="E247" s="29"/>
+      <c r="A247" s="28"/>
+      <c r="E247" s="28"/>
     </row>
     <row r="248" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A248" s="29"/>
-      <c r="E248" s="29"/>
+      <c r="A248" s="28"/>
+      <c r="E248" s="28"/>
     </row>
     <row r="249" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A249" s="29"/>
-      <c r="E249" s="29"/>
+      <c r="A249" s="28"/>
+      <c r="E249" s="28"/>
     </row>
     <row r="250" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A250" s="29"/>
-      <c r="E250" s="29"/>
+      <c r="A250" s="28"/>
+      <c r="E250" s="28"/>
     </row>
     <row r="251" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A251" s="29"/>
-      <c r="E251" s="29"/>
+      <c r="A251" s="28"/>
+      <c r="E251" s="28"/>
     </row>
     <row r="252" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A252" s="29"/>
-      <c r="E252" s="29"/>
+      <c r="A252" s="28"/>
+      <c r="E252" s="28"/>
     </row>
     <row r="253" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A253" s="29"/>
-      <c r="E253" s="29"/>
+      <c r="A253" s="28"/>
+      <c r="E253" s="28"/>
     </row>
     <row r="254" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A254" s="29"/>
-      <c r="E254" s="29"/>
+      <c r="A254" s="28"/>
+      <c r="E254" s="28"/>
     </row>
     <row r="255" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A255" s="29"/>
-      <c r="E255" s="29"/>
+      <c r="A255" s="28"/>
+      <c r="E255" s="28"/>
     </row>
     <row r="256" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A256" s="29"/>
-      <c r="E256" s="29"/>
-    </row>
-    <row r="257" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A257" s="29"/>
-      <c r="E257" s="29"/>
-    </row>
-    <row r="258" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A258" s="29"/>
-      <c r="E258" s="29"/>
-    </row>
-    <row r="259" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A259" s="29"/>
-      <c r="E259" s="29"/>
-    </row>
-    <row r="260" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A260" s="29"/>
-      <c r="E260" s="29"/>
-    </row>
-    <row r="261" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A261" s="29"/>
-      <c r="E261" s="29"/>
-    </row>
-    <row r="262" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A262" s="29"/>
-      <c r="E262" s="29"/>
-    </row>
-    <row r="263" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A263" s="29"/>
-      <c r="E263" s="29"/>
-    </row>
-    <row r="264" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A264" s="29"/>
-      <c r="E264" s="29"/>
-    </row>
-    <row r="265" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A265" s="29"/>
-      <c r="E265" s="29"/>
-    </row>
-    <row r="266" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A266" s="29"/>
-      <c r="E266" s="29"/>
-    </row>
-    <row r="267" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A267" s="29"/>
-      <c r="E267" s="29"/>
-    </row>
-    <row r="268" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A268" s="29"/>
-      <c r="E268" s="29"/>
-    </row>
-    <row r="269" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A269" s="29"/>
-      <c r="E269" s="29"/>
-    </row>
-    <row r="270" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A270" s="29"/>
-      <c r="E270" s="29"/>
-    </row>
-    <row r="271" spans="1:5" ht="14.25" customHeight="1"/>
-    <row r="272" spans="1:5" ht="14.25" customHeight="1"/>
-    <row r="273" ht="14.25" customHeight="1"/>
-    <row r="274" ht="14.25" customHeight="1"/>
-    <row r="275" ht="14.25" customHeight="1"/>
-    <row r="276" ht="14.25" customHeight="1"/>
-    <row r="277" ht="14.25" customHeight="1"/>
-    <row r="278" ht="14.25" customHeight="1"/>
-    <row r="279" ht="14.25" customHeight="1"/>
-    <row r="280" ht="14.25" customHeight="1"/>
-    <row r="281" ht="14.25" customHeight="1"/>
-    <row r="282" ht="14.25" customHeight="1"/>
-    <row r="283" ht="14.25" customHeight="1"/>
-    <row r="284" ht="14.25" customHeight="1"/>
-    <row r="285" ht="14.25" customHeight="1"/>
-    <row r="286" ht="14.25" customHeight="1"/>
-    <row r="287" ht="14.25" customHeight="1"/>
-    <row r="288" ht="14.25" customHeight="1"/>
-    <row r="289" spans="1:5" ht="14.25" customHeight="1"/>
+      <c r="A256" s="28"/>
+      <c r="E256" s="28"/>
+    </row>
+    <row r="257" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A257" s="28"/>
+      <c r="E257" s="28"/>
+    </row>
+    <row r="258" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A258" s="28"/>
+      <c r="E258" s="28"/>
+    </row>
+    <row r="259" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A259" s="28"/>
+      <c r="E259" s="28"/>
+    </row>
+    <row r="260" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A260" s="28"/>
+      <c r="E260" s="28"/>
+    </row>
+    <row r="261" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A261" s="28"/>
+      <c r="E261" s="28"/>
+    </row>
+    <row r="262" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A262" s="28"/>
+      <c r="E262" s="28"/>
+    </row>
+    <row r="263" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A263" s="28"/>
+      <c r="E263" s="28"/>
+    </row>
+    <row r="264" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A264" s="28"/>
+      <c r="E264" s="28"/>
+    </row>
+    <row r="265" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A265" s="28"/>
+      <c r="E265" s="28"/>
+    </row>
+    <row r="266" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A266" s="28"/>
+      <c r="E266" s="28"/>
+    </row>
+    <row r="267" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A267" s="28"/>
+      <c r="E267" s="28"/>
+    </row>
+    <row r="268" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A268" s="28"/>
+      <c r="E268" s="28"/>
+    </row>
+    <row r="269" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A269" s="28"/>
+      <c r="D269" s="29"/>
+      <c r="E269" s="76" t="s">
+        <v>53</v>
+      </c>
+      <c r="F269" s="77"/>
+      <c r="G269" s="77"/>
+      <c r="H269" s="78"/>
+      <c r="I269" s="55" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="270" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A270" s="28"/>
+      <c r="D270" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="E270" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="F270" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="G270" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="H270" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="I270" s="22" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="271" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A271" s="28"/>
+      <c r="D271" s="75" t="s">
+        <v>134</v>
+      </c>
+      <c r="E271" s="75" t="s">
+        <v>135</v>
+      </c>
+      <c r="F271" s="72" t="s">
+        <v>136</v>
+      </c>
+      <c r="G271" s="75" t="s">
+        <v>137</v>
+      </c>
+      <c r="H271" s="30">
+        <v>1</v>
+      </c>
+      <c r="I271" s="31" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="272" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A272" s="28"/>
+      <c r="D272" s="73"/>
+      <c r="E272" s="73"/>
+      <c r="F272" s="73"/>
+      <c r="G272" s="73"/>
+      <c r="H272" s="30">
+        <v>2</v>
+      </c>
+      <c r="I272" s="31" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="273" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A273" s="28"/>
+      <c r="D273" s="73"/>
+      <c r="E273" s="73"/>
+      <c r="F273" s="73"/>
+      <c r="G273" s="73"/>
+      <c r="H273" s="30">
+        <v>3</v>
+      </c>
+      <c r="I273" s="31" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="274" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A274" s="28"/>
+      <c r="D274" s="74"/>
+      <c r="E274" s="74"/>
+      <c r="F274" s="74"/>
+      <c r="G274" s="74"/>
+      <c r="H274" s="30">
+        <v>4</v>
+      </c>
+      <c r="I274" s="31" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="275" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A275" s="28"/>
+      <c r="D275" s="32"/>
+      <c r="E275" s="32"/>
+      <c r="F275" s="33"/>
+      <c r="G275" s="32"/>
+      <c r="H275" s="32"/>
+      <c r="I275" s="32"/>
+    </row>
+    <row r="276" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A276" s="28"/>
+      <c r="D276" s="75" t="s">
+        <v>134</v>
+      </c>
+      <c r="E276" s="75" t="s">
+        <v>135</v>
+      </c>
+      <c r="F276" s="72" t="s">
+        <v>136</v>
+      </c>
+      <c r="G276" s="75" t="s">
+        <v>137</v>
+      </c>
+      <c r="H276" s="30">
+        <v>1</v>
+      </c>
+      <c r="I276" s="31" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="277" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A277" s="28"/>
+      <c r="D277" s="73"/>
+      <c r="E277" s="73"/>
+      <c r="F277" s="73"/>
+      <c r="G277" s="73"/>
+      <c r="H277" s="30">
+        <v>2</v>
+      </c>
+      <c r="I277" s="31" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="278" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A278" s="28"/>
+      <c r="D278" s="73"/>
+      <c r="E278" s="73"/>
+      <c r="F278" s="73"/>
+      <c r="G278" s="73"/>
+      <c r="H278" s="30">
+        <v>3</v>
+      </c>
+      <c r="I278" s="31" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="279" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A279" s="28"/>
+      <c r="D279" s="74"/>
+      <c r="E279" s="74"/>
+      <c r="F279" s="74"/>
+      <c r="G279" s="74"/>
+      <c r="H279" s="30">
+        <v>4</v>
+      </c>
+      <c r="I279" s="31" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="280" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A280" s="28"/>
+      <c r="D280" s="32"/>
+      <c r="E280" s="32"/>
+      <c r="F280" s="33"/>
+      <c r="G280" s="32"/>
+      <c r="H280" s="32"/>
+      <c r="I280" s="32"/>
+    </row>
+    <row r="281" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A281" s="28"/>
+      <c r="D281" s="75" t="s">
+        <v>134</v>
+      </c>
+      <c r="E281" s="75" t="s">
+        <v>135</v>
+      </c>
+      <c r="F281" s="72" t="s">
+        <v>136</v>
+      </c>
+      <c r="G281" s="75" t="s">
+        <v>137</v>
+      </c>
+      <c r="H281" s="30">
+        <v>1</v>
+      </c>
+      <c r="I281" s="31" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="282" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A282" s="28"/>
+      <c r="D282" s="73"/>
+      <c r="E282" s="73"/>
+      <c r="F282" s="73"/>
+      <c r="G282" s="73"/>
+      <c r="H282" s="30">
+        <v>2</v>
+      </c>
+      <c r="I282" s="31" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="283" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A283" s="28"/>
+      <c r="D283" s="73"/>
+      <c r="E283" s="73"/>
+      <c r="F283" s="73"/>
+      <c r="G283" s="73"/>
+      <c r="H283" s="30">
+        <v>3</v>
+      </c>
+      <c r="I283" s="31" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="284" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A284" s="28"/>
+      <c r="D284" s="74"/>
+      <c r="E284" s="74"/>
+      <c r="F284" s="74"/>
+      <c r="G284" s="74"/>
+      <c r="H284" s="30">
+        <v>4</v>
+      </c>
+      <c r="I284" s="31" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="285" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A285" s="28"/>
+      <c r="D285" s="32"/>
+      <c r="E285" s="32"/>
+      <c r="F285" s="33"/>
+      <c r="G285" s="32"/>
+      <c r="H285" s="32"/>
+      <c r="I285" s="32"/>
+    </row>
+    <row r="286" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A286" s="28"/>
+      <c r="E286" s="28"/>
+    </row>
+    <row r="287" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A287" s="28"/>
+      <c r="E287" s="28"/>
+    </row>
+    <row r="288" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A288" s="28"/>
+      <c r="E288" s="28"/>
+    </row>
+    <row r="289" spans="1:5" ht="14.25" customHeight="1">
+      <c r="A289" s="28"/>
+      <c r="E289" s="28"/>
+    </row>
     <row r="290" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A290" s="29"/>
-      <c r="E290" s="29"/>
+      <c r="A290" s="28"/>
+      <c r="E290" s="28"/>
     </row>
     <row r="291" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A291" s="29"/>
-      <c r="E291" s="29"/>
+      <c r="A291" s="28"/>
+      <c r="E291" s="28"/>
     </row>
     <row r="292" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A292" s="29"/>
-      <c r="E292" s="29"/>
+      <c r="A292" s="28"/>
+      <c r="E292" s="28"/>
     </row>
     <row r="293" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A293" s="29"/>
-      <c r="E293" s="29"/>
+      <c r="A293" s="28"/>
+      <c r="E293" s="28"/>
     </row>
     <row r="294" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A294" s="29"/>
-      <c r="E294" s="29"/>
+      <c r="A294" s="28"/>
+      <c r="E294" s="28"/>
     </row>
     <row r="295" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A295" s="29"/>
-      <c r="E295" s="29"/>
+      <c r="A295" s="28"/>
+      <c r="E295" s="28"/>
     </row>
     <row r="296" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A296" s="29"/>
-      <c r="E296" s="29"/>
+      <c r="A296" s="28"/>
+      <c r="E296" s="28"/>
     </row>
     <row r="297" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A297" s="29"/>
-      <c r="E297" s="29"/>
+      <c r="A297" s="28"/>
+      <c r="E297" s="28"/>
     </row>
     <row r="298" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A298" s="29"/>
-      <c r="E298" s="29"/>
+      <c r="A298" s="28"/>
+      <c r="E298" s="28"/>
     </row>
     <row r="299" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A299" s="29"/>
-      <c r="E299" s="29"/>
+      <c r="A299" s="28"/>
+      <c r="E299" s="28"/>
     </row>
     <row r="300" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A300" s="29"/>
-      <c r="E300" s="29"/>
+      <c r="A300" s="28"/>
+      <c r="E300" s="28"/>
     </row>
     <row r="301" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A301" s="29"/>
-      <c r="E301" s="29"/>
+      <c r="A301" s="28"/>
+      <c r="E301" s="28"/>
     </row>
     <row r="302" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A302" s="29"/>
-      <c r="E302" s="29"/>
+      <c r="A302" s="28"/>
+      <c r="E302" s="28"/>
     </row>
     <row r="303" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A303" s="29"/>
-      <c r="E303" s="29"/>
+      <c r="A303" s="28"/>
+      <c r="E303" s="28"/>
     </row>
     <row r="304" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A304" s="29"/>
-      <c r="E304" s="29"/>
+      <c r="A304" s="28"/>
+      <c r="E304" s="28"/>
     </row>
     <row r="305" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A305" s="29"/>
-      <c r="E305" s="29"/>
+      <c r="A305" s="28"/>
+      <c r="E305" s="28"/>
     </row>
     <row r="306" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A306" s="29"/>
-      <c r="E306" s="29"/>
+      <c r="A306" s="28"/>
+      <c r="E306" s="28"/>
     </row>
     <row r="307" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A307" s="29"/>
-      <c r="E307" s="29"/>
+      <c r="A307" s="28"/>
+      <c r="E307" s="28"/>
     </row>
     <row r="308" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A308" s="29"/>
-      <c r="E308" s="29"/>
+      <c r="A308" s="28"/>
+      <c r="E308" s="28"/>
     </row>
     <row r="309" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A309" s="29"/>
-      <c r="E309" s="29"/>
+      <c r="A309" s="28"/>
+      <c r="E309" s="28"/>
     </row>
     <row r="310" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A310" s="29"/>
-      <c r="E310" s="29"/>
+      <c r="A310" s="28"/>
+      <c r="E310" s="28"/>
     </row>
     <row r="311" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A311" s="29"/>
-      <c r="E311" s="29"/>
+      <c r="A311" s="28"/>
+      <c r="E311" s="28"/>
     </row>
     <row r="312" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A312" s="29"/>
-      <c r="E312" s="29"/>
+      <c r="A312" s="28"/>
+      <c r="E312" s="28"/>
     </row>
     <row r="313" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A313" s="29"/>
-      <c r="E313" s="29"/>
+      <c r="A313" s="28"/>
+      <c r="E313" s="28"/>
     </row>
     <row r="314" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A314" s="29"/>
-      <c r="E314" s="29"/>
+      <c r="A314" s="28"/>
+      <c r="E314" s="28"/>
     </row>
     <row r="315" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A315" s="29"/>
-      <c r="E315" s="29"/>
+      <c r="A315" s="28"/>
+      <c r="E315" s="28"/>
     </row>
     <row r="316" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A316" s="29"/>
-      <c r="E316" s="29"/>
+      <c r="A316" s="28"/>
+      <c r="E316" s="28"/>
     </row>
     <row r="317" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A317" s="29"/>
-      <c r="E317" s="29"/>
+      <c r="A317" s="28"/>
+      <c r="E317" s="28"/>
     </row>
     <row r="318" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A318" s="29"/>
-      <c r="E318" s="29"/>
+      <c r="A318" s="28"/>
+      <c r="E318" s="28"/>
     </row>
     <row r="319" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A319" s="29"/>
-      <c r="E319" s="29"/>
+      <c r="A319" s="28"/>
+      <c r="E319" s="28"/>
     </row>
     <row r="320" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A320" s="29"/>
-      <c r="E320" s="29"/>
+      <c r="A320" s="28"/>
+      <c r="E320" s="28"/>
     </row>
     <row r="321" spans="1:12" ht="14.25" customHeight="1">
-      <c r="A321" s="29"/>
-      <c r="E321" s="29"/>
+      <c r="A321" s="28"/>
+      <c r="E321" s="28"/>
     </row>
     <row r="322" spans="1:12" ht="14.25" customHeight="1">
-      <c r="A322" s="29"/>
-      <c r="E322" s="29"/>
+      <c r="A322" s="28"/>
+      <c r="E322" s="28"/>
     </row>
     <row r="323" spans="1:12" ht="14.25" customHeight="1">
-      <c r="A323" s="29"/>
-      <c r="E323" s="29"/>
+      <c r="A323" s="28"/>
+      <c r="E323" s="28"/>
     </row>
     <row r="324" spans="1:12" ht="14.25" customHeight="1">
-      <c r="A324" s="29"/>
-      <c r="E324" s="29"/>
+      <c r="A324" s="28"/>
+      <c r="E324" s="28"/>
     </row>
     <row r="325" spans="1:12" ht="14.25" customHeight="1">
-      <c r="A325" s="29"/>
-      <c r="D325" s="30"/>
-      <c r="E325" s="67" t="s">
-        <v>53</v>
-      </c>
-      <c r="F325" s="70"/>
-      <c r="G325" s="70"/>
-      <c r="H325" s="71"/>
-      <c r="I325" s="67" t="s">
-        <v>54</v>
-      </c>
-      <c r="J325" s="68"/>
-      <c r="K325" s="68"/>
-      <c r="L325" s="69"/>
+      <c r="A325" s="28"/>
+      <c r="E325" s="28"/>
+      <c r="J325" s="56"/>
+      <c r="K325" s="56"/>
+      <c r="L325" s="57"/>
     </row>
     <row r="326" spans="1:12" ht="14.25" customHeight="1">
-      <c r="A326" s="29"/>
-      <c r="D326" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="E326" s="22" t="s">
-        <v>56</v>
-      </c>
-      <c r="F326" s="22" t="s">
-        <v>57</v>
-      </c>
-      <c r="G326" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="H326" s="22" t="s">
-        <v>59</v>
-      </c>
-      <c r="I326" s="22" t="s">
-        <v>60</v>
-      </c>
+      <c r="A326" s="28"/>
+      <c r="E326" s="28"/>
       <c r="J326" s="22" t="s">
         <v>61</v>
       </c>
@@ -5567,2767 +5804,2455 @@
       </c>
     </row>
     <row r="327" spans="1:12" ht="14.25" customHeight="1">
-      <c r="A327" s="29"/>
-      <c r="D327" s="92" t="s">
-        <v>134</v>
-      </c>
-      <c r="E327" s="92" t="s">
-        <v>135</v>
-      </c>
-      <c r="F327" s="91" t="s">
-        <v>136</v>
-      </c>
-      <c r="G327" s="92" t="s">
-        <v>137</v>
-      </c>
-      <c r="H327" s="31">
-        <v>1</v>
-      </c>
-      <c r="I327" s="32" t="s">
-        <v>138</v>
-      </c>
-      <c r="J327" s="32" t="s">
+      <c r="A327" s="28"/>
+      <c r="E327" s="28"/>
+      <c r="J327" s="31" t="s">
         <v>139</v>
       </c>
-      <c r="K327" s="32" t="s">
+      <c r="K327" s="31" t="s">
         <v>140</v>
       </c>
-      <c r="L327" s="32" t="s">
+      <c r="L327" s="31" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="328" spans="1:12" ht="14.25" customHeight="1">
-      <c r="A328" s="29"/>
-      <c r="D328" s="73"/>
-      <c r="E328" s="73"/>
-      <c r="F328" s="73"/>
-      <c r="G328" s="73"/>
-      <c r="H328" s="31">
-        <v>2</v>
-      </c>
-      <c r="I328" s="32" t="s">
-        <v>138</v>
-      </c>
-      <c r="J328" s="32" t="s">
+      <c r="A328" s="28"/>
+      <c r="E328" s="28"/>
+      <c r="J328" s="31" t="s">
         <v>139</v>
       </c>
-      <c r="K328" s="32" t="s">
+      <c r="K328" s="31" t="s">
         <v>140</v>
       </c>
-      <c r="L328" s="32" t="s">
+      <c r="L328" s="31" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="329" spans="1:12" ht="14.25" customHeight="1">
-      <c r="A329" s="29"/>
-      <c r="D329" s="73"/>
-      <c r="E329" s="73"/>
-      <c r="F329" s="73"/>
-      <c r="G329" s="73"/>
-      <c r="H329" s="31">
-        <v>3</v>
-      </c>
-      <c r="I329" s="32" t="s">
-        <v>138</v>
-      </c>
-      <c r="J329" s="32" t="s">
+      <c r="A329" s="28"/>
+      <c r="E329" s="28"/>
+      <c r="J329" s="31" t="s">
         <v>139</v>
       </c>
-      <c r="K329" s="32" t="s">
+      <c r="K329" s="31" t="s">
         <v>140</v>
       </c>
-      <c r="L329" s="32" t="s">
+      <c r="L329" s="31" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="330" spans="1:12" ht="14.25" customHeight="1">
-      <c r="A330" s="29"/>
-      <c r="D330" s="74"/>
-      <c r="E330" s="74"/>
-      <c r="F330" s="74"/>
-      <c r="G330" s="74"/>
-      <c r="H330" s="31">
-        <v>4</v>
-      </c>
-      <c r="I330" s="32" t="s">
-        <v>138</v>
-      </c>
-      <c r="J330" s="32" t="s">
+      <c r="A330" s="28"/>
+      <c r="E330" s="28"/>
+      <c r="J330" s="31" t="s">
         <v>139</v>
       </c>
-      <c r="K330" s="32" t="s">
+      <c r="K330" s="31" t="s">
         <v>140</v>
       </c>
-      <c r="L330" s="32" t="s">
+      <c r="L330" s="31" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="331" spans="1:12" ht="14.25" customHeight="1">
-      <c r="A331" s="29"/>
-      <c r="D331" s="33"/>
-      <c r="E331" s="33"/>
-      <c r="F331" s="34"/>
-      <c r="G331" s="33"/>
-      <c r="H331" s="33"/>
-      <c r="I331" s="33"/>
-      <c r="J331" s="33"/>
-      <c r="K331" s="33"/>
-      <c r="L331" s="33"/>
+      <c r="A331" s="28"/>
+      <c r="E331" s="28"/>
+      <c r="J331" s="32"/>
+      <c r="K331" s="32"/>
+      <c r="L331" s="32"/>
     </row>
     <row r="332" spans="1:12" ht="14.25" customHeight="1">
-      <c r="A332" s="29"/>
-      <c r="D332" s="92" t="s">
-        <v>134</v>
-      </c>
-      <c r="E332" s="92" t="s">
-        <v>135</v>
-      </c>
-      <c r="F332" s="91" t="s">
-        <v>136</v>
-      </c>
-      <c r="G332" s="92" t="s">
-        <v>137</v>
-      </c>
-      <c r="H332" s="31">
-        <v>1</v>
-      </c>
-      <c r="I332" s="32" t="s">
-        <v>138</v>
-      </c>
-      <c r="J332" s="32" t="s">
+      <c r="A332" s="28"/>
+      <c r="E332" s="28"/>
+      <c r="J332" s="31" t="s">
         <v>139</v>
       </c>
-      <c r="K332" s="32" t="s">
+      <c r="K332" s="31" t="s">
         <v>140</v>
       </c>
-      <c r="L332" s="32" t="s">
+      <c r="L332" s="31" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="333" spans="1:12" ht="14.25" customHeight="1">
-      <c r="A333" s="29"/>
-      <c r="D333" s="73"/>
-      <c r="E333" s="73"/>
-      <c r="F333" s="73"/>
-      <c r="G333" s="73"/>
-      <c r="H333" s="31">
-        <v>2</v>
-      </c>
-      <c r="I333" s="32" t="s">
-        <v>138</v>
-      </c>
-      <c r="J333" s="32" t="s">
+      <c r="A333" s="28"/>
+      <c r="E333" s="28"/>
+      <c r="J333" s="31" t="s">
         <v>139</v>
       </c>
-      <c r="K333" s="32" t="s">
+      <c r="K333" s="31" t="s">
         <v>140</v>
       </c>
-      <c r="L333" s="32" t="s">
+      <c r="L333" s="31" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="334" spans="1:12" ht="14.25" customHeight="1">
-      <c r="A334" s="29"/>
-      <c r="D334" s="73"/>
-      <c r="E334" s="73"/>
-      <c r="F334" s="73"/>
-      <c r="G334" s="73"/>
-      <c r="H334" s="31">
-        <v>3</v>
-      </c>
-      <c r="I334" s="32" t="s">
-        <v>138</v>
-      </c>
-      <c r="J334" s="32" t="s">
+      <c r="A334" s="28"/>
+      <c r="E334" s="28"/>
+      <c r="J334" s="31" t="s">
         <v>139</v>
       </c>
-      <c r="K334" s="32" t="s">
+      <c r="K334" s="31" t="s">
         <v>140</v>
       </c>
-      <c r="L334" s="32" t="s">
+      <c r="L334" s="31" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="335" spans="1:12" ht="14.25" customHeight="1">
-      <c r="A335" s="29"/>
-      <c r="D335" s="74"/>
-      <c r="E335" s="74"/>
-      <c r="F335" s="74"/>
-      <c r="G335" s="74"/>
-      <c r="H335" s="31">
-        <v>4</v>
-      </c>
-      <c r="I335" s="32" t="s">
-        <v>138</v>
-      </c>
-      <c r="J335" s="32" t="s">
+      <c r="A335" s="28"/>
+      <c r="E335" s="28"/>
+      <c r="J335" s="31" t="s">
         <v>139</v>
       </c>
-      <c r="K335" s="32" t="s">
+      <c r="K335" s="31" t="s">
         <v>140</v>
       </c>
-      <c r="L335" s="32" t="s">
+      <c r="L335" s="31" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="336" spans="1:12" ht="14.25" customHeight="1">
-      <c r="A336" s="29"/>
-      <c r="D336" s="33"/>
-      <c r="E336" s="33"/>
-      <c r="F336" s="34"/>
-      <c r="G336" s="33"/>
-      <c r="H336" s="33"/>
-      <c r="I336" s="33"/>
-      <c r="J336" s="33"/>
-      <c r="K336" s="33"/>
-      <c r="L336" s="33"/>
+      <c r="A336" s="28"/>
+      <c r="E336" s="28"/>
+      <c r="J336" s="32"/>
+      <c r="K336" s="32"/>
+      <c r="L336" s="32"/>
     </row>
     <row r="337" spans="1:12" ht="14.25" customHeight="1">
-      <c r="A337" s="29"/>
-      <c r="D337" s="92" t="s">
-        <v>134</v>
-      </c>
-      <c r="E337" s="92" t="s">
-        <v>135</v>
-      </c>
-      <c r="F337" s="91" t="s">
-        <v>136</v>
-      </c>
-      <c r="G337" s="92" t="s">
-        <v>137</v>
-      </c>
-      <c r="H337" s="31">
-        <v>1</v>
-      </c>
-      <c r="I337" s="32" t="s">
-        <v>138</v>
-      </c>
-      <c r="J337" s="32" t="s">
+      <c r="A337" s="28"/>
+      <c r="E337" s="28"/>
+      <c r="J337" s="31" t="s">
         <v>139</v>
       </c>
-      <c r="K337" s="32" t="s">
+      <c r="K337" s="31" t="s">
         <v>140</v>
       </c>
-      <c r="L337" s="32" t="s">
+      <c r="L337" s="31" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="338" spans="1:12" ht="14.25" customHeight="1">
-      <c r="A338" s="29"/>
-      <c r="D338" s="73"/>
-      <c r="E338" s="73"/>
-      <c r="F338" s="73"/>
-      <c r="G338" s="73"/>
-      <c r="H338" s="31">
-        <v>2</v>
-      </c>
-      <c r="I338" s="32" t="s">
-        <v>138</v>
-      </c>
-      <c r="J338" s="32" t="s">
+      <c r="A338" s="28"/>
+      <c r="E338" s="28"/>
+      <c r="J338" s="31" t="s">
         <v>139</v>
       </c>
-      <c r="K338" s="32" t="s">
+      <c r="K338" s="31" t="s">
         <v>140</v>
       </c>
-      <c r="L338" s="32" t="s">
+      <c r="L338" s="31" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="339" spans="1:12" ht="14.25" customHeight="1">
-      <c r="A339" s="29"/>
-      <c r="D339" s="73"/>
-      <c r="E339" s="73"/>
-      <c r="F339" s="73"/>
-      <c r="G339" s="73"/>
-      <c r="H339" s="31">
-        <v>3</v>
-      </c>
-      <c r="I339" s="32" t="s">
-        <v>138</v>
-      </c>
-      <c r="J339" s="32" t="s">
+      <c r="A339" s="28"/>
+      <c r="E339" s="28"/>
+      <c r="J339" s="31" t="s">
         <v>139</v>
       </c>
-      <c r="K339" s="32" t="s">
+      <c r="K339" s="31" t="s">
         <v>140</v>
       </c>
-      <c r="L339" s="32" t="s">
+      <c r="L339" s="31" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="340" spans="1:12" ht="14.25" customHeight="1">
-      <c r="A340" s="29"/>
-      <c r="D340" s="74"/>
-      <c r="E340" s="74"/>
-      <c r="F340" s="74"/>
-      <c r="G340" s="74"/>
-      <c r="H340" s="31">
-        <v>4</v>
-      </c>
-      <c r="I340" s="32" t="s">
-        <v>138</v>
-      </c>
-      <c r="J340" s="32" t="s">
+      <c r="A340" s="28"/>
+      <c r="E340" s="28"/>
+      <c r="J340" s="31" t="s">
         <v>139</v>
       </c>
-      <c r="K340" s="32" t="s">
+      <c r="K340" s="31" t="s">
         <v>140</v>
       </c>
-      <c r="L340" s="32" t="s">
+      <c r="L340" s="31" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="341" spans="1:12" ht="14.25" customHeight="1">
-      <c r="A341" s="29"/>
-      <c r="D341" s="33"/>
-      <c r="E341" s="33"/>
-      <c r="F341" s="34"/>
-      <c r="G341" s="33"/>
-      <c r="H341" s="33"/>
-      <c r="I341" s="33"/>
-      <c r="J341" s="33"/>
-      <c r="K341" s="33"/>
-      <c r="L341" s="33"/>
+      <c r="A341" s="28"/>
+      <c r="E341" s="28"/>
+      <c r="J341" s="32"/>
+      <c r="K341" s="32"/>
+      <c r="L341" s="32"/>
     </row>
     <row r="342" spans="1:12" ht="14.25" customHeight="1">
-      <c r="A342" s="29"/>
-      <c r="E342" s="29"/>
+      <c r="A342" s="28"/>
+      <c r="E342" s="28"/>
     </row>
     <row r="343" spans="1:12" ht="14.25" customHeight="1">
-      <c r="A343" s="29"/>
-      <c r="E343" s="29"/>
+      <c r="A343" s="28"/>
+      <c r="E343" s="28"/>
     </row>
     <row r="344" spans="1:12" ht="14.25" customHeight="1">
-      <c r="A344" s="29"/>
-      <c r="E344" s="29"/>
+      <c r="A344" s="28"/>
+      <c r="E344" s="28"/>
     </row>
     <row r="345" spans="1:12" ht="14.25" customHeight="1">
-      <c r="A345" s="29"/>
-      <c r="E345" s="29"/>
+      <c r="A345" s="28"/>
+      <c r="E345" s="28"/>
     </row>
     <row r="346" spans="1:12" ht="14.25" customHeight="1">
-      <c r="A346" s="29"/>
-      <c r="E346" s="29"/>
+      <c r="A346" s="28"/>
+      <c r="E346" s="28"/>
     </row>
     <row r="347" spans="1:12" ht="14.25" customHeight="1">
-      <c r="A347" s="29"/>
-      <c r="E347" s="29"/>
+      <c r="A347" s="28"/>
+      <c r="E347" s="28"/>
     </row>
     <row r="348" spans="1:12" ht="14.25" customHeight="1">
-      <c r="A348" s="29"/>
-      <c r="E348" s="29"/>
+      <c r="A348" s="28"/>
+      <c r="E348" s="28"/>
     </row>
     <row r="349" spans="1:12" ht="14.25" customHeight="1">
-      <c r="A349" s="29"/>
-      <c r="E349" s="29"/>
+      <c r="A349" s="28"/>
+      <c r="E349" s="28"/>
     </row>
     <row r="350" spans="1:12" ht="14.25" customHeight="1">
-      <c r="A350" s="29"/>
-      <c r="E350" s="29"/>
+      <c r="A350" s="28"/>
+      <c r="E350" s="28"/>
     </row>
     <row r="351" spans="1:12" ht="14.25" customHeight="1">
-      <c r="A351" s="29"/>
-      <c r="E351" s="29"/>
+      <c r="A351" s="28"/>
+      <c r="E351" s="28"/>
     </row>
     <row r="352" spans="1:12" ht="14.25" customHeight="1">
-      <c r="A352" s="29"/>
-      <c r="E352" s="29"/>
+      <c r="A352" s="28"/>
+      <c r="E352" s="28"/>
     </row>
     <row r="353" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A353" s="29"/>
-      <c r="E353" s="29"/>
+      <c r="A353" s="28"/>
+      <c r="E353" s="28"/>
     </row>
     <row r="354" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A354" s="29"/>
-      <c r="E354" s="29"/>
+      <c r="A354" s="28"/>
+      <c r="E354" s="28"/>
     </row>
     <row r="355" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A355" s="29"/>
-      <c r="E355" s="29"/>
+      <c r="A355" s="28"/>
+      <c r="E355" s="28"/>
     </row>
     <row r="356" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A356" s="29"/>
-      <c r="E356" s="29"/>
+      <c r="A356" s="28"/>
+      <c r="E356" s="28"/>
     </row>
     <row r="357" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A357" s="29"/>
-      <c r="E357" s="29"/>
+      <c r="A357" s="28"/>
+      <c r="E357" s="28"/>
     </row>
     <row r="358" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A358" s="29"/>
-      <c r="E358" s="29"/>
+      <c r="A358" s="28"/>
+      <c r="E358" s="28"/>
     </row>
     <row r="359" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A359" s="29"/>
-      <c r="E359" s="29"/>
+      <c r="A359" s="28"/>
+      <c r="E359" s="28"/>
     </row>
     <row r="360" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A360" s="29"/>
-      <c r="E360" s="29"/>
+      <c r="A360" s="28"/>
+      <c r="E360" s="28"/>
     </row>
     <row r="361" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A361" s="29"/>
-      <c r="E361" s="29"/>
+      <c r="A361" s="28"/>
+      <c r="E361" s="28"/>
     </row>
     <row r="362" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A362" s="29"/>
-      <c r="E362" s="29"/>
+      <c r="A362" s="28"/>
+      <c r="E362" s="28"/>
     </row>
     <row r="363" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A363" s="29"/>
-      <c r="E363" s="29"/>
+      <c r="A363" s="28"/>
+      <c r="E363" s="28"/>
     </row>
     <row r="364" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A364" s="29"/>
-      <c r="E364" s="29"/>
+      <c r="A364" s="28"/>
+      <c r="E364" s="28"/>
     </row>
     <row r="365" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A365" s="29"/>
-      <c r="E365" s="29"/>
+      <c r="A365" s="28"/>
+      <c r="E365" s="28"/>
     </row>
     <row r="366" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A366" s="29"/>
-      <c r="E366" s="29"/>
+      <c r="A366" s="28"/>
+      <c r="E366" s="28"/>
     </row>
     <row r="367" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A367" s="29"/>
-      <c r="E367" s="29"/>
+      <c r="A367" s="28"/>
+      <c r="E367" s="28"/>
     </row>
     <row r="368" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A368" s="29"/>
-      <c r="E368" s="29"/>
+      <c r="A368" s="28"/>
+      <c r="E368" s="28"/>
     </row>
     <row r="369" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A369" s="29"/>
-      <c r="E369" s="29"/>
+      <c r="A369" s="28"/>
+      <c r="E369" s="28"/>
     </row>
     <row r="370" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A370" s="29"/>
-      <c r="E370" s="29"/>
+      <c r="A370" s="28"/>
+      <c r="E370" s="28"/>
     </row>
     <row r="371" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A371" s="29"/>
-      <c r="E371" s="29"/>
+      <c r="A371" s="28"/>
+      <c r="E371" s="28"/>
     </row>
     <row r="372" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A372" s="29"/>
-      <c r="E372" s="29"/>
+      <c r="A372" s="28"/>
+      <c r="E372" s="28"/>
     </row>
     <row r="373" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A373" s="29"/>
-      <c r="E373" s="29"/>
+      <c r="A373" s="28"/>
+      <c r="E373" s="28"/>
     </row>
     <row r="374" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A374" s="29"/>
-      <c r="E374" s="29"/>
+      <c r="A374" s="28"/>
+      <c r="E374" s="28"/>
     </row>
     <row r="375" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A375" s="29"/>
-      <c r="E375" s="29"/>
+      <c r="A375" s="28"/>
+      <c r="E375" s="28"/>
     </row>
     <row r="376" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A376" s="29"/>
-      <c r="E376" s="29"/>
+      <c r="A376" s="28"/>
+      <c r="E376" s="28"/>
     </row>
     <row r="377" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A377" s="29"/>
-      <c r="E377" s="29"/>
+      <c r="A377" s="28"/>
+      <c r="E377" s="28"/>
     </row>
     <row r="378" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A378" s="29"/>
-      <c r="E378" s="29"/>
+      <c r="A378" s="28"/>
+      <c r="E378" s="28"/>
     </row>
     <row r="379" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A379" s="29"/>
-      <c r="E379" s="29"/>
+      <c r="A379" s="28"/>
+      <c r="E379" s="28"/>
     </row>
     <row r="380" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A380" s="29"/>
-      <c r="E380" s="29"/>
+      <c r="A380" s="28"/>
+      <c r="E380" s="28"/>
     </row>
     <row r="381" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A381" s="29"/>
-      <c r="E381" s="29"/>
+      <c r="A381" s="28"/>
+      <c r="E381" s="28"/>
     </row>
     <row r="382" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A382" s="29"/>
-      <c r="E382" s="29"/>
+      <c r="A382" s="28"/>
+      <c r="E382" s="28"/>
     </row>
     <row r="383" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A383" s="29"/>
-      <c r="E383" s="29"/>
+      <c r="A383" s="28"/>
+      <c r="E383" s="28"/>
     </row>
     <row r="384" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A384" s="29"/>
-      <c r="E384" s="29"/>
+      <c r="A384" s="28"/>
+      <c r="E384" s="28"/>
     </row>
     <row r="385" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A385" s="29"/>
-      <c r="E385" s="29"/>
+      <c r="A385" s="28"/>
+      <c r="E385" s="28"/>
     </row>
     <row r="386" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A386" s="29"/>
-      <c r="E386" s="29"/>
+      <c r="A386" s="28"/>
+      <c r="E386" s="28"/>
     </row>
     <row r="387" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A387" s="29"/>
-      <c r="E387" s="29"/>
+      <c r="A387" s="28"/>
+      <c r="E387" s="28"/>
     </row>
     <row r="388" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A388" s="29"/>
-      <c r="E388" s="29"/>
+      <c r="A388" s="28"/>
+      <c r="E388" s="28"/>
     </row>
     <row r="389" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A389" s="29"/>
-      <c r="E389" s="29"/>
+      <c r="A389" s="28"/>
+      <c r="E389" s="28"/>
     </row>
     <row r="390" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A390" s="29"/>
-      <c r="E390" s="29"/>
+      <c r="A390" s="28"/>
+      <c r="E390" s="28"/>
     </row>
     <row r="391" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A391" s="29"/>
-      <c r="E391" s="29"/>
+      <c r="A391" s="28"/>
+      <c r="E391" s="28"/>
     </row>
     <row r="392" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A392" s="29"/>
-      <c r="E392" s="29"/>
+      <c r="A392" s="28"/>
+      <c r="E392" s="28"/>
     </row>
     <row r="393" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A393" s="29"/>
-      <c r="E393" s="29"/>
+      <c r="A393" s="28"/>
+      <c r="E393" s="28"/>
     </row>
     <row r="394" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A394" s="29"/>
-      <c r="E394" s="29"/>
+      <c r="A394" s="28"/>
+      <c r="E394" s="28"/>
     </row>
     <row r="395" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A395" s="29"/>
-      <c r="E395" s="29"/>
+      <c r="A395" s="28"/>
+      <c r="E395" s="28"/>
     </row>
     <row r="396" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A396" s="29"/>
-      <c r="E396" s="29"/>
+      <c r="A396" s="28"/>
+      <c r="E396" s="28"/>
     </row>
     <row r="397" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A397" s="29"/>
-      <c r="E397" s="29"/>
+      <c r="A397" s="28"/>
+      <c r="E397" s="28"/>
     </row>
     <row r="398" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A398" s="29"/>
-      <c r="E398" s="29"/>
+      <c r="A398" s="28"/>
+      <c r="E398" s="28"/>
     </row>
     <row r="399" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A399" s="29"/>
-      <c r="E399" s="29"/>
+      <c r="A399" s="28"/>
+      <c r="E399" s="28"/>
     </row>
     <row r="400" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A400" s="29"/>
-      <c r="E400" s="29"/>
+      <c r="A400" s="28"/>
+      <c r="E400" s="28"/>
     </row>
     <row r="401" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A401" s="29"/>
-      <c r="E401" s="29"/>
+      <c r="A401" s="28"/>
+      <c r="E401" s="28"/>
     </row>
     <row r="402" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A402" s="29"/>
-      <c r="E402" s="29"/>
+      <c r="A402" s="28"/>
+      <c r="E402" s="28"/>
     </row>
     <row r="403" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A403" s="29"/>
-      <c r="E403" s="29"/>
+      <c r="A403" s="28"/>
+      <c r="E403" s="28"/>
     </row>
     <row r="404" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A404" s="29"/>
-      <c r="E404" s="29"/>
+      <c r="A404" s="28"/>
+      <c r="E404" s="28"/>
     </row>
     <row r="405" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A405" s="29"/>
-      <c r="E405" s="29"/>
+      <c r="A405" s="28"/>
+      <c r="E405" s="28"/>
     </row>
     <row r="406" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A406" s="29"/>
-      <c r="E406" s="29"/>
+      <c r="A406" s="28"/>
+      <c r="E406" s="28"/>
     </row>
     <row r="407" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A407" s="29"/>
-      <c r="E407" s="29"/>
+      <c r="A407" s="28"/>
+      <c r="E407" s="28"/>
     </row>
     <row r="408" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A408" s="29"/>
-      <c r="E408" s="29"/>
+      <c r="A408" s="28"/>
+      <c r="E408" s="28"/>
     </row>
     <row r="409" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A409" s="29"/>
-      <c r="E409" s="29"/>
+      <c r="A409" s="28"/>
+      <c r="E409" s="28"/>
     </row>
     <row r="410" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A410" s="29"/>
-      <c r="E410" s="29"/>
+      <c r="A410" s="28"/>
+      <c r="E410" s="28"/>
     </row>
     <row r="411" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A411" s="29"/>
-      <c r="E411" s="29"/>
+      <c r="A411" s="28"/>
+      <c r="E411" s="28"/>
     </row>
     <row r="412" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A412" s="29"/>
-      <c r="E412" s="29"/>
+      <c r="A412" s="28"/>
+      <c r="E412" s="28"/>
     </row>
     <row r="413" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A413" s="29"/>
-      <c r="E413" s="29"/>
+      <c r="A413" s="28"/>
+      <c r="E413" s="28"/>
     </row>
     <row r="414" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A414" s="29"/>
-      <c r="E414" s="29"/>
+      <c r="A414" s="28"/>
+      <c r="E414" s="28"/>
     </row>
     <row r="415" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A415" s="29"/>
-      <c r="E415" s="29"/>
+      <c r="A415" s="28"/>
+      <c r="E415" s="28"/>
     </row>
     <row r="416" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A416" s="29"/>
-      <c r="E416" s="29"/>
+      <c r="A416" s="28"/>
+      <c r="E416" s="28"/>
     </row>
     <row r="417" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A417" s="29"/>
-      <c r="E417" s="29"/>
+      <c r="A417" s="28"/>
+      <c r="E417" s="28"/>
     </row>
     <row r="418" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A418" s="29"/>
-      <c r="E418" s="29"/>
+      <c r="A418" s="28"/>
+      <c r="E418" s="28"/>
     </row>
     <row r="419" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A419" s="29"/>
-      <c r="E419" s="29"/>
+      <c r="A419" s="28"/>
+      <c r="E419" s="28"/>
     </row>
     <row r="420" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A420" s="29"/>
-      <c r="E420" s="29"/>
+      <c r="A420" s="28"/>
+      <c r="E420" s="28"/>
     </row>
     <row r="421" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A421" s="29"/>
-      <c r="E421" s="29"/>
+      <c r="A421" s="28"/>
+      <c r="E421" s="28"/>
     </row>
     <row r="422" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A422" s="29"/>
-      <c r="E422" s="29"/>
+      <c r="A422" s="28"/>
+      <c r="E422" s="28"/>
     </row>
     <row r="423" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A423" s="29"/>
-      <c r="E423" s="29"/>
+      <c r="A423" s="28"/>
+      <c r="E423" s="28"/>
     </row>
     <row r="424" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A424" s="29"/>
-      <c r="E424" s="29"/>
+      <c r="A424" s="28"/>
+      <c r="E424" s="28"/>
     </row>
     <row r="425" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A425" s="29"/>
-      <c r="E425" s="29"/>
+      <c r="A425" s="28"/>
+      <c r="E425" s="28"/>
     </row>
     <row r="426" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A426" s="29"/>
-      <c r="E426" s="29"/>
+      <c r="A426" s="28"/>
+      <c r="E426" s="28"/>
     </row>
     <row r="427" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A427" s="29"/>
-      <c r="E427" s="29"/>
+      <c r="A427" s="28"/>
+      <c r="E427" s="28"/>
     </row>
     <row r="428" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A428" s="29"/>
-      <c r="E428" s="29"/>
+      <c r="A428" s="28"/>
+      <c r="E428" s="28"/>
     </row>
     <row r="429" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A429" s="29"/>
-      <c r="E429" s="29"/>
+      <c r="A429" s="28"/>
+      <c r="E429" s="28"/>
     </row>
     <row r="430" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A430" s="29"/>
-      <c r="E430" s="29"/>
+      <c r="A430" s="28"/>
+      <c r="E430" s="28"/>
     </row>
     <row r="431" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A431" s="29"/>
-      <c r="E431" s="29"/>
+      <c r="A431" s="28"/>
+      <c r="E431" s="28"/>
     </row>
     <row r="432" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A432" s="29"/>
-      <c r="E432" s="29"/>
+      <c r="A432" s="28"/>
+      <c r="E432" s="28"/>
     </row>
     <row r="433" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A433" s="29"/>
-      <c r="E433" s="29"/>
+      <c r="A433" s="28"/>
+      <c r="E433" s="28"/>
     </row>
     <row r="434" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A434" s="29"/>
-      <c r="E434" s="29"/>
+      <c r="A434" s="28"/>
+      <c r="E434" s="28"/>
     </row>
     <row r="435" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A435" s="29"/>
-      <c r="E435" s="29"/>
+      <c r="A435" s="28"/>
+      <c r="E435" s="28"/>
     </row>
     <row r="436" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A436" s="29"/>
-      <c r="E436" s="29"/>
+      <c r="A436" s="28"/>
+      <c r="E436" s="28"/>
     </row>
     <row r="437" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A437" s="29"/>
-      <c r="E437" s="29"/>
+      <c r="A437" s="28"/>
+      <c r="E437" s="28"/>
     </row>
     <row r="438" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A438" s="29"/>
-      <c r="E438" s="29"/>
+      <c r="A438" s="28"/>
+      <c r="E438" s="28"/>
     </row>
     <row r="439" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A439" s="29"/>
-      <c r="E439" s="29"/>
+      <c r="A439" s="28"/>
+      <c r="E439" s="28"/>
     </row>
     <row r="440" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A440" s="29"/>
-      <c r="E440" s="29"/>
+      <c r="A440" s="28"/>
+      <c r="E440" s="28"/>
     </row>
     <row r="441" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A441" s="29"/>
-      <c r="E441" s="29"/>
+      <c r="A441" s="28"/>
+      <c r="E441" s="28"/>
     </row>
     <row r="442" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A442" s="29"/>
-      <c r="E442" s="29"/>
+      <c r="A442" s="28"/>
+      <c r="E442" s="28"/>
     </row>
     <row r="443" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A443" s="29"/>
-      <c r="E443" s="29"/>
+      <c r="A443" s="28"/>
+      <c r="E443" s="28"/>
     </row>
     <row r="444" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A444" s="29"/>
-      <c r="E444" s="29"/>
+      <c r="A444" s="28"/>
+      <c r="E444" s="28"/>
     </row>
     <row r="445" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A445" s="29"/>
-      <c r="E445" s="29"/>
+      <c r="A445" s="28"/>
+      <c r="E445" s="28"/>
     </row>
     <row r="446" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A446" s="29"/>
-      <c r="E446" s="29"/>
+      <c r="A446" s="28"/>
+      <c r="E446" s="28"/>
     </row>
     <row r="447" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A447" s="29"/>
-      <c r="E447" s="29"/>
+      <c r="A447" s="28"/>
+      <c r="E447" s="28"/>
     </row>
     <row r="448" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A448" s="29"/>
-      <c r="E448" s="29"/>
+      <c r="A448" s="28"/>
+      <c r="E448" s="28"/>
     </row>
     <row r="449" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A449" s="29"/>
-      <c r="E449" s="29"/>
+      <c r="A449" s="28"/>
+      <c r="E449" s="28"/>
     </row>
     <row r="450" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A450" s="29"/>
-      <c r="E450" s="29"/>
+      <c r="A450" s="28"/>
+      <c r="E450" s="28"/>
     </row>
     <row r="451" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A451" s="29"/>
-      <c r="E451" s="29"/>
+      <c r="A451" s="28"/>
+      <c r="E451" s="28"/>
     </row>
     <row r="452" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A452" s="29"/>
-      <c r="E452" s="29"/>
+      <c r="A452" s="28"/>
+      <c r="E452" s="28"/>
     </row>
     <row r="453" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A453" s="29"/>
-      <c r="E453" s="29"/>
+      <c r="A453" s="28"/>
+      <c r="E453" s="28"/>
     </row>
     <row r="454" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A454" s="29"/>
-      <c r="E454" s="29"/>
+      <c r="A454" s="28"/>
+      <c r="E454" s="28"/>
     </row>
     <row r="455" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A455" s="29"/>
-      <c r="E455" s="29"/>
+      <c r="A455" s="28"/>
+      <c r="E455" s="28"/>
     </row>
     <row r="456" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A456" s="29"/>
-      <c r="E456" s="29"/>
+      <c r="A456" s="28"/>
+      <c r="E456" s="28"/>
     </row>
     <row r="457" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A457" s="29"/>
-      <c r="E457" s="29"/>
+      <c r="A457" s="28"/>
+      <c r="E457" s="28"/>
     </row>
     <row r="458" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A458" s="29"/>
-      <c r="E458" s="29"/>
+      <c r="A458" s="28"/>
+      <c r="E458" s="28"/>
     </row>
     <row r="459" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A459" s="29"/>
-      <c r="E459" s="29"/>
+      <c r="A459" s="28"/>
+      <c r="E459" s="28"/>
     </row>
     <row r="460" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A460" s="29"/>
-      <c r="E460" s="29"/>
+      <c r="A460" s="28"/>
+      <c r="E460" s="28"/>
     </row>
     <row r="461" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A461" s="29"/>
-      <c r="E461" s="29"/>
+      <c r="A461" s="28"/>
+      <c r="E461" s="28"/>
     </row>
     <row r="462" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A462" s="29"/>
-      <c r="E462" s="29"/>
+      <c r="A462" s="28"/>
+      <c r="E462" s="28"/>
     </row>
     <row r="463" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A463" s="29"/>
-      <c r="E463" s="29"/>
+      <c r="A463" s="28"/>
+      <c r="E463" s="28"/>
     </row>
     <row r="464" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A464" s="29"/>
-      <c r="E464" s="29"/>
+      <c r="A464" s="28"/>
+      <c r="E464" s="28"/>
     </row>
     <row r="465" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A465" s="29"/>
-      <c r="E465" s="29"/>
+      <c r="A465" s="28"/>
+      <c r="E465" s="28"/>
     </row>
     <row r="466" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A466" s="29"/>
-      <c r="E466" s="29"/>
+      <c r="A466" s="28"/>
+      <c r="E466" s="28"/>
     </row>
     <row r="467" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A467" s="29"/>
-      <c r="E467" s="29"/>
+      <c r="A467" s="28"/>
+      <c r="E467" s="28"/>
     </row>
     <row r="468" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A468" s="29"/>
-      <c r="E468" s="29"/>
+      <c r="A468" s="28"/>
+      <c r="E468" s="28"/>
     </row>
     <row r="469" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A469" s="29"/>
-      <c r="E469" s="29"/>
+      <c r="A469" s="28"/>
+      <c r="E469" s="28"/>
     </row>
     <row r="470" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A470" s="29"/>
-      <c r="E470" s="29"/>
+      <c r="A470" s="28"/>
+      <c r="E470" s="28"/>
     </row>
     <row r="471" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A471" s="29"/>
-      <c r="E471" s="29"/>
+      <c r="A471" s="28"/>
+      <c r="E471" s="28"/>
     </row>
     <row r="472" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A472" s="29"/>
-      <c r="E472" s="29"/>
+      <c r="A472" s="28"/>
+      <c r="E472" s="28"/>
     </row>
     <row r="473" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A473" s="29"/>
-      <c r="E473" s="29"/>
+      <c r="A473" s="28"/>
+      <c r="E473" s="28"/>
     </row>
     <row r="474" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A474" s="29"/>
-      <c r="E474" s="29"/>
+      <c r="A474" s="28"/>
+      <c r="E474" s="28"/>
     </row>
     <row r="475" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A475" s="29"/>
-      <c r="E475" s="29"/>
+      <c r="A475" s="28"/>
+      <c r="E475" s="28"/>
     </row>
     <row r="476" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A476" s="29"/>
-      <c r="E476" s="29"/>
+      <c r="A476" s="28"/>
+      <c r="E476" s="28"/>
     </row>
     <row r="477" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A477" s="29"/>
-      <c r="E477" s="29"/>
+      <c r="A477" s="28"/>
+      <c r="E477" s="28"/>
     </row>
     <row r="478" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A478" s="29"/>
-      <c r="E478" s="29"/>
+      <c r="A478" s="28"/>
+      <c r="E478" s="28"/>
     </row>
     <row r="479" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A479" s="29"/>
-      <c r="E479" s="29"/>
+      <c r="A479" s="28"/>
+      <c r="E479" s="28"/>
     </row>
     <row r="480" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A480" s="29"/>
-      <c r="E480" s="29"/>
+      <c r="A480" s="28"/>
+      <c r="E480" s="28"/>
     </row>
     <row r="481" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A481" s="29"/>
-      <c r="E481" s="29"/>
+      <c r="A481" s="28"/>
+      <c r="E481" s="28"/>
     </row>
     <row r="482" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A482" s="29"/>
-      <c r="E482" s="29"/>
+      <c r="A482" s="28"/>
+      <c r="E482" s="28"/>
     </row>
     <row r="483" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A483" s="29"/>
-      <c r="E483" s="29"/>
+      <c r="A483" s="28"/>
+      <c r="E483" s="28"/>
     </row>
     <row r="484" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A484" s="29"/>
-      <c r="E484" s="29"/>
+      <c r="A484" s="28"/>
+      <c r="E484" s="28"/>
     </row>
     <row r="485" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A485" s="29"/>
-      <c r="E485" s="29"/>
+      <c r="A485" s="28"/>
+      <c r="E485" s="28"/>
     </row>
     <row r="486" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A486" s="29"/>
-      <c r="E486" s="29"/>
+      <c r="A486" s="28"/>
+      <c r="E486" s="28"/>
     </row>
     <row r="487" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A487" s="29"/>
-      <c r="E487" s="29"/>
+      <c r="A487" s="28"/>
+      <c r="E487" s="28"/>
     </row>
     <row r="488" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A488" s="29"/>
-      <c r="E488" s="29"/>
+      <c r="A488" s="28"/>
+      <c r="E488" s="28"/>
     </row>
     <row r="489" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A489" s="29"/>
-      <c r="E489" s="29"/>
+      <c r="A489" s="28"/>
+      <c r="E489" s="28"/>
     </row>
     <row r="490" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A490" s="29"/>
-      <c r="E490" s="29"/>
+      <c r="A490" s="28"/>
+      <c r="E490" s="28"/>
     </row>
     <row r="491" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A491" s="29"/>
-      <c r="E491" s="29"/>
+      <c r="A491" s="28"/>
+      <c r="E491" s="28"/>
     </row>
     <row r="492" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A492" s="29"/>
-      <c r="E492" s="29"/>
+      <c r="A492" s="28"/>
+      <c r="E492" s="28"/>
     </row>
     <row r="493" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A493" s="29"/>
-      <c r="E493" s="29"/>
+      <c r="A493" s="28"/>
+      <c r="E493" s="28"/>
     </row>
     <row r="494" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A494" s="29"/>
-      <c r="E494" s="29"/>
+      <c r="A494" s="28"/>
+      <c r="E494" s="28"/>
     </row>
     <row r="495" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A495" s="29"/>
-      <c r="E495" s="29"/>
+      <c r="A495" s="28"/>
+      <c r="E495" s="28"/>
     </row>
     <row r="496" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A496" s="29"/>
-      <c r="E496" s="29"/>
+      <c r="A496" s="28"/>
+      <c r="E496" s="28"/>
     </row>
     <row r="497" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A497" s="29"/>
-      <c r="E497" s="29"/>
+      <c r="A497" s="28"/>
+      <c r="E497" s="28"/>
     </row>
     <row r="498" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A498" s="29"/>
-      <c r="E498" s="29"/>
+      <c r="A498" s="28"/>
+      <c r="E498" s="28"/>
     </row>
     <row r="499" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A499" s="29"/>
-      <c r="E499" s="29"/>
+      <c r="A499" s="28"/>
+      <c r="E499" s="28"/>
     </row>
     <row r="500" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A500" s="29"/>
-      <c r="E500" s="29"/>
+      <c r="A500" s="28"/>
+      <c r="E500" s="28"/>
     </row>
     <row r="501" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A501" s="29"/>
-      <c r="E501" s="29"/>
+      <c r="A501" s="28"/>
+      <c r="E501" s="28"/>
     </row>
     <row r="502" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A502" s="29"/>
-      <c r="E502" s="29"/>
+      <c r="A502" s="28"/>
+      <c r="E502" s="28"/>
     </row>
     <row r="503" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A503" s="29"/>
-      <c r="E503" s="29"/>
+      <c r="A503" s="28"/>
+      <c r="E503" s="28"/>
     </row>
     <row r="504" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A504" s="29"/>
-      <c r="E504" s="29"/>
+      <c r="A504" s="28"/>
+      <c r="E504" s="28"/>
     </row>
     <row r="505" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A505" s="29"/>
-      <c r="E505" s="29"/>
+      <c r="A505" s="28"/>
+      <c r="E505" s="28"/>
     </row>
     <row r="506" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A506" s="29"/>
-      <c r="E506" s="29"/>
+      <c r="A506" s="28"/>
+      <c r="E506" s="28"/>
     </row>
     <row r="507" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A507" s="29"/>
-      <c r="E507" s="29"/>
+      <c r="A507" s="28"/>
+      <c r="E507" s="28"/>
     </row>
     <row r="508" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A508" s="29"/>
-      <c r="E508" s="29"/>
+      <c r="A508" s="28"/>
+      <c r="E508" s="28"/>
     </row>
     <row r="509" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A509" s="29"/>
-      <c r="E509" s="29"/>
+      <c r="A509" s="28"/>
+      <c r="E509" s="28"/>
     </row>
     <row r="510" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A510" s="29"/>
-      <c r="E510" s="29"/>
+      <c r="A510" s="28"/>
+      <c r="E510" s="28"/>
     </row>
     <row r="511" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A511" s="29"/>
-      <c r="E511" s="29"/>
+      <c r="A511" s="28"/>
+      <c r="E511" s="28"/>
     </row>
     <row r="512" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A512" s="29"/>
-      <c r="E512" s="29"/>
+      <c r="A512" s="28"/>
+      <c r="E512" s="28"/>
     </row>
     <row r="513" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A513" s="29"/>
-      <c r="E513" s="29"/>
+      <c r="A513" s="28"/>
+      <c r="E513" s="28"/>
     </row>
     <row r="514" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A514" s="29"/>
-      <c r="E514" s="29"/>
+      <c r="A514" s="28"/>
+      <c r="E514" s="28"/>
     </row>
     <row r="515" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A515" s="29"/>
-      <c r="E515" s="29"/>
+      <c r="A515" s="28"/>
+      <c r="E515" s="28"/>
     </row>
     <row r="516" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A516" s="29"/>
-      <c r="E516" s="29"/>
+      <c r="A516" s="28"/>
+      <c r="E516" s="28"/>
     </row>
     <row r="517" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A517" s="29"/>
-      <c r="E517" s="29"/>
+      <c r="A517" s="28"/>
+      <c r="E517" s="28"/>
     </row>
     <row r="518" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A518" s="29"/>
-      <c r="E518" s="29"/>
+      <c r="A518" s="28"/>
+      <c r="E518" s="28"/>
     </row>
     <row r="519" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A519" s="29"/>
-      <c r="E519" s="29"/>
+      <c r="A519" s="28"/>
+      <c r="E519" s="28"/>
     </row>
     <row r="520" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A520" s="29"/>
-      <c r="E520" s="29"/>
+      <c r="A520" s="28"/>
+      <c r="E520" s="28"/>
     </row>
     <row r="521" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A521" s="29"/>
-      <c r="E521" s="29"/>
+      <c r="A521" s="28"/>
+      <c r="E521" s="28"/>
     </row>
     <row r="522" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A522" s="29"/>
-      <c r="E522" s="29"/>
+      <c r="A522" s="28"/>
+      <c r="E522" s="28"/>
     </row>
     <row r="523" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A523" s="29"/>
-      <c r="E523" s="29"/>
+      <c r="A523" s="28"/>
+      <c r="E523" s="28"/>
     </row>
     <row r="524" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A524" s="29"/>
-      <c r="E524" s="29"/>
+      <c r="A524" s="28"/>
+      <c r="E524" s="28"/>
     </row>
     <row r="525" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A525" s="29"/>
-      <c r="E525" s="29"/>
+      <c r="A525" s="28"/>
+      <c r="E525" s="28"/>
     </row>
     <row r="526" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A526" s="29"/>
-      <c r="E526" s="29"/>
+      <c r="A526" s="28"/>
+      <c r="E526" s="28"/>
     </row>
     <row r="527" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A527" s="29"/>
-      <c r="E527" s="29"/>
+      <c r="A527" s="28"/>
+      <c r="E527" s="28"/>
     </row>
     <row r="528" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A528" s="29"/>
-      <c r="E528" s="29"/>
+      <c r="A528" s="28"/>
+      <c r="E528" s="28"/>
     </row>
     <row r="529" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A529" s="29"/>
-      <c r="E529" s="29"/>
+      <c r="A529" s="28"/>
+      <c r="E529" s="28"/>
     </row>
     <row r="530" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A530" s="29"/>
-      <c r="E530" s="29"/>
+      <c r="A530" s="28"/>
+      <c r="E530" s="28"/>
     </row>
     <row r="531" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A531" s="29"/>
-      <c r="E531" s="29"/>
+      <c r="A531" s="28"/>
+      <c r="E531" s="28"/>
     </row>
     <row r="532" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A532" s="29"/>
-      <c r="E532" s="29"/>
+      <c r="A532" s="28"/>
+      <c r="E532" s="28"/>
     </row>
     <row r="533" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A533" s="29"/>
-      <c r="E533" s="29"/>
+      <c r="A533" s="28"/>
+      <c r="E533" s="28"/>
     </row>
     <row r="534" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A534" s="29"/>
-      <c r="E534" s="29"/>
+      <c r="A534" s="28"/>
+      <c r="E534" s="28"/>
     </row>
     <row r="535" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A535" s="29"/>
-      <c r="E535" s="29"/>
+      <c r="A535" s="28"/>
+      <c r="E535" s="28"/>
     </row>
     <row r="536" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A536" s="29"/>
-      <c r="E536" s="29"/>
+      <c r="A536" s="28"/>
+      <c r="E536" s="28"/>
     </row>
     <row r="537" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A537" s="29"/>
-      <c r="E537" s="29"/>
+      <c r="A537" s="28"/>
+      <c r="E537" s="28"/>
     </row>
     <row r="538" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A538" s="29"/>
-      <c r="E538" s="29"/>
+      <c r="A538" s="28"/>
+      <c r="E538" s="28"/>
     </row>
     <row r="539" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A539" s="29"/>
-      <c r="E539" s="29"/>
+      <c r="A539" s="28"/>
+      <c r="E539" s="28"/>
     </row>
     <row r="540" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A540" s="29"/>
-      <c r="E540" s="29"/>
+      <c r="A540" s="28"/>
+      <c r="E540" s="28"/>
     </row>
     <row r="541" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A541" s="29"/>
-      <c r="E541" s="29"/>
+      <c r="A541" s="28"/>
+      <c r="E541" s="28"/>
     </row>
     <row r="542" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A542" s="29"/>
-      <c r="E542" s="29"/>
+      <c r="A542" s="28"/>
+      <c r="E542" s="28"/>
     </row>
     <row r="543" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A543" s="29"/>
-      <c r="E543" s="29"/>
+      <c r="A543" s="28"/>
+      <c r="E543" s="28"/>
     </row>
     <row r="544" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A544" s="29"/>
-      <c r="E544" s="29"/>
+      <c r="A544" s="28"/>
+      <c r="E544" s="28"/>
     </row>
     <row r="545" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A545" s="29"/>
-      <c r="E545" s="29"/>
+      <c r="A545" s="28"/>
+      <c r="E545" s="28"/>
     </row>
     <row r="546" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A546" s="29"/>
-      <c r="E546" s="29"/>
+      <c r="A546" s="28"/>
+      <c r="E546" s="28"/>
     </row>
     <row r="547" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A547" s="29"/>
-      <c r="E547" s="29"/>
+      <c r="A547" s="28"/>
+      <c r="E547" s="28"/>
     </row>
     <row r="548" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A548" s="29"/>
-      <c r="E548" s="29"/>
+      <c r="A548" s="28"/>
+      <c r="E548" s="28"/>
     </row>
     <row r="549" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A549" s="29"/>
-      <c r="E549" s="29"/>
+      <c r="A549" s="28"/>
+      <c r="E549" s="28"/>
     </row>
     <row r="550" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A550" s="29"/>
-      <c r="E550" s="29"/>
+      <c r="A550" s="28"/>
+      <c r="E550" s="28"/>
     </row>
     <row r="551" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A551" s="29"/>
-      <c r="E551" s="29"/>
+      <c r="A551" s="28"/>
+      <c r="E551" s="28"/>
     </row>
     <row r="552" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A552" s="29"/>
-      <c r="E552" s="29"/>
+      <c r="A552" s="28"/>
+      <c r="E552" s="28"/>
     </row>
     <row r="553" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A553" s="29"/>
-      <c r="E553" s="29"/>
+      <c r="A553" s="28"/>
+      <c r="E553" s="28"/>
     </row>
     <row r="554" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A554" s="29"/>
-      <c r="E554" s="29"/>
+      <c r="A554" s="28"/>
+      <c r="E554" s="28"/>
     </row>
     <row r="555" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A555" s="29"/>
-      <c r="E555" s="29"/>
+      <c r="A555" s="28"/>
+      <c r="E555" s="28"/>
     </row>
     <row r="556" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A556" s="29"/>
-      <c r="E556" s="29"/>
+      <c r="A556" s="28"/>
+      <c r="E556" s="28"/>
     </row>
     <row r="557" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A557" s="29"/>
-      <c r="E557" s="29"/>
+      <c r="A557" s="28"/>
+      <c r="E557" s="28"/>
     </row>
     <row r="558" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A558" s="29"/>
-      <c r="E558" s="29"/>
+      <c r="A558" s="28"/>
+      <c r="E558" s="28"/>
     </row>
     <row r="559" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A559" s="29"/>
-      <c r="E559" s="29"/>
+      <c r="A559" s="28"/>
+      <c r="E559" s="28"/>
     </row>
     <row r="560" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A560" s="29"/>
-      <c r="E560" s="29"/>
+      <c r="A560" s="28"/>
+      <c r="E560" s="28"/>
     </row>
     <row r="561" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A561" s="29"/>
-      <c r="E561" s="29"/>
+      <c r="A561" s="28"/>
+      <c r="E561" s="28"/>
     </row>
     <row r="562" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A562" s="29"/>
-      <c r="E562" s="29"/>
+      <c r="A562" s="28"/>
+      <c r="E562" s="28"/>
     </row>
     <row r="563" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A563" s="29"/>
-      <c r="E563" s="29"/>
+      <c r="A563" s="28"/>
+      <c r="E563" s="28"/>
     </row>
     <row r="564" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A564" s="29"/>
-      <c r="E564" s="29"/>
+      <c r="A564" s="28"/>
+      <c r="E564" s="28"/>
     </row>
     <row r="565" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A565" s="29"/>
-      <c r="E565" s="29"/>
+      <c r="A565" s="28"/>
+      <c r="E565" s="28"/>
     </row>
     <row r="566" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A566" s="29"/>
-      <c r="E566" s="29"/>
+      <c r="A566" s="28"/>
+      <c r="E566" s="28"/>
     </row>
     <row r="567" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A567" s="29"/>
-      <c r="E567" s="29"/>
+      <c r="A567" s="28"/>
+      <c r="E567" s="28"/>
     </row>
     <row r="568" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A568" s="29"/>
-      <c r="E568" s="29"/>
+      <c r="A568" s="28"/>
+      <c r="E568" s="28"/>
     </row>
     <row r="569" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A569" s="29"/>
-      <c r="E569" s="29"/>
+      <c r="A569" s="28"/>
+      <c r="E569" s="28"/>
     </row>
     <row r="570" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A570" s="29"/>
-      <c r="E570" s="29"/>
+      <c r="A570" s="28"/>
+      <c r="E570" s="28"/>
     </row>
     <row r="571" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A571" s="29"/>
-      <c r="E571" s="29"/>
+      <c r="A571" s="28"/>
+      <c r="E571" s="28"/>
     </row>
     <row r="572" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A572" s="29"/>
-      <c r="E572" s="29"/>
+      <c r="A572" s="28"/>
+      <c r="E572" s="28"/>
     </row>
     <row r="573" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A573" s="29"/>
-      <c r="E573" s="29"/>
+      <c r="A573" s="28"/>
+      <c r="E573" s="28"/>
     </row>
     <row r="574" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A574" s="29"/>
-      <c r="E574" s="29"/>
+      <c r="A574" s="28"/>
+      <c r="E574" s="28"/>
     </row>
     <row r="575" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A575" s="29"/>
-      <c r="E575" s="29"/>
+      <c r="A575" s="28"/>
+      <c r="E575" s="28"/>
     </row>
     <row r="576" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A576" s="29"/>
-      <c r="E576" s="29"/>
+      <c r="A576" s="28"/>
+      <c r="E576" s="28"/>
     </row>
     <row r="577" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A577" s="29"/>
-      <c r="E577" s="29"/>
+      <c r="A577" s="28"/>
+      <c r="E577" s="28"/>
     </row>
     <row r="578" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A578" s="29"/>
-      <c r="E578" s="29"/>
+      <c r="A578" s="28"/>
+      <c r="E578" s="28"/>
     </row>
     <row r="579" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A579" s="29"/>
-      <c r="E579" s="29"/>
+      <c r="A579" s="28"/>
+      <c r="E579" s="28"/>
     </row>
     <row r="580" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A580" s="29"/>
-      <c r="E580" s="29"/>
+      <c r="A580" s="28"/>
+      <c r="E580" s="28"/>
     </row>
     <row r="581" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A581" s="29"/>
-      <c r="E581" s="29"/>
+      <c r="A581" s="28"/>
+      <c r="E581" s="28"/>
     </row>
     <row r="582" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A582" s="29"/>
-      <c r="E582" s="29"/>
+      <c r="A582" s="28"/>
+      <c r="E582" s="28"/>
     </row>
     <row r="583" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A583" s="29"/>
-      <c r="E583" s="29"/>
+      <c r="A583" s="28"/>
+      <c r="E583" s="28"/>
     </row>
     <row r="584" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A584" s="29"/>
-      <c r="E584" s="29"/>
+      <c r="A584" s="28"/>
+      <c r="E584" s="28"/>
     </row>
     <row r="585" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A585" s="29"/>
-      <c r="E585" s="29"/>
+      <c r="A585" s="28"/>
+      <c r="E585" s="28"/>
     </row>
     <row r="586" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A586" s="29"/>
-      <c r="E586" s="29"/>
+      <c r="A586" s="28"/>
+      <c r="E586" s="28"/>
     </row>
     <row r="587" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A587" s="29"/>
-      <c r="E587" s="29"/>
+      <c r="A587" s="28"/>
+      <c r="E587" s="28"/>
     </row>
     <row r="588" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A588" s="29"/>
-      <c r="E588" s="29"/>
+      <c r="A588" s="28"/>
+      <c r="E588" s="28"/>
     </row>
     <row r="589" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A589" s="29"/>
-      <c r="E589" s="29"/>
+      <c r="A589" s="28"/>
+      <c r="E589" s="28"/>
     </row>
     <row r="590" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A590" s="29"/>
-      <c r="E590" s="29"/>
+      <c r="A590" s="28"/>
+      <c r="E590" s="28"/>
     </row>
     <row r="591" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A591" s="29"/>
-      <c r="E591" s="29"/>
+      <c r="A591" s="28"/>
+      <c r="E591" s="28"/>
     </row>
     <row r="592" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A592" s="29"/>
-      <c r="E592" s="29"/>
+      <c r="A592" s="28"/>
+      <c r="E592" s="28"/>
     </row>
     <row r="593" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A593" s="29"/>
-      <c r="E593" s="29"/>
+      <c r="A593" s="28"/>
+      <c r="E593" s="28"/>
     </row>
     <row r="594" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A594" s="29"/>
-      <c r="E594" s="29"/>
+      <c r="A594" s="28"/>
+      <c r="E594" s="28"/>
     </row>
     <row r="595" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A595" s="29"/>
-      <c r="E595" s="29"/>
+      <c r="A595" s="28"/>
+      <c r="E595" s="28"/>
     </row>
     <row r="596" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A596" s="29"/>
-      <c r="E596" s="29"/>
+      <c r="A596" s="28"/>
+      <c r="E596" s="28"/>
     </row>
     <row r="597" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A597" s="29"/>
-      <c r="E597" s="29"/>
+      <c r="A597" s="28"/>
+      <c r="E597" s="28"/>
     </row>
     <row r="598" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A598" s="29"/>
-      <c r="E598" s="29"/>
+      <c r="A598" s="28"/>
+      <c r="E598" s="28"/>
     </row>
     <row r="599" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A599" s="29"/>
-      <c r="E599" s="29"/>
+      <c r="A599" s="28"/>
+      <c r="E599" s="28"/>
     </row>
     <row r="600" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A600" s="29"/>
-      <c r="E600" s="29"/>
+      <c r="A600" s="28"/>
+      <c r="E600" s="28"/>
     </row>
     <row r="601" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A601" s="29"/>
-      <c r="E601" s="29"/>
+      <c r="A601" s="28"/>
+      <c r="E601" s="28"/>
     </row>
     <row r="602" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A602" s="29"/>
-      <c r="E602" s="29"/>
+      <c r="A602" s="28"/>
+      <c r="E602" s="28"/>
     </row>
     <row r="603" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A603" s="29"/>
-      <c r="E603" s="29"/>
+      <c r="A603" s="28"/>
+      <c r="E603" s="28"/>
     </row>
     <row r="604" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A604" s="29"/>
-      <c r="E604" s="29"/>
+      <c r="A604" s="28"/>
+      <c r="E604" s="28"/>
     </row>
     <row r="605" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A605" s="29"/>
-      <c r="E605" s="29"/>
+      <c r="A605" s="28"/>
+      <c r="E605" s="28"/>
     </row>
     <row r="606" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A606" s="29"/>
-      <c r="E606" s="29"/>
+      <c r="A606" s="28"/>
+      <c r="E606" s="28"/>
     </row>
     <row r="607" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A607" s="29"/>
-      <c r="E607" s="29"/>
+      <c r="A607" s="28"/>
+      <c r="E607" s="28"/>
     </row>
     <row r="608" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A608" s="29"/>
-      <c r="E608" s="29"/>
+      <c r="A608" s="28"/>
+      <c r="E608" s="28"/>
     </row>
     <row r="609" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A609" s="29"/>
-      <c r="E609" s="29"/>
+      <c r="A609" s="28"/>
+      <c r="E609" s="28"/>
     </row>
     <row r="610" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A610" s="29"/>
-      <c r="E610" s="29"/>
+      <c r="A610" s="28"/>
+      <c r="E610" s="28"/>
     </row>
     <row r="611" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A611" s="29"/>
-      <c r="E611" s="29"/>
+      <c r="A611" s="28"/>
+      <c r="E611" s="28"/>
     </row>
     <row r="612" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A612" s="29"/>
-      <c r="E612" s="29"/>
+      <c r="A612" s="28"/>
+      <c r="E612" s="28"/>
     </row>
     <row r="613" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A613" s="29"/>
-      <c r="E613" s="29"/>
+      <c r="A613" s="28"/>
+      <c r="E613" s="28"/>
     </row>
     <row r="614" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A614" s="29"/>
-      <c r="E614" s="29"/>
+      <c r="A614" s="28"/>
+      <c r="E614" s="28"/>
     </row>
     <row r="615" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A615" s="29"/>
-      <c r="E615" s="29"/>
+      <c r="A615" s="28"/>
+      <c r="E615" s="28"/>
     </row>
     <row r="616" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A616" s="29"/>
-      <c r="E616" s="29"/>
+      <c r="A616" s="28"/>
+      <c r="E616" s="28"/>
     </row>
     <row r="617" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A617" s="29"/>
-      <c r="E617" s="29"/>
+      <c r="A617" s="28"/>
+      <c r="E617" s="28"/>
     </row>
     <row r="618" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A618" s="29"/>
-      <c r="E618" s="29"/>
+      <c r="A618" s="28"/>
+      <c r="E618" s="28"/>
     </row>
     <row r="619" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A619" s="29"/>
-      <c r="E619" s="29"/>
+      <c r="A619" s="28"/>
+      <c r="E619" s="28"/>
     </row>
     <row r="620" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A620" s="29"/>
-      <c r="E620" s="29"/>
+      <c r="A620" s="28"/>
+      <c r="E620" s="28"/>
     </row>
     <row r="621" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A621" s="29"/>
-      <c r="E621" s="29"/>
+      <c r="A621" s="28"/>
+      <c r="E621" s="28"/>
     </row>
     <row r="622" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A622" s="29"/>
-      <c r="E622" s="29"/>
+      <c r="A622" s="28"/>
+      <c r="E622" s="28"/>
     </row>
     <row r="623" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A623" s="29"/>
-      <c r="E623" s="29"/>
+      <c r="A623" s="28"/>
+      <c r="E623" s="28"/>
     </row>
     <row r="624" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A624" s="29"/>
-      <c r="E624" s="29"/>
+      <c r="A624" s="28"/>
+      <c r="E624" s="28"/>
     </row>
     <row r="625" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A625" s="29"/>
-      <c r="E625" s="29"/>
+      <c r="A625" s="28"/>
+      <c r="E625" s="28"/>
     </row>
     <row r="626" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A626" s="29"/>
-      <c r="E626" s="29"/>
+      <c r="A626" s="28"/>
+      <c r="E626" s="28"/>
     </row>
     <row r="627" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A627" s="29"/>
-      <c r="E627" s="29"/>
+      <c r="A627" s="28"/>
+      <c r="E627" s="28"/>
     </row>
     <row r="628" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A628" s="29"/>
-      <c r="E628" s="29"/>
+      <c r="A628" s="28"/>
+      <c r="E628" s="28"/>
     </row>
     <row r="629" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A629" s="29"/>
-      <c r="E629" s="29"/>
+      <c r="A629" s="28"/>
+      <c r="E629" s="28"/>
     </row>
     <row r="630" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A630" s="29"/>
-      <c r="E630" s="29"/>
+      <c r="A630" s="28"/>
+      <c r="E630" s="28"/>
     </row>
     <row r="631" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A631" s="29"/>
-      <c r="E631" s="29"/>
+      <c r="A631" s="28"/>
+      <c r="E631" s="28"/>
     </row>
     <row r="632" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A632" s="29"/>
-      <c r="E632" s="29"/>
+      <c r="A632" s="28"/>
+      <c r="E632" s="28"/>
     </row>
     <row r="633" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A633" s="29"/>
-      <c r="E633" s="29"/>
+      <c r="A633" s="28"/>
+      <c r="E633" s="28"/>
     </row>
     <row r="634" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A634" s="29"/>
-      <c r="E634" s="29"/>
+      <c r="A634" s="28"/>
+      <c r="E634" s="28"/>
     </row>
     <row r="635" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A635" s="29"/>
-      <c r="E635" s="29"/>
+      <c r="A635" s="28"/>
+      <c r="E635" s="28"/>
     </row>
     <row r="636" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A636" s="29"/>
-      <c r="E636" s="29"/>
+      <c r="A636" s="28"/>
+      <c r="E636" s="28"/>
     </row>
     <row r="637" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A637" s="29"/>
-      <c r="E637" s="29"/>
+      <c r="A637" s="28"/>
+      <c r="E637" s="28"/>
     </row>
     <row r="638" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A638" s="29"/>
-      <c r="E638" s="29"/>
+      <c r="A638" s="28"/>
+      <c r="E638" s="28"/>
     </row>
     <row r="639" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A639" s="29"/>
-      <c r="E639" s="29"/>
+      <c r="A639" s="28"/>
+      <c r="E639" s="28"/>
     </row>
     <row r="640" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A640" s="29"/>
-      <c r="E640" s="29"/>
+      <c r="A640" s="28"/>
+      <c r="E640" s="28"/>
     </row>
     <row r="641" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A641" s="29"/>
-      <c r="E641" s="29"/>
+      <c r="A641" s="28"/>
+      <c r="E641" s="28"/>
     </row>
     <row r="642" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A642" s="29"/>
-      <c r="E642" s="29"/>
+      <c r="A642" s="28"/>
+      <c r="E642" s="28"/>
     </row>
     <row r="643" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A643" s="29"/>
-      <c r="E643" s="29"/>
+      <c r="A643" s="28"/>
+      <c r="E643" s="28"/>
     </row>
     <row r="644" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A644" s="29"/>
-      <c r="E644" s="29"/>
+      <c r="A644" s="28"/>
+      <c r="E644" s="28"/>
     </row>
     <row r="645" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A645" s="29"/>
-      <c r="E645" s="29"/>
+      <c r="A645" s="28"/>
+      <c r="E645" s="28"/>
     </row>
     <row r="646" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A646" s="29"/>
-      <c r="E646" s="29"/>
+      <c r="A646" s="28"/>
+      <c r="E646" s="28"/>
     </row>
     <row r="647" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A647" s="29"/>
-      <c r="E647" s="29"/>
+      <c r="A647" s="28"/>
+      <c r="E647" s="28"/>
     </row>
     <row r="648" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A648" s="29"/>
-      <c r="E648" s="29"/>
+      <c r="A648" s="28"/>
+      <c r="E648" s="28"/>
     </row>
     <row r="649" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A649" s="29"/>
-      <c r="E649" s="29"/>
+      <c r="A649" s="28"/>
+      <c r="E649" s="28"/>
     </row>
     <row r="650" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A650" s="29"/>
-      <c r="E650" s="29"/>
+      <c r="A650" s="28"/>
+      <c r="E650" s="28"/>
     </row>
     <row r="651" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A651" s="29"/>
-      <c r="E651" s="29"/>
+      <c r="A651" s="28"/>
+      <c r="E651" s="28"/>
     </row>
     <row r="652" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A652" s="29"/>
-      <c r="E652" s="29"/>
+      <c r="A652" s="28"/>
+      <c r="E652" s="28"/>
     </row>
     <row r="653" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A653" s="29"/>
-      <c r="E653" s="29"/>
+      <c r="A653" s="28"/>
+      <c r="E653" s="28"/>
     </row>
     <row r="654" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A654" s="29"/>
-      <c r="E654" s="29"/>
+      <c r="A654" s="28"/>
+      <c r="E654" s="28"/>
     </row>
     <row r="655" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A655" s="29"/>
-      <c r="E655" s="29"/>
+      <c r="A655" s="28"/>
+      <c r="E655" s="28"/>
     </row>
     <row r="656" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A656" s="29"/>
-      <c r="E656" s="29"/>
+      <c r="A656" s="28"/>
+      <c r="E656" s="28"/>
     </row>
     <row r="657" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A657" s="29"/>
-      <c r="E657" s="29"/>
+      <c r="A657" s="28"/>
+      <c r="E657" s="28"/>
     </row>
     <row r="658" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A658" s="29"/>
-      <c r="E658" s="29"/>
+      <c r="A658" s="28"/>
+      <c r="E658" s="28"/>
     </row>
     <row r="659" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A659" s="29"/>
-      <c r="E659" s="29"/>
+      <c r="A659" s="28"/>
+      <c r="E659" s="28"/>
     </row>
     <row r="660" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A660" s="29"/>
-      <c r="E660" s="29"/>
+      <c r="A660" s="28"/>
+      <c r="E660" s="28"/>
     </row>
     <row r="661" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A661" s="29"/>
-      <c r="E661" s="29"/>
+      <c r="A661" s="28"/>
+      <c r="E661" s="28"/>
     </row>
     <row r="662" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A662" s="29"/>
-      <c r="E662" s="29"/>
+      <c r="A662" s="28"/>
+      <c r="E662" s="28"/>
     </row>
     <row r="663" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A663" s="29"/>
-      <c r="E663" s="29"/>
+      <c r="A663" s="28"/>
+      <c r="E663" s="28"/>
     </row>
     <row r="664" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A664" s="29"/>
-      <c r="E664" s="29"/>
+      <c r="A664" s="28"/>
+      <c r="E664" s="28"/>
     </row>
     <row r="665" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A665" s="29"/>
-      <c r="E665" s="29"/>
+      <c r="A665" s="28"/>
+      <c r="E665" s="28"/>
     </row>
     <row r="666" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A666" s="29"/>
-      <c r="E666" s="29"/>
+      <c r="A666" s="28"/>
+      <c r="E666" s="28"/>
     </row>
     <row r="667" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A667" s="29"/>
-      <c r="E667" s="29"/>
+      <c r="A667" s="28"/>
+      <c r="E667" s="28"/>
     </row>
     <row r="668" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A668" s="29"/>
-      <c r="E668" s="29"/>
+      <c r="A668" s="28"/>
+      <c r="E668" s="28"/>
     </row>
     <row r="669" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A669" s="29"/>
-      <c r="E669" s="29"/>
+      <c r="A669" s="28"/>
+      <c r="E669" s="28"/>
     </row>
     <row r="670" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A670" s="29"/>
-      <c r="E670" s="29"/>
+      <c r="A670" s="28"/>
+      <c r="E670" s="28"/>
     </row>
     <row r="671" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A671" s="29"/>
-      <c r="E671" s="29"/>
+      <c r="A671" s="28"/>
+      <c r="E671" s="28"/>
     </row>
     <row r="672" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A672" s="29"/>
-      <c r="E672" s="29"/>
+      <c r="A672" s="28"/>
+      <c r="E672" s="28"/>
     </row>
     <row r="673" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A673" s="29"/>
-      <c r="E673" s="29"/>
+      <c r="A673" s="28"/>
+      <c r="E673" s="28"/>
     </row>
     <row r="674" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A674" s="29"/>
-      <c r="E674" s="29"/>
+      <c r="A674" s="28"/>
+      <c r="E674" s="28"/>
     </row>
     <row r="675" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A675" s="29"/>
-      <c r="E675" s="29"/>
+      <c r="A675" s="28"/>
+      <c r="E675" s="28"/>
     </row>
     <row r="676" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A676" s="29"/>
-      <c r="E676" s="29"/>
+      <c r="A676" s="28"/>
+      <c r="E676" s="28"/>
     </row>
     <row r="677" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A677" s="29"/>
-      <c r="E677" s="29"/>
+      <c r="A677" s="28"/>
+      <c r="E677" s="28"/>
     </row>
     <row r="678" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A678" s="29"/>
-      <c r="E678" s="29"/>
+      <c r="A678" s="28"/>
+      <c r="E678" s="28"/>
     </row>
     <row r="679" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A679" s="29"/>
-      <c r="E679" s="29"/>
+      <c r="A679" s="28"/>
+      <c r="E679" s="28"/>
     </row>
     <row r="680" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A680" s="29"/>
-      <c r="E680" s="29"/>
+      <c r="A680" s="28"/>
+      <c r="E680" s="28"/>
     </row>
     <row r="681" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A681" s="29"/>
-      <c r="E681" s="29"/>
+      <c r="A681" s="28"/>
+      <c r="E681" s="28"/>
     </row>
     <row r="682" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A682" s="29"/>
-      <c r="E682" s="29"/>
+      <c r="A682" s="28"/>
+      <c r="E682" s="28"/>
     </row>
     <row r="683" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A683" s="29"/>
-      <c r="E683" s="29"/>
+      <c r="A683" s="28"/>
+      <c r="E683" s="28"/>
     </row>
     <row r="684" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A684" s="29"/>
-      <c r="E684" s="29"/>
+      <c r="A684" s="28"/>
+      <c r="E684" s="28"/>
     </row>
     <row r="685" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A685" s="29"/>
-      <c r="E685" s="29"/>
+      <c r="A685" s="28"/>
+      <c r="E685" s="28"/>
     </row>
     <row r="686" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A686" s="29"/>
-      <c r="E686" s="29"/>
+      <c r="A686" s="28"/>
+      <c r="E686" s="28"/>
     </row>
     <row r="687" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A687" s="29"/>
-      <c r="E687" s="29"/>
+      <c r="A687" s="28"/>
+      <c r="E687" s="28"/>
     </row>
     <row r="688" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A688" s="29"/>
-      <c r="E688" s="29"/>
+      <c r="A688" s="28"/>
+      <c r="E688" s="28"/>
     </row>
     <row r="689" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A689" s="29"/>
-      <c r="E689" s="29"/>
+      <c r="A689" s="28"/>
+      <c r="E689" s="28"/>
     </row>
     <row r="690" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A690" s="29"/>
-      <c r="E690" s="29"/>
+      <c r="A690" s="28"/>
+      <c r="E690" s="28"/>
     </row>
     <row r="691" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A691" s="29"/>
-      <c r="E691" s="29"/>
+      <c r="A691" s="28"/>
+      <c r="E691" s="28"/>
     </row>
     <row r="692" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A692" s="29"/>
-      <c r="E692" s="29"/>
+      <c r="A692" s="28"/>
+      <c r="E692" s="28"/>
     </row>
     <row r="693" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A693" s="29"/>
-      <c r="E693" s="29"/>
+      <c r="A693" s="28"/>
+      <c r="E693" s="28"/>
     </row>
     <row r="694" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A694" s="29"/>
-      <c r="E694" s="29"/>
+      <c r="A694" s="28"/>
+      <c r="E694" s="28"/>
     </row>
     <row r="695" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A695" s="29"/>
-      <c r="E695" s="29"/>
+      <c r="A695" s="28"/>
+      <c r="E695" s="28"/>
     </row>
     <row r="696" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A696" s="29"/>
-      <c r="E696" s="29"/>
+      <c r="A696" s="28"/>
+      <c r="E696" s="28"/>
     </row>
     <row r="697" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A697" s="29"/>
-      <c r="E697" s="29"/>
+      <c r="A697" s="28"/>
+      <c r="E697" s="28"/>
     </row>
     <row r="698" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A698" s="29"/>
-      <c r="E698" s="29"/>
+      <c r="A698" s="28"/>
+      <c r="E698" s="28"/>
     </row>
     <row r="699" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A699" s="29"/>
-      <c r="E699" s="29"/>
+      <c r="A699" s="28"/>
+      <c r="E699" s="28"/>
     </row>
     <row r="700" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A700" s="29"/>
-      <c r="E700" s="29"/>
+      <c r="A700" s="28"/>
+      <c r="E700" s="28"/>
     </row>
     <row r="701" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A701" s="29"/>
-      <c r="E701" s="29"/>
+      <c r="A701" s="28"/>
+      <c r="E701" s="28"/>
     </row>
     <row r="702" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A702" s="29"/>
-      <c r="E702" s="29"/>
+      <c r="A702" s="28"/>
+      <c r="E702" s="28"/>
     </row>
     <row r="703" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A703" s="29"/>
-      <c r="E703" s="29"/>
+      <c r="A703" s="28"/>
+      <c r="E703" s="28"/>
     </row>
     <row r="704" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A704" s="29"/>
-      <c r="E704" s="29"/>
+      <c r="A704" s="28"/>
+      <c r="E704" s="28"/>
     </row>
     <row r="705" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A705" s="29"/>
-      <c r="E705" s="29"/>
+      <c r="A705" s="28"/>
+      <c r="E705" s="28"/>
     </row>
     <row r="706" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A706" s="29"/>
-      <c r="E706" s="29"/>
+      <c r="A706" s="28"/>
+      <c r="E706" s="28"/>
     </row>
     <row r="707" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A707" s="29"/>
-      <c r="E707" s="29"/>
+      <c r="A707" s="28"/>
+      <c r="E707" s="28"/>
     </row>
     <row r="708" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A708" s="29"/>
-      <c r="E708" s="29"/>
+      <c r="A708" s="28"/>
+      <c r="E708" s="28"/>
     </row>
     <row r="709" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A709" s="29"/>
-      <c r="E709" s="29"/>
+      <c r="A709" s="28"/>
+      <c r="E709" s="28"/>
     </row>
     <row r="710" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A710" s="29"/>
-      <c r="E710" s="29"/>
+      <c r="A710" s="28"/>
+      <c r="E710" s="28"/>
     </row>
     <row r="711" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A711" s="29"/>
-      <c r="E711" s="29"/>
+      <c r="A711" s="28"/>
+      <c r="E711" s="28"/>
     </row>
     <row r="712" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A712" s="29"/>
-      <c r="E712" s="29"/>
+      <c r="A712" s="28"/>
+      <c r="E712" s="28"/>
     </row>
     <row r="713" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A713" s="29"/>
-      <c r="E713" s="29"/>
+      <c r="A713" s="28"/>
+      <c r="E713" s="28"/>
     </row>
     <row r="714" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A714" s="29"/>
-      <c r="E714" s="29"/>
+      <c r="A714" s="28"/>
+      <c r="E714" s="28"/>
     </row>
     <row r="715" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A715" s="29"/>
-      <c r="E715" s="29"/>
+      <c r="A715" s="28"/>
+      <c r="E715" s="28"/>
     </row>
     <row r="716" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A716" s="29"/>
-      <c r="E716" s="29"/>
+      <c r="A716" s="28"/>
+      <c r="E716" s="28"/>
     </row>
     <row r="717" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A717" s="29"/>
-      <c r="E717" s="29"/>
+      <c r="A717" s="28"/>
+      <c r="E717" s="28"/>
     </row>
     <row r="718" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A718" s="29"/>
-      <c r="E718" s="29"/>
+      <c r="A718" s="28"/>
+      <c r="E718" s="28"/>
     </row>
     <row r="719" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A719" s="29"/>
-      <c r="E719" s="29"/>
+      <c r="A719" s="28"/>
+      <c r="E719" s="28"/>
     </row>
     <row r="720" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A720" s="29"/>
-      <c r="E720" s="29"/>
+      <c r="A720" s="28"/>
+      <c r="E720" s="28"/>
     </row>
     <row r="721" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A721" s="29"/>
-      <c r="E721" s="29"/>
+      <c r="A721" s="28"/>
+      <c r="E721" s="28"/>
     </row>
     <row r="722" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A722" s="29"/>
-      <c r="E722" s="29"/>
+      <c r="A722" s="28"/>
+      <c r="E722" s="28"/>
     </row>
     <row r="723" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A723" s="29"/>
-      <c r="E723" s="29"/>
+      <c r="A723" s="28"/>
+      <c r="E723" s="28"/>
     </row>
     <row r="724" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A724" s="29"/>
-      <c r="E724" s="29"/>
+      <c r="A724" s="28"/>
+      <c r="E724" s="28"/>
     </row>
     <row r="725" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A725" s="29"/>
-      <c r="E725" s="29"/>
+      <c r="A725" s="28"/>
+      <c r="E725" s="28"/>
     </row>
     <row r="726" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A726" s="29"/>
-      <c r="E726" s="29"/>
+      <c r="A726" s="28"/>
+      <c r="E726" s="28"/>
     </row>
     <row r="727" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A727" s="29"/>
-      <c r="E727" s="29"/>
+      <c r="A727" s="28"/>
+      <c r="E727" s="28"/>
     </row>
     <row r="728" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A728" s="29"/>
-      <c r="E728" s="29"/>
+      <c r="A728" s="28"/>
+      <c r="E728" s="28"/>
     </row>
     <row r="729" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A729" s="29"/>
-      <c r="E729" s="29"/>
+      <c r="A729" s="28"/>
+      <c r="E729" s="28"/>
     </row>
     <row r="730" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A730" s="29"/>
-      <c r="E730" s="29"/>
+      <c r="A730" s="28"/>
+      <c r="E730" s="28"/>
     </row>
     <row r="731" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A731" s="29"/>
-      <c r="E731" s="29"/>
+      <c r="A731" s="28"/>
+      <c r="E731" s="28"/>
     </row>
     <row r="732" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A732" s="29"/>
-      <c r="E732" s="29"/>
+      <c r="A732" s="28"/>
+      <c r="E732" s="28"/>
     </row>
     <row r="733" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A733" s="29"/>
-      <c r="E733" s="29"/>
+      <c r="A733" s="28"/>
+      <c r="E733" s="28"/>
     </row>
     <row r="734" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A734" s="29"/>
-      <c r="E734" s="29"/>
+      <c r="A734" s="28"/>
+      <c r="E734" s="28"/>
     </row>
     <row r="735" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A735" s="29"/>
-      <c r="E735" s="29"/>
+      <c r="A735" s="28"/>
+      <c r="E735" s="28"/>
     </row>
     <row r="736" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A736" s="29"/>
-      <c r="E736" s="29"/>
+      <c r="A736" s="28"/>
+      <c r="E736" s="28"/>
     </row>
     <row r="737" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A737" s="29"/>
-      <c r="E737" s="29"/>
+      <c r="A737" s="28"/>
+      <c r="E737" s="28"/>
     </row>
     <row r="738" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A738" s="29"/>
-      <c r="E738" s="29"/>
+      <c r="A738" s="28"/>
+      <c r="E738" s="28"/>
     </row>
     <row r="739" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A739" s="29"/>
-      <c r="E739" s="29"/>
+      <c r="A739" s="28"/>
+      <c r="E739" s="28"/>
     </row>
     <row r="740" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A740" s="29"/>
-      <c r="E740" s="29"/>
+      <c r="A740" s="28"/>
+      <c r="E740" s="28"/>
     </row>
     <row r="741" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A741" s="29"/>
-      <c r="E741" s="29"/>
+      <c r="A741" s="28"/>
+      <c r="E741" s="28"/>
     </row>
     <row r="742" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A742" s="29"/>
-      <c r="E742" s="29"/>
+      <c r="A742" s="28"/>
+      <c r="E742" s="28"/>
     </row>
     <row r="743" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A743" s="29"/>
-      <c r="E743" s="29"/>
+      <c r="A743" s="28"/>
+      <c r="E743" s="28"/>
     </row>
     <row r="744" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A744" s="29"/>
-      <c r="E744" s="29"/>
+      <c r="A744" s="28"/>
+      <c r="E744" s="28"/>
     </row>
     <row r="745" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A745" s="29"/>
-      <c r="E745" s="29"/>
+      <c r="A745" s="28"/>
+      <c r="E745" s="28"/>
     </row>
     <row r="746" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A746" s="29"/>
-      <c r="E746" s="29"/>
+      <c r="A746" s="28"/>
+      <c r="E746" s="28"/>
     </row>
     <row r="747" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A747" s="29"/>
-      <c r="E747" s="29"/>
+      <c r="A747" s="28"/>
+      <c r="E747" s="28"/>
     </row>
     <row r="748" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A748" s="29"/>
-      <c r="E748" s="29"/>
+      <c r="A748" s="28"/>
+      <c r="E748" s="28"/>
     </row>
     <row r="749" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A749" s="29"/>
-      <c r="E749" s="29"/>
+      <c r="A749" s="28"/>
+      <c r="E749" s="28"/>
     </row>
     <row r="750" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A750" s="29"/>
-      <c r="E750" s="29"/>
+      <c r="A750" s="28"/>
+      <c r="E750" s="28"/>
     </row>
     <row r="751" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A751" s="29"/>
-      <c r="E751" s="29"/>
+      <c r="A751" s="28"/>
+      <c r="E751" s="28"/>
     </row>
     <row r="752" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A752" s="29"/>
-      <c r="E752" s="29"/>
+      <c r="A752" s="28"/>
+      <c r="E752" s="28"/>
     </row>
     <row r="753" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A753" s="29"/>
-      <c r="E753" s="29"/>
+      <c r="A753" s="28"/>
+      <c r="E753" s="28"/>
     </row>
     <row r="754" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A754" s="29"/>
-      <c r="E754" s="29"/>
+      <c r="A754" s="28"/>
+      <c r="E754" s="28"/>
     </row>
     <row r="755" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A755" s="29"/>
-      <c r="E755" s="29"/>
+      <c r="A755" s="28"/>
+      <c r="E755" s="28"/>
     </row>
     <row r="756" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A756" s="29"/>
-      <c r="E756" s="29"/>
+      <c r="A756" s="28"/>
+      <c r="E756" s="28"/>
     </row>
     <row r="757" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A757" s="29"/>
-      <c r="E757" s="29"/>
+      <c r="A757" s="28"/>
+      <c r="E757" s="28"/>
     </row>
     <row r="758" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A758" s="29"/>
-      <c r="E758" s="29"/>
+      <c r="A758" s="28"/>
+      <c r="E758" s="28"/>
     </row>
     <row r="759" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A759" s="29"/>
-      <c r="E759" s="29"/>
+      <c r="A759" s="28"/>
+      <c r="E759" s="28"/>
     </row>
     <row r="760" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A760" s="29"/>
-      <c r="E760" s="29"/>
+      <c r="A760" s="28"/>
+      <c r="E760" s="28"/>
     </row>
     <row r="761" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A761" s="29"/>
-      <c r="E761" s="29"/>
+      <c r="A761" s="28"/>
+      <c r="E761" s="28"/>
     </row>
     <row r="762" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A762" s="29"/>
-      <c r="E762" s="29"/>
+      <c r="A762" s="28"/>
+      <c r="E762" s="28"/>
     </row>
     <row r="763" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A763" s="29"/>
-      <c r="E763" s="29"/>
+      <c r="A763" s="28"/>
+      <c r="E763" s="28"/>
     </row>
     <row r="764" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A764" s="29"/>
-      <c r="E764" s="29"/>
+      <c r="A764" s="28"/>
+      <c r="E764" s="28"/>
     </row>
     <row r="765" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A765" s="29"/>
-      <c r="E765" s="29"/>
+      <c r="A765" s="28"/>
+      <c r="E765" s="28"/>
     </row>
     <row r="766" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A766" s="29"/>
-      <c r="E766" s="29"/>
+      <c r="A766" s="28"/>
+      <c r="E766" s="28"/>
     </row>
     <row r="767" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A767" s="29"/>
-      <c r="E767" s="29"/>
+      <c r="A767" s="28"/>
+      <c r="E767" s="28"/>
     </row>
     <row r="768" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A768" s="29"/>
-      <c r="E768" s="29"/>
+      <c r="A768" s="28"/>
+      <c r="E768" s="28"/>
     </row>
     <row r="769" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A769" s="29"/>
-      <c r="E769" s="29"/>
+      <c r="A769" s="28"/>
+      <c r="E769" s="28"/>
     </row>
     <row r="770" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A770" s="29"/>
-      <c r="E770" s="29"/>
+      <c r="A770" s="28"/>
+      <c r="E770" s="28"/>
     </row>
     <row r="771" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A771" s="29"/>
-      <c r="E771" s="29"/>
+      <c r="A771" s="28"/>
+      <c r="E771" s="28"/>
     </row>
     <row r="772" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A772" s="29"/>
-      <c r="E772" s="29"/>
+      <c r="A772" s="28"/>
+      <c r="E772" s="28"/>
     </row>
     <row r="773" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A773" s="29"/>
-      <c r="E773" s="29"/>
+      <c r="A773" s="28"/>
+      <c r="E773" s="28"/>
     </row>
     <row r="774" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A774" s="29"/>
-      <c r="E774" s="29"/>
+      <c r="A774" s="28"/>
+      <c r="E774" s="28"/>
     </row>
     <row r="775" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A775" s="29"/>
-      <c r="E775" s="29"/>
+      <c r="A775" s="28"/>
+      <c r="E775" s="28"/>
     </row>
     <row r="776" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A776" s="29"/>
-      <c r="E776" s="29"/>
+      <c r="A776" s="28"/>
+      <c r="E776" s="28"/>
     </row>
     <row r="777" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A777" s="29"/>
-      <c r="E777" s="29"/>
+      <c r="A777" s="28"/>
+      <c r="E777" s="28"/>
     </row>
     <row r="778" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A778" s="29"/>
-      <c r="E778" s="29"/>
+      <c r="A778" s="28"/>
+      <c r="E778" s="28"/>
     </row>
     <row r="779" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A779" s="29"/>
-      <c r="E779" s="29"/>
+      <c r="A779" s="28"/>
+      <c r="E779" s="28"/>
     </row>
     <row r="780" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A780" s="29"/>
-      <c r="E780" s="29"/>
+      <c r="A780" s="28"/>
+      <c r="E780" s="28"/>
     </row>
     <row r="781" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A781" s="29"/>
-      <c r="E781" s="29"/>
+      <c r="A781" s="28"/>
+      <c r="E781" s="28"/>
     </row>
     <row r="782" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A782" s="29"/>
-      <c r="E782" s="29"/>
+      <c r="A782" s="28"/>
+      <c r="E782" s="28"/>
     </row>
     <row r="783" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A783" s="29"/>
-      <c r="E783" s="29"/>
+      <c r="A783" s="28"/>
+      <c r="E783" s="28"/>
     </row>
     <row r="784" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A784" s="29"/>
-      <c r="E784" s="29"/>
+      <c r="A784" s="28"/>
+      <c r="E784" s="28"/>
     </row>
     <row r="785" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A785" s="29"/>
-      <c r="E785" s="29"/>
+      <c r="A785" s="28"/>
+      <c r="E785" s="28"/>
     </row>
     <row r="786" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A786" s="29"/>
-      <c r="E786" s="29"/>
+      <c r="A786" s="28"/>
+      <c r="E786" s="28"/>
     </row>
     <row r="787" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A787" s="29"/>
-      <c r="E787" s="29"/>
+      <c r="A787" s="28"/>
+      <c r="E787" s="28"/>
     </row>
     <row r="788" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A788" s="29"/>
-      <c r="E788" s="29"/>
+      <c r="A788" s="28"/>
+      <c r="E788" s="28"/>
     </row>
     <row r="789" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A789" s="29"/>
-      <c r="E789" s="29"/>
+      <c r="A789" s="28"/>
+      <c r="E789" s="28"/>
     </row>
     <row r="790" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A790" s="29"/>
-      <c r="E790" s="29"/>
+      <c r="A790" s="28"/>
+      <c r="E790" s="28"/>
     </row>
     <row r="791" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A791" s="29"/>
-      <c r="E791" s="29"/>
+      <c r="A791" s="28"/>
+      <c r="E791" s="28"/>
     </row>
     <row r="792" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A792" s="29"/>
-      <c r="E792" s="29"/>
+      <c r="A792" s="28"/>
+      <c r="E792" s="28"/>
     </row>
     <row r="793" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A793" s="29"/>
-      <c r="E793" s="29"/>
+      <c r="A793" s="28"/>
+      <c r="E793" s="28"/>
     </row>
     <row r="794" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A794" s="29"/>
-      <c r="E794" s="29"/>
+      <c r="A794" s="28"/>
+      <c r="E794" s="28"/>
     </row>
     <row r="795" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A795" s="29"/>
-      <c r="E795" s="29"/>
+      <c r="A795" s="28"/>
+      <c r="E795" s="28"/>
     </row>
     <row r="796" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A796" s="29"/>
-      <c r="E796" s="29"/>
+      <c r="A796" s="28"/>
+      <c r="E796" s="28"/>
     </row>
     <row r="797" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A797" s="29"/>
-      <c r="E797" s="29"/>
+      <c r="A797" s="28"/>
+      <c r="E797" s="28"/>
     </row>
     <row r="798" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A798" s="29"/>
-      <c r="E798" s="29"/>
+      <c r="A798" s="28"/>
+      <c r="E798" s="28"/>
     </row>
     <row r="799" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A799" s="29"/>
-      <c r="E799" s="29"/>
+      <c r="A799" s="28"/>
+      <c r="E799" s="28"/>
     </row>
     <row r="800" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A800" s="29"/>
-      <c r="E800" s="29"/>
+      <c r="A800" s="28"/>
+      <c r="E800" s="28"/>
     </row>
     <row r="801" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A801" s="29"/>
-      <c r="E801" s="29"/>
+      <c r="A801" s="28"/>
+      <c r="E801" s="28"/>
     </row>
     <row r="802" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A802" s="29"/>
-      <c r="E802" s="29"/>
+      <c r="A802" s="28"/>
+      <c r="E802" s="28"/>
     </row>
     <row r="803" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A803" s="29"/>
-      <c r="E803" s="29"/>
+      <c r="A803" s="28"/>
+      <c r="E803" s="28"/>
     </row>
     <row r="804" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A804" s="29"/>
-      <c r="E804" s="29"/>
+      <c r="A804" s="28"/>
+      <c r="E804" s="28"/>
     </row>
     <row r="805" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A805" s="29"/>
-      <c r="E805" s="29"/>
+      <c r="A805" s="28"/>
+      <c r="E805" s="28"/>
     </row>
     <row r="806" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A806" s="29"/>
-      <c r="E806" s="29"/>
+      <c r="A806" s="28"/>
+      <c r="E806" s="28"/>
     </row>
     <row r="807" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A807" s="29"/>
-      <c r="E807" s="29"/>
+      <c r="A807" s="28"/>
+      <c r="E807" s="28"/>
     </row>
     <row r="808" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A808" s="29"/>
-      <c r="E808" s="29"/>
+      <c r="A808" s="28"/>
+      <c r="E808" s="28"/>
     </row>
     <row r="809" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A809" s="29"/>
-      <c r="E809" s="29"/>
+      <c r="A809" s="28"/>
+      <c r="E809" s="28"/>
     </row>
     <row r="810" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A810" s="29"/>
-      <c r="E810" s="29"/>
+      <c r="A810" s="28"/>
+      <c r="E810" s="28"/>
     </row>
     <row r="811" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A811" s="29"/>
-      <c r="E811" s="29"/>
+      <c r="A811" s="28"/>
+      <c r="E811" s="28"/>
     </row>
     <row r="812" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A812" s="29"/>
-      <c r="E812" s="29"/>
+      <c r="A812" s="28"/>
+      <c r="E812" s="28"/>
     </row>
     <row r="813" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A813" s="29"/>
-      <c r="E813" s="29"/>
+      <c r="A813" s="28"/>
+      <c r="E813" s="28"/>
     </row>
     <row r="814" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A814" s="29"/>
-      <c r="E814" s="29"/>
+      <c r="A814" s="28"/>
+      <c r="E814" s="28"/>
     </row>
     <row r="815" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A815" s="29"/>
-      <c r="E815" s="29"/>
+      <c r="A815" s="28"/>
+      <c r="E815" s="28"/>
     </row>
     <row r="816" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A816" s="29"/>
-      <c r="E816" s="29"/>
+      <c r="A816" s="28"/>
+      <c r="E816" s="28"/>
     </row>
     <row r="817" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A817" s="29"/>
-      <c r="E817" s="29"/>
+      <c r="A817" s="28"/>
+      <c r="E817" s="28"/>
     </row>
     <row r="818" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A818" s="29"/>
-      <c r="E818" s="29"/>
+      <c r="A818" s="28"/>
+      <c r="E818" s="28"/>
     </row>
     <row r="819" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A819" s="29"/>
-      <c r="E819" s="29"/>
+      <c r="A819" s="28"/>
+      <c r="E819" s="28"/>
     </row>
     <row r="820" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A820" s="29"/>
-      <c r="E820" s="29"/>
+      <c r="A820" s="28"/>
+      <c r="E820" s="28"/>
     </row>
     <row r="821" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A821" s="29"/>
-      <c r="E821" s="29"/>
+      <c r="A821" s="28"/>
+      <c r="E821" s="28"/>
     </row>
     <row r="822" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A822" s="29"/>
-      <c r="E822" s="29"/>
+      <c r="A822" s="28"/>
+      <c r="E822" s="28"/>
     </row>
     <row r="823" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A823" s="29"/>
-      <c r="E823" s="29"/>
+      <c r="A823" s="28"/>
+      <c r="E823" s="28"/>
     </row>
     <row r="824" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A824" s="29"/>
-      <c r="E824" s="29"/>
+      <c r="A824" s="28"/>
+      <c r="E824" s="28"/>
     </row>
     <row r="825" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A825" s="29"/>
-      <c r="E825" s="29"/>
+      <c r="A825" s="28"/>
+      <c r="E825" s="28"/>
     </row>
     <row r="826" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A826" s="29"/>
-      <c r="E826" s="29"/>
+      <c r="A826" s="28"/>
+      <c r="E826" s="28"/>
     </row>
     <row r="827" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A827" s="29"/>
-      <c r="E827" s="29"/>
+      <c r="A827" s="28"/>
+      <c r="E827" s="28"/>
     </row>
     <row r="828" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A828" s="29"/>
-      <c r="E828" s="29"/>
+      <c r="A828" s="28"/>
+      <c r="E828" s="28"/>
     </row>
     <row r="829" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A829" s="29"/>
-      <c r="E829" s="29"/>
+      <c r="A829" s="28"/>
+      <c r="E829" s="28"/>
     </row>
     <row r="830" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A830" s="29"/>
-      <c r="E830" s="29"/>
+      <c r="A830" s="28"/>
+      <c r="E830" s="28"/>
     </row>
     <row r="831" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A831" s="29"/>
-      <c r="E831" s="29"/>
+      <c r="A831" s="28"/>
+      <c r="E831" s="28"/>
     </row>
     <row r="832" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A832" s="29"/>
-      <c r="E832" s="29"/>
+      <c r="A832" s="28"/>
+      <c r="E832" s="28"/>
     </row>
     <row r="833" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A833" s="29"/>
-      <c r="E833" s="29"/>
+      <c r="A833" s="28"/>
+      <c r="E833" s="28"/>
     </row>
     <row r="834" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A834" s="29"/>
-      <c r="E834" s="29"/>
+      <c r="A834" s="28"/>
+      <c r="E834" s="28"/>
     </row>
     <row r="835" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A835" s="29"/>
-      <c r="E835" s="29"/>
+      <c r="A835" s="28"/>
+      <c r="E835" s="28"/>
     </row>
     <row r="836" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A836" s="29"/>
-      <c r="E836" s="29"/>
+      <c r="A836" s="28"/>
+      <c r="E836" s="28"/>
     </row>
     <row r="837" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A837" s="29"/>
-      <c r="E837" s="29"/>
+      <c r="A837" s="28"/>
+      <c r="E837" s="28"/>
     </row>
     <row r="838" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A838" s="29"/>
-      <c r="E838" s="29"/>
+      <c r="A838" s="28"/>
+      <c r="E838" s="28"/>
     </row>
     <row r="839" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A839" s="29"/>
-      <c r="E839" s="29"/>
+      <c r="A839" s="28"/>
+      <c r="E839" s="28"/>
     </row>
     <row r="840" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A840" s="29"/>
-      <c r="E840" s="29"/>
+      <c r="A840" s="28"/>
+      <c r="E840" s="28"/>
     </row>
     <row r="841" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A841" s="29"/>
-      <c r="E841" s="29"/>
+      <c r="A841" s="28"/>
+      <c r="E841" s="28"/>
     </row>
     <row r="842" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A842" s="29"/>
-      <c r="E842" s="29"/>
+      <c r="A842" s="28"/>
+      <c r="E842" s="28"/>
     </row>
     <row r="843" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A843" s="29"/>
-      <c r="E843" s="29"/>
+      <c r="A843" s="28"/>
+      <c r="E843" s="28"/>
     </row>
     <row r="844" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A844" s="29"/>
-      <c r="E844" s="29"/>
+      <c r="A844" s="28"/>
+      <c r="E844" s="28"/>
     </row>
     <row r="845" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A845" s="29"/>
-      <c r="E845" s="29"/>
+      <c r="A845" s="28"/>
+      <c r="E845" s="28"/>
     </row>
     <row r="846" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A846" s="29"/>
-      <c r="E846" s="29"/>
+      <c r="A846" s="28"/>
+      <c r="E846" s="28"/>
     </row>
     <row r="847" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A847" s="29"/>
-      <c r="E847" s="29"/>
+      <c r="A847" s="28"/>
+      <c r="E847" s="28"/>
     </row>
     <row r="848" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A848" s="29"/>
-      <c r="E848" s="29"/>
+      <c r="A848" s="28"/>
+      <c r="E848" s="28"/>
     </row>
     <row r="849" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A849" s="29"/>
-      <c r="E849" s="29"/>
+      <c r="A849" s="28"/>
+      <c r="E849" s="28"/>
     </row>
     <row r="850" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A850" s="29"/>
-      <c r="E850" s="29"/>
+      <c r="A850" s="28"/>
+      <c r="E850" s="28"/>
     </row>
     <row r="851" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A851" s="29"/>
-      <c r="E851" s="29"/>
+      <c r="A851" s="28"/>
+      <c r="E851" s="28"/>
     </row>
     <row r="852" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A852" s="29"/>
-      <c r="E852" s="29"/>
+      <c r="A852" s="28"/>
+      <c r="E852" s="28"/>
     </row>
     <row r="853" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A853" s="29"/>
-      <c r="E853" s="29"/>
+      <c r="A853" s="28"/>
+      <c r="E853" s="28"/>
     </row>
     <row r="854" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A854" s="29"/>
-      <c r="E854" s="29"/>
+      <c r="A854" s="28"/>
+      <c r="E854" s="28"/>
     </row>
     <row r="855" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A855" s="29"/>
-      <c r="E855" s="29"/>
+      <c r="A855" s="28"/>
+      <c r="E855" s="28"/>
     </row>
     <row r="856" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A856" s="29"/>
-      <c r="E856" s="29"/>
+      <c r="A856" s="28"/>
+      <c r="E856" s="28"/>
     </row>
     <row r="857" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A857" s="29"/>
-      <c r="E857" s="29"/>
+      <c r="A857" s="28"/>
+      <c r="E857" s="28"/>
     </row>
     <row r="858" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A858" s="29"/>
-      <c r="E858" s="29"/>
+      <c r="A858" s="28"/>
+      <c r="E858" s="28"/>
     </row>
     <row r="859" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A859" s="29"/>
-      <c r="E859" s="29"/>
+      <c r="A859" s="28"/>
+      <c r="E859" s="28"/>
     </row>
     <row r="860" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A860" s="29"/>
-      <c r="E860" s="29"/>
+      <c r="A860" s="28"/>
+      <c r="E860" s="28"/>
     </row>
     <row r="861" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A861" s="29"/>
-      <c r="E861" s="29"/>
+      <c r="A861" s="28"/>
+      <c r="E861" s="28"/>
     </row>
     <row r="862" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A862" s="29"/>
-      <c r="E862" s="29"/>
+      <c r="A862" s="28"/>
+      <c r="E862" s="28"/>
     </row>
     <row r="863" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A863" s="29"/>
-      <c r="E863" s="29"/>
+      <c r="A863" s="28"/>
+      <c r="E863" s="28"/>
     </row>
     <row r="864" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A864" s="29"/>
-      <c r="E864" s="29"/>
+      <c r="A864" s="28"/>
+      <c r="E864" s="28"/>
     </row>
     <row r="865" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A865" s="29"/>
-      <c r="E865" s="29"/>
+      <c r="A865" s="28"/>
+      <c r="E865" s="28"/>
     </row>
     <row r="866" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A866" s="29"/>
-      <c r="E866" s="29"/>
+      <c r="A866" s="28"/>
+      <c r="E866" s="28"/>
     </row>
     <row r="867" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A867" s="29"/>
-      <c r="E867" s="29"/>
+      <c r="A867" s="28"/>
+      <c r="E867" s="28"/>
     </row>
     <row r="868" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A868" s="29"/>
-      <c r="E868" s="29"/>
+      <c r="A868" s="28"/>
+      <c r="E868" s="28"/>
     </row>
     <row r="869" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A869" s="29"/>
-      <c r="E869" s="29"/>
+      <c r="A869" s="28"/>
+      <c r="E869" s="28"/>
     </row>
     <row r="870" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A870" s="29"/>
-      <c r="E870" s="29"/>
+      <c r="A870" s="28"/>
+      <c r="E870" s="28"/>
     </row>
     <row r="871" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A871" s="29"/>
-      <c r="E871" s="29"/>
+      <c r="A871" s="28"/>
+      <c r="E871" s="28"/>
     </row>
     <row r="872" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A872" s="29"/>
-      <c r="E872" s="29"/>
+      <c r="A872" s="28"/>
+      <c r="E872" s="28"/>
     </row>
     <row r="873" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A873" s="29"/>
-      <c r="E873" s="29"/>
+      <c r="A873" s="28"/>
+      <c r="E873" s="28"/>
     </row>
     <row r="874" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A874" s="29"/>
-      <c r="E874" s="29"/>
+      <c r="A874" s="28"/>
+      <c r="E874" s="28"/>
     </row>
     <row r="875" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A875" s="29"/>
-      <c r="E875" s="29"/>
+      <c r="A875" s="28"/>
+      <c r="E875" s="28"/>
     </row>
     <row r="876" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A876" s="29"/>
-      <c r="E876" s="29"/>
+      <c r="A876" s="28"/>
+      <c r="E876" s="28"/>
     </row>
     <row r="877" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A877" s="29"/>
-      <c r="E877" s="29"/>
+      <c r="A877" s="28"/>
+      <c r="E877" s="28"/>
     </row>
     <row r="878" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A878" s="29"/>
-      <c r="E878" s="29"/>
-    </row>
-    <row r="879" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A879" s="29"/>
-      <c r="E879" s="29"/>
-    </row>
-    <row r="880" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A880" s="29"/>
-      <c r="E880" s="29"/>
-    </row>
-    <row r="881" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A881" s="29"/>
-      <c r="E881" s="29"/>
-    </row>
-    <row r="882" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A882" s="29"/>
-      <c r="E882" s="29"/>
-    </row>
-    <row r="883" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A883" s="29"/>
-      <c r="E883" s="29"/>
-    </row>
-    <row r="884" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A884" s="29"/>
-      <c r="E884" s="29"/>
-    </row>
-    <row r="885" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A885" s="29"/>
-      <c r="E885" s="29"/>
-    </row>
-    <row r="886" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A886" s="29"/>
-      <c r="E886" s="29"/>
-    </row>
-    <row r="887" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A887" s="29"/>
-      <c r="E887" s="29"/>
-    </row>
-    <row r="888" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A888" s="29"/>
-      <c r="E888" s="29"/>
-    </row>
-    <row r="889" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A889" s="29"/>
-      <c r="E889" s="29"/>
-    </row>
-    <row r="890" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A890" s="29"/>
-      <c r="E890" s="29"/>
-    </row>
-    <row r="891" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A891" s="29"/>
-      <c r="E891" s="29"/>
-    </row>
-    <row r="892" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A892" s="29"/>
-      <c r="E892" s="29"/>
-    </row>
-    <row r="893" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A893" s="29"/>
-      <c r="E893" s="29"/>
-    </row>
-    <row r="894" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A894" s="29"/>
-      <c r="E894" s="29"/>
-    </row>
-    <row r="895" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A895" s="29"/>
-      <c r="E895" s="29"/>
-    </row>
-    <row r="896" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A896" s="29"/>
-      <c r="E896" s="29"/>
-    </row>
-    <row r="897" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A897" s="29"/>
-      <c r="E897" s="29"/>
-    </row>
-    <row r="898" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A898" s="29"/>
-      <c r="E898" s="29"/>
-    </row>
-    <row r="899" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A899" s="29"/>
-      <c r="E899" s="29"/>
-    </row>
-    <row r="900" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A900" s="29"/>
-      <c r="E900" s="29"/>
-    </row>
-    <row r="901" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A901" s="29"/>
-      <c r="E901" s="29"/>
-    </row>
-    <row r="902" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A902" s="29"/>
-      <c r="E902" s="29"/>
-    </row>
-    <row r="903" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A903" s="29"/>
-      <c r="E903" s="29"/>
-    </row>
-    <row r="904" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A904" s="29"/>
-      <c r="E904" s="29"/>
-    </row>
-    <row r="905" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A905" s="29"/>
-      <c r="E905" s="29"/>
-    </row>
-    <row r="906" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A906" s="29"/>
-      <c r="E906" s="29"/>
-    </row>
-    <row r="907" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A907" s="29"/>
-      <c r="E907" s="29"/>
-    </row>
-    <row r="908" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A908" s="29"/>
-      <c r="E908" s="29"/>
-    </row>
-    <row r="909" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A909" s="29"/>
-      <c r="E909" s="29"/>
-    </row>
-    <row r="910" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A910" s="29"/>
-      <c r="E910" s="29"/>
-    </row>
-    <row r="911" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A911" s="29"/>
-      <c r="E911" s="29"/>
-    </row>
-    <row r="912" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A912" s="29"/>
-      <c r="E912" s="29"/>
-    </row>
-    <row r="913" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A913" s="29"/>
-      <c r="E913" s="29"/>
-    </row>
-    <row r="914" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A914" s="29"/>
-      <c r="E914" s="29"/>
-    </row>
-    <row r="915" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A915" s="29"/>
-      <c r="E915" s="29"/>
-    </row>
-    <row r="916" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A916" s="29"/>
-      <c r="E916" s="29"/>
-    </row>
-    <row r="917" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A917" s="29"/>
-      <c r="E917" s="29"/>
-    </row>
-    <row r="918" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A918" s="29"/>
-      <c r="E918" s="29"/>
-    </row>
-    <row r="919" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A919" s="29"/>
-      <c r="E919" s="29"/>
-    </row>
-    <row r="920" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A920" s="29"/>
-      <c r="E920" s="29"/>
-    </row>
-    <row r="921" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A921" s="29"/>
-      <c r="E921" s="29"/>
-    </row>
-    <row r="922" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A922" s="29"/>
-      <c r="E922" s="29"/>
-    </row>
-    <row r="923" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A923" s="29"/>
-      <c r="E923" s="29"/>
-    </row>
-    <row r="924" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A924" s="29"/>
-      <c r="E924" s="29"/>
-    </row>
-    <row r="925" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A925" s="29"/>
-      <c r="E925" s="29"/>
-    </row>
-    <row r="926" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A926" s="29"/>
-      <c r="E926" s="29"/>
-    </row>
-    <row r="927" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A927" s="29"/>
-      <c r="E927" s="29"/>
-    </row>
-    <row r="928" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A928" s="29"/>
-      <c r="E928" s="29"/>
-    </row>
-    <row r="929" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A929" s="29"/>
-      <c r="E929" s="29"/>
-    </row>
-    <row r="930" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A930" s="29"/>
-      <c r="E930" s="29"/>
-    </row>
-    <row r="931" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A931" s="29"/>
-      <c r="E931" s="29"/>
-    </row>
-    <row r="932" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A932" s="29"/>
-      <c r="E932" s="29"/>
-    </row>
-    <row r="933" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A933" s="29"/>
-      <c r="E933" s="29"/>
-    </row>
-    <row r="934" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A934" s="29"/>
-      <c r="E934" s="29"/>
-    </row>
+      <c r="A878" s="28"/>
+      <c r="E878" s="28"/>
+    </row>
+    <row r="879" spans="1:5" ht="14.25" customHeight="1"/>
+    <row r="880" spans="1:5" ht="14.25" customHeight="1"/>
+    <row r="881" ht="14.25" customHeight="1"/>
+    <row r="882" ht="14.25" customHeight="1"/>
+    <row r="883" ht="14.25" customHeight="1"/>
+    <row r="884" ht="14.25" customHeight="1"/>
+    <row r="885" ht="14.25" customHeight="1"/>
+    <row r="886" ht="14.25" customHeight="1"/>
+    <row r="887" ht="14.25" customHeight="1"/>
+    <row r="888" ht="14.25" customHeight="1"/>
+    <row r="889" ht="14.25" customHeight="1"/>
+    <row r="890" ht="14.25" customHeight="1"/>
+    <row r="891" ht="14.25" customHeight="1"/>
+    <row r="892" ht="14.25" customHeight="1"/>
+    <row r="893" ht="14.25" customHeight="1"/>
+    <row r="894" ht="14.25" customHeight="1"/>
+    <row r="895" ht="14.25" customHeight="1"/>
+    <row r="896" ht="14.25" customHeight="1"/>
+    <row r="897" ht="14.25" customHeight="1"/>
+    <row r="898" ht="14.25" customHeight="1"/>
+    <row r="899" ht="14.25" customHeight="1"/>
+    <row r="900" ht="14.25" customHeight="1"/>
+    <row r="901" ht="14.25" customHeight="1"/>
+    <row r="902" ht="14.25" customHeight="1"/>
+    <row r="903" ht="14.25" customHeight="1"/>
+    <row r="904" ht="14.25" customHeight="1"/>
+    <row r="905" ht="14.25" customHeight="1"/>
+    <row r="906" ht="14.25" customHeight="1"/>
+    <row r="907" ht="14.25" customHeight="1"/>
+    <row r="908" ht="14.25" customHeight="1"/>
+    <row r="909" ht="14.25" customHeight="1"/>
+    <row r="910" ht="14.25" customHeight="1"/>
+    <row r="911" ht="14.25" customHeight="1"/>
+    <row r="912" ht="14.25" customHeight="1"/>
+    <row r="913" ht="14.25" customHeight="1"/>
+    <row r="914" ht="14.25" customHeight="1"/>
+    <row r="915" ht="14.25" customHeight="1"/>
+    <row r="916" ht="14.25" customHeight="1"/>
+    <row r="917" ht="14.25" customHeight="1"/>
+    <row r="918" ht="14.25" customHeight="1"/>
+    <row r="919" ht="14.25" customHeight="1"/>
+    <row r="920" ht="14.25" customHeight="1"/>
+    <row r="921" ht="14.25" customHeight="1"/>
+    <row r="922" ht="14.25" customHeight="1"/>
+    <row r="923" ht="14.25" customHeight="1"/>
+    <row r="924" ht="14.25" customHeight="1"/>
+    <row r="925" ht="14.25" customHeight="1"/>
+    <row r="926" ht="14.25" customHeight="1"/>
+    <row r="927" ht="14.25" customHeight="1"/>
+    <row r="928" ht="14.25" customHeight="1"/>
+    <row r="929" ht="14.25" customHeight="1"/>
+    <row r="930" ht="14.25" customHeight="1"/>
+    <row r="931" ht="14.25" customHeight="1"/>
+    <row r="932" ht="14.25" customHeight="1"/>
+    <row r="933" ht="14.25" customHeight="1"/>
+    <row r="934" ht="14.25" customHeight="1"/>
   </sheetData>
-  <mergeCells count="64">
-    <mergeCell ref="F337:F340"/>
-    <mergeCell ref="G337:G340"/>
-    <mergeCell ref="D327:D330"/>
-    <mergeCell ref="D332:D335"/>
-    <mergeCell ref="E332:E335"/>
-    <mergeCell ref="F332:F335"/>
-    <mergeCell ref="G332:G335"/>
-    <mergeCell ref="D337:D340"/>
-    <mergeCell ref="E337:E340"/>
-    <mergeCell ref="E327:E330"/>
-    <mergeCell ref="F327:F330"/>
-    <mergeCell ref="G327:G330"/>
+  <mergeCells count="67">
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="D72:D73"/>
+    <mergeCell ref="A58:A60"/>
+    <mergeCell ref="B58:B60"/>
+    <mergeCell ref="C58:C60"/>
+    <mergeCell ref="D58:D60"/>
+    <mergeCell ref="A62:A64"/>
+    <mergeCell ref="B62:B64"/>
+    <mergeCell ref="C62:C64"/>
+    <mergeCell ref="D62:D64"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="D49:D50"/>
+    <mergeCell ref="A52:A54"/>
+    <mergeCell ref="B52:B54"/>
+    <mergeCell ref="C52:C54"/>
+    <mergeCell ref="D52:D54"/>
+    <mergeCell ref="A42:A44"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="B28:B30"/>
+    <mergeCell ref="C28:C30"/>
+    <mergeCell ref="D28:D30"/>
+    <mergeCell ref="A15:A18"/>
+    <mergeCell ref="B15:B18"/>
+    <mergeCell ref="C15:C18"/>
+    <mergeCell ref="D15:D18"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="B20:B23"/>
+    <mergeCell ref="C20:C23"/>
+    <mergeCell ref="D20:D23"/>
+    <mergeCell ref="E269:H269"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="D9:D11"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="B1:E1"/>
     <mergeCell ref="F1:I1"/>
     <mergeCell ref="A3:A7"/>
     <mergeCell ref="B3:B7"/>
     <mergeCell ref="C3:C7"/>
     <mergeCell ref="D3:D7"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="D9:D11"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="A15:A18"/>
-    <mergeCell ref="D15:D18"/>
-    <mergeCell ref="B37:B39"/>
-    <mergeCell ref="C37:C39"/>
-    <mergeCell ref="B15:B18"/>
-    <mergeCell ref="C15:C18"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="D37:D39"/>
-    <mergeCell ref="A37:A39"/>
-    <mergeCell ref="A23:A25"/>
-    <mergeCell ref="B23:B25"/>
-    <mergeCell ref="C23:C25"/>
-    <mergeCell ref="D23:D25"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="A47:A49"/>
-    <mergeCell ref="B47:B49"/>
-    <mergeCell ref="C47:C49"/>
-    <mergeCell ref="D47:D49"/>
-    <mergeCell ref="A53:A55"/>
-    <mergeCell ref="A57:A59"/>
-    <mergeCell ref="B57:B59"/>
-    <mergeCell ref="C57:C59"/>
-    <mergeCell ref="D57:D59"/>
-    <mergeCell ref="D67:D68"/>
-    <mergeCell ref="C67:C68"/>
-    <mergeCell ref="B67:B68"/>
-    <mergeCell ref="A67:A68"/>
-    <mergeCell ref="I325:L325"/>
-    <mergeCell ref="E325:H325"/>
-    <mergeCell ref="B53:B55"/>
-    <mergeCell ref="C53:C55"/>
-    <mergeCell ref="D53:D55"/>
+    <mergeCell ref="F281:F284"/>
+    <mergeCell ref="G281:G284"/>
+    <mergeCell ref="D271:D274"/>
+    <mergeCell ref="D276:D279"/>
+    <mergeCell ref="E276:E279"/>
+    <mergeCell ref="F276:F279"/>
+    <mergeCell ref="G276:G279"/>
+    <mergeCell ref="D281:D284"/>
+    <mergeCell ref="E281:E284"/>
+    <mergeCell ref="E271:E274"/>
+    <mergeCell ref="F271:F274"/>
+    <mergeCell ref="G271:G274"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>

--- a/1.Project-with_Monolithic_Architecture/requirements/requirements_specification.xlsx
+++ b/1.Project-with_Monolithic_Architecture/requirements/requirements_specification.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\SoftwareProjects\Piedrazul-Medical-Services-Network\1.Project-with_Monolithic_Architecture\requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84CD7D34-7751-49D0-A0FD-0078F6079AC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4CB5331-4C7F-40B9-88A1-E656DC1552EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2295" yWindow="2295" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Backlog" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="327">
   <si>
     <t>Sistema de gestion y agendamiento de citas medicas para centro de salud Piedra azul</t>
   </si>
@@ -941,17 +941,74 @@
     <t>Como administrador</t>
   </si>
   <si>
-    <t xml:space="preserve">Para tener control del acceso de los usuarios </t>
-  </si>
-  <si>
     <t>Quiero desactivar usuarios</t>
+  </si>
+  <si>
+    <t>Para impedir que un usuario acceda al sistema sin eliminar su información</t>
+  </si>
+  <si>
+    <t>Desactivación exitosa</t>
+  </si>
+  <si>
+    <t>Intento de desactivar el último administrador</t>
+  </si>
+  <si>
+    <t>Usuario ya inactivo</t>
+  </si>
+  <si>
+    <t>Intento de acceso con usuario desactivado</t>
+  </si>
+  <si>
+    <t>En caso que el administrador esté autenticado y el usuario objetivo exista y esté en estado ACTIVO y exista al menos otro administrador activo en el sistema</t>
+  </si>
+  <si>
+    <t>cuando el administrador seleccione la opción "Desacttivar usuario"</t>
+  </si>
+  <si>
+    <t>el sistema cambia el estado del usuario a INACTIVO, impide futuros accesos al sistema, registra la acción en auditoría y muestra mensaje de confirmación</t>
+  </si>
+  <si>
+    <t>En caso que el usuario objetivo sea el últiimo administrador activo</t>
+  </si>
+  <si>
+    <t>cuando se intente desactivarlo</t>
+  </si>
+  <si>
+    <t>el sistema bloquea la operación, mantiene el estado ACTIVO  y muestra mensaje: "No es posible desactivar el último administrador del sistema"</t>
+  </si>
+  <si>
+    <t>En caso que el usuario no exista en el sistema</t>
+  </si>
+  <si>
+    <t>cuando el administrador intente desactivarlo</t>
+  </si>
+  <si>
+    <t>el sistema no realiza ninguna acción y muestra mensaje de error indicando que el usuario no existe</t>
+  </si>
+  <si>
+    <t>En caso que el usuario ya esté en estado INACTIVO</t>
+  </si>
+  <si>
+    <t>cuando el administrador intente desactivarlo nuevamente</t>
+  </si>
+  <si>
+    <t>el sistema no realiza cambios y muestra mensaje informativo: "El usuario ya se encuentra inactivo"</t>
+  </si>
+  <si>
+    <t>En caso que el usuario esté en estado INACTIVO</t>
+  </si>
+  <si>
+    <t>cuando intente iniciar sesión</t>
+  </si>
+  <si>
+    <t>el sistema rechaza el acceso, muestra mensaje: "Usuario inactivo" y no crea sesión</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1023,13 +1080,6 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1283,7 +1333,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1456,6 +1506,8 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1466,24 +1518,44 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1501,42 +1573,21 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1779,22 +1830,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="36" customHeight="1">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="68"/>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="70"/>
     </row>
     <row r="2" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="70"/>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="71"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="73"/>
       <c r="F2" s="1"/>
     </row>
     <row r="3" spans="1:6" ht="14.25" customHeight="1">
@@ -1849,7 +1900,7 @@
       <c r="D6" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="100" t="s">
+      <c r="E6" s="101" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1860,7 +1911,7 @@
       <c r="D7" s="14" t="s">
         <v>303</v>
       </c>
-      <c r="E7" s="99" t="s">
+      <c r="E7" s="67" t="s">
         <v>304</v>
       </c>
       <c r="F7" s="10"/>
@@ -3173,7 +3224,7 @@
   <sheetPr>
     <tabColor rgb="FF00FF00"/>
   </sheetPr>
-  <dimension ref="A1:L934"/>
+  <dimension ref="A1:L935"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.625" customWidth="1"/>
@@ -3190,18 +3241,18 @@
   <sheetData>
     <row r="1" spans="1:9" ht="72" customHeight="1">
       <c r="A1" s="21"/>
-      <c r="B1" s="76" t="s">
+      <c r="B1" s="96" t="s">
         <v>53</v>
       </c>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="76" t="s">
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="98"/>
+      <c r="F1" s="96" t="s">
         <v>54</v>
       </c>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="78"/>
+      <c r="G1" s="97"/>
+      <c r="H1" s="97"/>
+      <c r="I1" s="98"/>
     </row>
     <row r="2" spans="1:9" ht="45">
       <c r="A2" s="22" t="s">
@@ -3233,16 +3284,16 @@
       </c>
     </row>
     <row r="3" spans="1:9" ht="45">
-      <c r="A3" s="79" t="s">
+      <c r="A3" s="85" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="81" t="s">
+      <c r="B3" s="88" t="s">
         <v>99</v>
       </c>
-      <c r="C3" s="81" t="s">
+      <c r="C3" s="88" t="s">
         <v>142</v>
       </c>
-      <c r="D3" s="81" t="s">
+      <c r="D3" s="88" t="s">
         <v>143</v>
       </c>
       <c r="E3" s="23">
@@ -3262,10 +3313,10 @@
       </c>
     </row>
     <row r="4" spans="1:9" s="41" customFormat="1" ht="45">
-      <c r="A4" s="79"/>
-      <c r="B4" s="82"/>
-      <c r="C4" s="82"/>
-      <c r="D4" s="82"/>
+      <c r="A4" s="85"/>
+      <c r="B4" s="90"/>
+      <c r="C4" s="90"/>
+      <c r="D4" s="90"/>
       <c r="E4" s="27">
         <v>2</v>
       </c>
@@ -3283,10 +3334,10 @@
       </c>
     </row>
     <row r="5" spans="1:9" ht="30">
-      <c r="A5" s="80"/>
-      <c r="B5" s="73"/>
-      <c r="C5" s="73"/>
-      <c r="D5" s="73"/>
+      <c r="A5" s="86"/>
+      <c r="B5" s="78"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
       <c r="E5" s="23">
         <v>3</v>
       </c>
@@ -3304,10 +3355,10 @@
       </c>
     </row>
     <row r="6" spans="1:9" ht="45">
-      <c r="A6" s="80"/>
-      <c r="B6" s="73"/>
-      <c r="C6" s="73"/>
-      <c r="D6" s="73"/>
+      <c r="A6" s="86"/>
+      <c r="B6" s="78"/>
+      <c r="C6" s="78"/>
+      <c r="D6" s="78"/>
       <c r="E6" s="23">
         <v>4</v>
       </c>
@@ -3325,10 +3376,10 @@
       </c>
     </row>
     <row r="7" spans="1:9" ht="30">
-      <c r="A7" s="80"/>
-      <c r="B7" s="74"/>
-      <c r="C7" s="74"/>
-      <c r="D7" s="74"/>
+      <c r="A7" s="86"/>
+      <c r="B7" s="79"/>
+      <c r="C7" s="79"/>
+      <c r="D7" s="79"/>
       <c r="E7" s="23">
         <v>5</v>
       </c>
@@ -3357,16 +3408,16 @@
       <c r="I8" s="25"/>
     </row>
     <row r="9" spans="1:9" ht="30">
-      <c r="A9" s="79" t="s">
+      <c r="A9" s="85" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="81" t="s">
+      <c r="B9" s="88" t="s">
         <v>99</v>
       </c>
-      <c r="C9" s="81" t="s">
+      <c r="C9" s="88" t="s">
         <v>157</v>
       </c>
-      <c r="D9" s="81" t="s">
+      <c r="D9" s="88" t="s">
         <v>158</v>
       </c>
       <c r="E9" s="23">
@@ -3386,10 +3437,10 @@
       </c>
     </row>
     <row r="10" spans="1:9" s="41" customFormat="1" ht="45">
-      <c r="A10" s="79"/>
-      <c r="B10" s="82"/>
-      <c r="C10" s="82"/>
-      <c r="D10" s="82"/>
+      <c r="A10" s="85"/>
+      <c r="B10" s="90"/>
+      <c r="C10" s="90"/>
+      <c r="D10" s="90"/>
       <c r="E10" s="27">
         <v>2</v>
       </c>
@@ -3407,10 +3458,10 @@
       </c>
     </row>
     <row r="11" spans="1:9" ht="30">
-      <c r="A11" s="80"/>
-      <c r="B11" s="73"/>
-      <c r="C11" s="73"/>
-      <c r="D11" s="73"/>
+      <c r="A11" s="86"/>
+      <c r="B11" s="78"/>
+      <c r="C11" s="78"/>
+      <c r="D11" s="78"/>
       <c r="E11" s="27">
         <v>3</v>
       </c>
@@ -3478,1197 +3529,1246 @@
       <c r="H14" s="25"/>
       <c r="I14" s="25"/>
     </row>
-    <row r="15" spans="1:9">
-      <c r="A15" s="83" t="s">
+    <row r="15" spans="1:9" ht="60">
+      <c r="A15" s="91" t="s">
         <v>303</v>
       </c>
-      <c r="B15" s="81" t="s">
+      <c r="B15" s="88" t="s">
         <v>305</v>
       </c>
-      <c r="C15" s="81" t="s">
+      <c r="C15" s="88" t="s">
+        <v>306</v>
+      </c>
+      <c r="D15" s="88" t="s">
         <v>307</v>
-      </c>
-      <c r="D15" s="81" t="s">
-        <v>306</v>
       </c>
       <c r="E15" s="27">
         <v>1</v>
       </c>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="34"/>
-    </row>
-    <row r="16" spans="1:9" s="41" customFormat="1">
-      <c r="A16" s="84"/>
-      <c r="B16" s="82"/>
-      <c r="C16" s="82"/>
-      <c r="D16" s="82"/>
+      <c r="F15" s="34" t="s">
+        <v>308</v>
+      </c>
+      <c r="G15" s="34" t="s">
+        <v>312</v>
+      </c>
+      <c r="H15" s="34" t="s">
+        <v>313</v>
+      </c>
+      <c r="I15" s="34" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" s="41" customFormat="1" ht="45">
+      <c r="A16" s="92"/>
+      <c r="B16" s="90"/>
+      <c r="C16" s="90"/>
+      <c r="D16" s="90"/>
       <c r="E16" s="27">
         <v>2</v>
       </c>
-      <c r="F16" s="34"/>
-      <c r="G16" s="34"/>
-      <c r="H16" s="34"/>
-      <c r="I16" s="34"/>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="A17" s="85"/>
-      <c r="B17" s="87"/>
-      <c r="C17" s="87"/>
-      <c r="D17" s="87"/>
+      <c r="F16" s="34" t="s">
+        <v>309</v>
+      </c>
+      <c r="G16" s="34" t="s">
+        <v>315</v>
+      </c>
+      <c r="H16" s="34" t="s">
+        <v>316</v>
+      </c>
+      <c r="I16" s="34" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="30">
+      <c r="A17" s="93"/>
+      <c r="B17" s="77"/>
+      <c r="C17" s="77"/>
+      <c r="D17" s="77"/>
       <c r="E17" s="27">
         <v>3</v>
       </c>
-      <c r="F17" s="34"/>
-      <c r="G17" s="34"/>
-      <c r="H17" s="34"/>
-      <c r="I17" s="34"/>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="A18" s="86"/>
-      <c r="B18" s="88"/>
-      <c r="C18" s="88"/>
-      <c r="D18" s="88"/>
+      <c r="F17" s="34" t="s">
+        <v>188</v>
+      </c>
+      <c r="G17" s="34" t="s">
+        <v>318</v>
+      </c>
+      <c r="H17" s="34" t="s">
+        <v>319</v>
+      </c>
+      <c r="I17" s="34" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" s="66" customFormat="1" ht="30">
+      <c r="A18" s="93"/>
+      <c r="B18" s="77"/>
+      <c r="C18" s="77"/>
+      <c r="D18" s="77"/>
       <c r="E18" s="27">
         <v>4</v>
       </c>
-      <c r="F18" s="34"/>
-      <c r="G18" s="34"/>
-      <c r="H18" s="34"/>
-      <c r="I18" s="34"/>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="A19" s="25"/>
-      <c r="B19" s="25"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="25"/>
-      <c r="G19" s="25"/>
-      <c r="H19" s="25"/>
-      <c r="I19" s="25"/>
-    </row>
-    <row r="20" spans="1:9" ht="30">
-      <c r="A20" s="83" t="s">
+      <c r="F18" s="34" t="s">
+        <v>310</v>
+      </c>
+      <c r="G18" s="34" t="s">
+        <v>321</v>
+      </c>
+      <c r="H18" s="34" t="s">
+        <v>322</v>
+      </c>
+      <c r="I18" s="34" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="30">
+      <c r="A19" s="94"/>
+      <c r="B19" s="95"/>
+      <c r="C19" s="95"/>
+      <c r="D19" s="95"/>
+      <c r="E19" s="27">
+        <v>5</v>
+      </c>
+      <c r="F19" s="34" t="s">
+        <v>311</v>
+      </c>
+      <c r="G19" s="34" t="s">
+        <v>324</v>
+      </c>
+      <c r="H19" s="34" t="s">
+        <v>325</v>
+      </c>
+      <c r="I19" s="34" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="25"/>
+      <c r="B20" s="25"/>
+      <c r="C20" s="25"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="25"/>
+      <c r="G20" s="25"/>
+      <c r="H20" s="25"/>
+      <c r="I20" s="25"/>
+    </row>
+    <row r="21" spans="1:9" ht="30">
+      <c r="A21" s="91" t="s">
         <v>17</v>
       </c>
-      <c r="B20" s="81" t="s">
+      <c r="B21" s="88" t="s">
         <v>169</v>
       </c>
-      <c r="C20" s="81" t="s">
+      <c r="C21" s="88" t="s">
         <v>170</v>
       </c>
-      <c r="D20" s="81" t="s">
+      <c r="D21" s="88" t="s">
         <v>171</v>
       </c>
-      <c r="E20" s="27">
+      <c r="E21" s="27">
         <v>1</v>
       </c>
-      <c r="F20" s="34" t="s">
+      <c r="F21" s="34" t="s">
         <v>172</v>
       </c>
-      <c r="G20" s="34" t="s">
+      <c r="G21" s="34" t="s">
         <v>177</v>
       </c>
-      <c r="H20" s="34" t="s">
+      <c r="H21" s="34" t="s">
         <v>178</v>
       </c>
-      <c r="I20" s="34" t="s">
+      <c r="I21" s="34" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="30">
-      <c r="A21" s="84"/>
-      <c r="B21" s="82"/>
-      <c r="C21" s="82"/>
-      <c r="D21" s="82"/>
-      <c r="E21" s="27">
+    <row r="22" spans="1:9" ht="30">
+      <c r="A22" s="92"/>
+      <c r="B22" s="90"/>
+      <c r="C22" s="90"/>
+      <c r="D22" s="90"/>
+      <c r="E22" s="27">
         <v>2</v>
       </c>
-      <c r="F21" s="34" t="s">
+      <c r="F22" s="34" t="s">
         <v>295</v>
       </c>
-      <c r="G21" s="34" t="s">
+      <c r="G22" s="34" t="s">
         <v>296</v>
       </c>
-      <c r="H21" s="34" t="s">
+      <c r="H22" s="34" t="s">
         <v>297</v>
       </c>
-      <c r="I21" s="34" t="s">
+      <c r="I22" s="34" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="90">
-      <c r="A22" s="85"/>
-      <c r="B22" s="87"/>
-      <c r="C22" s="87"/>
-      <c r="D22" s="87"/>
-      <c r="E22" s="27">
+    <row r="23" spans="1:9" ht="90">
+      <c r="A23" s="93"/>
+      <c r="B23" s="77"/>
+      <c r="C23" s="77"/>
+      <c r="D23" s="77"/>
+      <c r="E23" s="27">
         <v>3</v>
       </c>
-      <c r="F22" s="34" t="s">
+      <c r="F23" s="34" t="s">
         <v>173</v>
       </c>
-      <c r="G22" s="34" t="s">
+      <c r="G23" s="34" t="s">
         <v>180</v>
       </c>
-      <c r="H22" s="34" t="s">
+      <c r="H23" s="34" t="s">
         <v>182</v>
       </c>
-      <c r="I22" s="34" t="s">
+      <c r="I23" s="34" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="30">
-      <c r="A23" s="86"/>
-      <c r="B23" s="88"/>
-      <c r="C23" s="88"/>
-      <c r="D23" s="88"/>
-      <c r="E23" s="27">
+    <row r="24" spans="1:9" ht="30">
+      <c r="A24" s="94"/>
+      <c r="B24" s="95"/>
+      <c r="C24" s="95"/>
+      <c r="D24" s="95"/>
+      <c r="E24" s="27">
         <v>4</v>
       </c>
-      <c r="F23" s="34" t="s">
+      <c r="F24" s="34" t="s">
         <v>174</v>
       </c>
-      <c r="G23" s="34" t="s">
+      <c r="G24" s="34" t="s">
         <v>181</v>
       </c>
-      <c r="H23" s="34" t="s">
+      <c r="H24" s="34" t="s">
         <v>183</v>
       </c>
-      <c r="I23" s="34" t="s">
+      <c r="I24" s="34" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="24" spans="1:9">
-      <c r="A24" s="25"/>
-      <c r="B24" s="25"/>
-      <c r="C24" s="25"/>
-      <c r="D24" s="25"/>
-      <c r="E24" s="26"/>
-      <c r="F24" s="25"/>
-      <c r="G24" s="25"/>
-      <c r="H24" s="25"/>
-      <c r="I24" s="25"/>
-    </row>
-    <row r="25" spans="1:9" ht="30">
-      <c r="A25" s="90" t="s">
+    <row r="25" spans="1:9">
+      <c r="A25" s="25"/>
+      <c r="B25" s="25"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="25"/>
+      <c r="H25" s="25"/>
+      <c r="I25" s="25"/>
+    </row>
+    <row r="26" spans="1:9" ht="30">
+      <c r="A26" s="87" t="s">
         <v>19</v>
       </c>
-      <c r="B25" s="81" t="s">
+      <c r="B26" s="88" t="s">
         <v>169</v>
       </c>
-      <c r="C25" s="81" t="s">
+      <c r="C26" s="88" t="s">
         <v>185</v>
       </c>
-      <c r="D25" s="81" t="s">
+      <c r="D26" s="88" t="s">
         <v>186</v>
       </c>
-      <c r="E25" s="27">
+      <c r="E26" s="27">
         <v>1</v>
       </c>
-      <c r="F25" s="34" t="s">
+      <c r="F26" s="34" t="s">
         <v>187</v>
       </c>
-      <c r="G25" s="34" t="s">
+      <c r="G26" s="34" t="s">
         <v>189</v>
-      </c>
-      <c r="H25" s="34" t="s">
-        <v>190</v>
-      </c>
-      <c r="I25" s="34" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9">
-      <c r="A26" s="73"/>
-      <c r="B26" s="73"/>
-      <c r="C26" s="73"/>
-      <c r="D26" s="73"/>
-      <c r="E26" s="27">
-        <v>2</v>
-      </c>
-      <c r="F26" s="34" t="s">
-        <v>188</v>
-      </c>
-      <c r="G26" s="34" t="s">
-        <v>193</v>
       </c>
       <c r="H26" s="34" t="s">
         <v>190</v>
       </c>
       <c r="I26" s="34" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="78"/>
+      <c r="B27" s="78"/>
+      <c r="C27" s="78"/>
+      <c r="D27" s="78"/>
+      <c r="E27" s="27">
+        <v>2</v>
+      </c>
+      <c r="F27" s="34" t="s">
+        <v>188</v>
+      </c>
+      <c r="G27" s="34" t="s">
+        <v>193</v>
+      </c>
+      <c r="H27" s="34" t="s">
+        <v>190</v>
+      </c>
+      <c r="I27" s="34" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="27" spans="1:9">
-      <c r="A27" s="25"/>
-      <c r="B27" s="25"/>
-      <c r="C27" s="25"/>
-      <c r="D27" s="25"/>
-      <c r="E27" s="26"/>
-      <c r="F27" s="25"/>
-      <c r="G27" s="25"/>
-      <c r="H27" s="25"/>
-      <c r="I27" s="25"/>
-    </row>
-    <row r="28" spans="1:9" ht="30">
-      <c r="A28" s="90" t="s">
+    <row r="28" spans="1:9">
+      <c r="A28" s="25"/>
+      <c r="B28" s="25"/>
+      <c r="C28" s="25"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="25"/>
+      <c r="G28" s="25"/>
+      <c r="H28" s="25"/>
+      <c r="I28" s="25"/>
+    </row>
+    <row r="29" spans="1:9" ht="30">
+      <c r="A29" s="87" t="s">
         <v>22</v>
       </c>
-      <c r="B28" s="81" t="s">
+      <c r="B29" s="88" t="s">
         <v>211</v>
       </c>
-      <c r="C28" s="81" t="s">
+      <c r="C29" s="88" t="s">
         <v>197</v>
       </c>
-      <c r="D28" s="81" t="s">
+      <c r="D29" s="88" t="s">
         <v>198</v>
       </c>
-      <c r="E28" s="27">
+      <c r="E29" s="27">
         <v>1</v>
       </c>
-      <c r="F28" s="34" t="s">
+      <c r="F29" s="34" t="s">
         <v>199</v>
       </c>
-      <c r="G28" s="34" t="s">
+      <c r="G29" s="34" t="s">
         <v>202</v>
       </c>
-      <c r="H28" s="34" t="s">
+      <c r="H29" s="34" t="s">
         <v>203</v>
       </c>
-      <c r="I28" s="34" t="s">
+      <c r="I29" s="34" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="30">
-      <c r="A29" s="92"/>
-      <c r="B29" s="82"/>
-      <c r="C29" s="82"/>
-      <c r="D29" s="82"/>
-      <c r="E29" s="27">
+    <row r="30" spans="1:9" ht="30">
+      <c r="A30" s="89"/>
+      <c r="B30" s="90"/>
+      <c r="C30" s="90"/>
+      <c r="D30" s="90"/>
+      <c r="E30" s="27">
         <v>2</v>
       </c>
-      <c r="F29" s="34" t="s">
+      <c r="F30" s="34" t="s">
         <v>200</v>
       </c>
-      <c r="G29" s="34" t="s">
+      <c r="G30" s="34" t="s">
         <v>205</v>
       </c>
-      <c r="H29" s="34" t="s">
+      <c r="H30" s="34" t="s">
         <v>206</v>
       </c>
-      <c r="I29" s="34" t="s">
+      <c r="I30" s="34" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="30">
-      <c r="A30" s="73"/>
-      <c r="B30" s="73"/>
-      <c r="C30" s="73"/>
-      <c r="D30" s="73"/>
-      <c r="E30" s="27">
+    <row r="31" spans="1:9" ht="30">
+      <c r="A31" s="78"/>
+      <c r="B31" s="78"/>
+      <c r="C31" s="78"/>
+      <c r="D31" s="78"/>
+      <c r="E31" s="27">
         <v>3</v>
       </c>
-      <c r="F30" s="34" t="s">
+      <c r="F31" s="34" t="s">
         <v>201</v>
       </c>
-      <c r="G30" s="34" t="s">
+      <c r="G31" s="34" t="s">
         <v>208</v>
       </c>
-      <c r="H30" s="34" t="s">
+      <c r="H31" s="34" t="s">
         <v>209</v>
       </c>
-      <c r="I30" s="34" t="s">
+      <c r="I31" s="34" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="31" spans="1:9">
-      <c r="A31" s="25"/>
-      <c r="B31" s="25"/>
-      <c r="C31" s="25"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="26"/>
-      <c r="F31" s="25"/>
-      <c r="G31" s="25"/>
-      <c r="H31" s="25"/>
-      <c r="I31" s="25"/>
-    </row>
-    <row r="32" spans="1:9" ht="30">
-      <c r="A32" s="65" t="s">
+    <row r="32" spans="1:9">
+      <c r="A32" s="25"/>
+      <c r="B32" s="25"/>
+      <c r="C32" s="25"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="25"/>
+      <c r="G32" s="25"/>
+      <c r="H32" s="25"/>
+      <c r="I32" s="25"/>
+    </row>
+    <row r="33" spans="1:9" ht="30">
+      <c r="A33" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="B32" s="64" t="s">
+      <c r="B33" s="64" t="s">
         <v>211</v>
       </c>
-      <c r="C32" s="64" t="s">
+      <c r="C33" s="64" t="s">
         <v>212</v>
       </c>
-      <c r="D32" s="64" t="s">
+      <c r="D33" s="64" t="s">
         <v>213</v>
       </c>
-      <c r="E32" s="27">
+      <c r="E33" s="27">
         <v>1</v>
       </c>
-      <c r="F32" s="34" t="s">
+      <c r="F33" s="34" t="s">
         <v>81</v>
       </c>
-      <c r="G32" s="34" t="s">
+      <c r="G33" s="34" t="s">
         <v>214</v>
       </c>
-      <c r="H32" s="34" t="s">
+      <c r="H33" s="34" t="s">
         <v>215</v>
       </c>
-      <c r="I32" s="34" t="s">
+      <c r="I33" s="34" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="33" spans="1:9">
-      <c r="A33" s="25"/>
-      <c r="B33" s="25"/>
-      <c r="C33" s="25"/>
-      <c r="D33" s="25"/>
-      <c r="E33" s="26"/>
-      <c r="F33" s="25"/>
-      <c r="G33" s="25"/>
-      <c r="H33" s="25"/>
-      <c r="I33" s="25"/>
-    </row>
-    <row r="34" spans="1:9" ht="30">
-      <c r="A34" s="65" t="s">
+    <row r="34" spans="1:9">
+      <c r="A34" s="25"/>
+      <c r="B34" s="25"/>
+      <c r="C34" s="25"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="25"/>
+      <c r="H34" s="25"/>
+      <c r="I34" s="25"/>
+    </row>
+    <row r="35" spans="1:9" ht="30">
+      <c r="A35" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="B34" s="64" t="s">
+      <c r="B35" s="64" t="s">
         <v>211</v>
       </c>
-      <c r="C34" s="64" t="s">
+      <c r="C35" s="64" t="s">
         <v>217</v>
       </c>
-      <c r="D34" s="64" t="s">
+      <c r="D35" s="64" t="s">
         <v>218</v>
       </c>
-      <c r="E34" s="27">
+      <c r="E35" s="27">
         <v>1</v>
       </c>
-      <c r="F34" s="34" t="s">
+      <c r="F35" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="G34" s="34" t="s">
+      <c r="G35" s="34" t="s">
         <v>220</v>
       </c>
-      <c r="H34" s="34" t="s">
+      <c r="H35" s="34" t="s">
         <v>221</v>
       </c>
-      <c r="I34" s="34" t="s">
+      <c r="I35" s="34" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="35" spans="1:9">
-      <c r="A35" s="25"/>
-      <c r="B35" s="25"/>
-      <c r="C35" s="25"/>
-      <c r="D35" s="25"/>
-      <c r="E35" s="26"/>
-      <c r="F35" s="25"/>
-      <c r="G35" s="25"/>
-      <c r="H35" s="25"/>
-      <c r="I35" s="25"/>
-    </row>
-    <row r="36" spans="1:9" ht="30">
-      <c r="A36" s="37" t="s">
+    <row r="36" spans="1:9">
+      <c r="A36" s="25"/>
+      <c r="B36" s="25"/>
+      <c r="C36" s="25"/>
+      <c r="D36" s="25"/>
+      <c r="E36" s="26"/>
+      <c r="F36" s="25"/>
+      <c r="G36" s="25"/>
+      <c r="H36" s="25"/>
+      <c r="I36" s="25"/>
+    </row>
+    <row r="37" spans="1:9" ht="30">
+      <c r="A37" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="B36" s="37" t="s">
+      <c r="B37" s="37" t="s">
         <v>223</v>
       </c>
-      <c r="C36" s="64" t="s">
+      <c r="C37" s="64" t="s">
         <v>224</v>
       </c>
-      <c r="D36" s="37" t="s">
+      <c r="D37" s="37" t="s">
         <v>225</v>
       </c>
-      <c r="E36" s="30">
+      <c r="E37" s="30">
         <v>1</v>
       </c>
-      <c r="F36" s="38" t="s">
+      <c r="F37" s="38" t="s">
         <v>199</v>
       </c>
-      <c r="G36" s="38" t="s">
+      <c r="G37" s="38" t="s">
         <v>226</v>
       </c>
-      <c r="H36" s="38" t="s">
+      <c r="H37" s="38" t="s">
         <v>233</v>
       </c>
-      <c r="I36" s="38" t="s">
+      <c r="I37" s="38" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="37" spans="1:9">
-      <c r="A37" s="32"/>
-      <c r="B37" s="32"/>
-      <c r="C37" s="33"/>
-      <c r="D37" s="32"/>
-      <c r="E37" s="32"/>
-      <c r="F37" s="32"/>
-      <c r="G37" s="32"/>
-      <c r="H37" s="32"/>
-      <c r="I37" s="32"/>
-    </row>
-    <row r="38" spans="1:9" ht="30">
-      <c r="A38" s="65" t="s">
+    <row r="38" spans="1:9">
+      <c r="A38" s="32"/>
+      <c r="B38" s="32"/>
+      <c r="C38" s="33"/>
+      <c r="D38" s="32"/>
+      <c r="E38" s="32"/>
+      <c r="F38" s="32"/>
+      <c r="G38" s="32"/>
+      <c r="H38" s="32"/>
+      <c r="I38" s="32"/>
+    </row>
+    <row r="39" spans="1:9" ht="30">
+      <c r="A39" s="65" t="s">
         <v>31</v>
       </c>
-      <c r="B38" s="64" t="s">
+      <c r="B39" s="64" t="s">
         <v>228</v>
       </c>
-      <c r="C38" s="64" t="s">
+      <c r="C39" s="64" t="s">
         <v>229</v>
       </c>
-      <c r="D38" s="64" t="s">
+      <c r="D39" s="64" t="s">
         <v>230</v>
       </c>
-      <c r="E38" s="27">
+      <c r="E39" s="27">
         <v>1</v>
       </c>
-      <c r="F38" s="34" t="s">
+      <c r="F39" s="34" t="s">
         <v>231</v>
       </c>
-      <c r="G38" s="34" t="s">
+      <c r="G39" s="34" t="s">
         <v>202</v>
       </c>
-      <c r="H38" s="34" t="s">
+      <c r="H39" s="34" t="s">
         <v>232</v>
       </c>
-      <c r="I38" s="34" t="s">
+      <c r="I39" s="34" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="39" spans="1:9">
-      <c r="A39" s="25"/>
-      <c r="B39" s="25"/>
-      <c r="C39" s="25"/>
-      <c r="D39" s="25"/>
-      <c r="E39" s="26"/>
-      <c r="F39" s="25"/>
-      <c r="G39" s="25"/>
-      <c r="H39" s="25"/>
-      <c r="I39" s="25"/>
-    </row>
-    <row r="40" spans="1:9" ht="30">
-      <c r="A40" s="65" t="s">
+    <row r="40" spans="1:9">
+      <c r="A40" s="25"/>
+      <c r="B40" s="25"/>
+      <c r="C40" s="25"/>
+      <c r="D40" s="25"/>
+      <c r="E40" s="26"/>
+      <c r="F40" s="25"/>
+      <c r="G40" s="25"/>
+      <c r="H40" s="25"/>
+      <c r="I40" s="25"/>
+    </row>
+    <row r="41" spans="1:9" ht="30">
+      <c r="A41" s="65" t="s">
         <v>33</v>
       </c>
-      <c r="B40" s="64" t="s">
+      <c r="B41" s="64" t="s">
         <v>228</v>
       </c>
-      <c r="C40" s="64" t="s">
+      <c r="C41" s="64" t="s">
         <v>235</v>
       </c>
-      <c r="D40" s="64" t="s">
+      <c r="D41" s="64" t="s">
         <v>236</v>
       </c>
-      <c r="E40" s="27">
+      <c r="E41" s="27">
         <v>1</v>
       </c>
-      <c r="F40" s="34" t="s">
+      <c r="F41" s="34" t="s">
         <v>237</v>
       </c>
-      <c r="G40" s="34" t="s">
+      <c r="G41" s="34" t="s">
         <v>238</v>
       </c>
-      <c r="H40" s="34" t="s">
+      <c r="H41" s="34" t="s">
         <v>239</v>
       </c>
-      <c r="I40" s="34" t="s">
+      <c r="I41" s="34" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="41" spans="1:9">
-      <c r="A41" s="25"/>
-      <c r="B41" s="25"/>
-      <c r="C41" s="39"/>
-      <c r="D41" s="25"/>
-      <c r="E41" s="26"/>
-      <c r="F41" s="25"/>
-      <c r="G41" s="25"/>
-      <c r="H41" s="25"/>
-      <c r="I41" s="25"/>
-    </row>
-    <row r="42" spans="1:9" ht="30">
-      <c r="A42" s="91" t="s">
+    <row r="42" spans="1:9">
+      <c r="A42" s="25"/>
+      <c r="B42" s="25"/>
+      <c r="C42" s="39"/>
+      <c r="D42" s="25"/>
+      <c r="E42" s="26"/>
+      <c r="F42" s="25"/>
+      <c r="G42" s="25"/>
+      <c r="H42" s="25"/>
+      <c r="I42" s="25"/>
+    </row>
+    <row r="43" spans="1:9" ht="30">
+      <c r="A43" s="74" t="s">
         <v>37</v>
       </c>
-      <c r="B42" s="89" t="s">
+      <c r="B43" s="76" t="s">
         <v>64</v>
       </c>
-      <c r="C42" s="89" t="s">
+      <c r="C43" s="76" t="s">
         <v>65</v>
       </c>
-      <c r="D42" s="89" t="s">
+      <c r="D43" s="76" t="s">
         <v>66</v>
       </c>
-      <c r="E42" s="27">
+      <c r="E43" s="27">
         <v>1</v>
       </c>
-      <c r="F42" s="24" t="s">
+      <c r="F43" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="G42" s="34" t="s">
+      <c r="G43" s="34" t="s">
         <v>68</v>
       </c>
-      <c r="H42" s="24" t="s">
+      <c r="H43" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="I42" s="24" t="s">
+      <c r="I43" s="24" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="30">
-      <c r="A43" s="73"/>
-      <c r="B43" s="73"/>
-      <c r="C43" s="73"/>
-      <c r="D43" s="73"/>
-      <c r="E43" s="27">
+    <row r="44" spans="1:9" ht="30">
+      <c r="A44" s="78"/>
+      <c r="B44" s="78"/>
+      <c r="C44" s="78"/>
+      <c r="D44" s="78"/>
+      <c r="E44" s="27">
         <v>2</v>
       </c>
-      <c r="F43" s="24" t="s">
+      <c r="F44" s="24" t="s">
         <v>71</v>
       </c>
-      <c r="G43" s="24" t="s">
+      <c r="G44" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="H43" s="24" t="s">
+      <c r="H44" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="I43" s="24" t="s">
+      <c r="I44" s="24" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="30">
-      <c r="A44" s="74"/>
-      <c r="B44" s="74"/>
-      <c r="C44" s="74"/>
-      <c r="D44" s="74"/>
-      <c r="E44" s="27">
+    <row r="45" spans="1:9" ht="30">
+      <c r="A45" s="79"/>
+      <c r="B45" s="79"/>
+      <c r="C45" s="79"/>
+      <c r="D45" s="79"/>
+      <c r="E45" s="27">
         <v>3</v>
       </c>
-      <c r="F44" s="24" t="s">
+      <c r="F45" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="G44" s="24" t="s">
+      <c r="G45" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="H44" s="24" t="s">
+      <c r="H45" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="I44" s="24" t="s">
+      <c r="I45" s="24" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="45" spans="1:9">
-      <c r="A45" s="25"/>
-      <c r="B45" s="25"/>
-      <c r="C45" s="25"/>
-      <c r="D45" s="25"/>
-      <c r="E45" s="26"/>
-      <c r="F45" s="25"/>
-      <c r="G45" s="25"/>
-      <c r="H45" s="25"/>
-      <c r="I45" s="25"/>
-    </row>
-    <row r="46" spans="1:9" ht="30">
-      <c r="A46" s="79" t="s">
+    <row r="46" spans="1:9">
+      <c r="A46" s="25"/>
+      <c r="B46" s="25"/>
+      <c r="C46" s="25"/>
+      <c r="D46" s="25"/>
+      <c r="E46" s="26"/>
+      <c r="F46" s="25"/>
+      <c r="G46" s="25"/>
+      <c r="H46" s="25"/>
+      <c r="I46" s="25"/>
+    </row>
+    <row r="47" spans="1:9" ht="30">
+      <c r="A47" s="85" t="s">
         <v>39</v>
       </c>
-      <c r="B46" s="89" t="s">
+      <c r="B47" s="76" t="s">
         <v>64</v>
       </c>
-      <c r="C46" s="89" t="s">
+      <c r="C47" s="76" t="s">
         <v>79</v>
       </c>
-      <c r="D46" s="89" t="s">
+      <c r="D47" s="76" t="s">
         <v>80</v>
       </c>
-      <c r="E46" s="27">
+      <c r="E47" s="27">
         <v>1</v>
       </c>
-      <c r="F46" s="24" t="s">
+      <c r="F47" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="G46" s="24" t="s">
+      <c r="G47" s="24" t="s">
         <v>82</v>
       </c>
-      <c r="H46" s="24" t="s">
+      <c r="H47" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="I46" s="24" t="s">
+      <c r="I47" s="24" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="30">
-      <c r="A47" s="80"/>
-      <c r="B47" s="74"/>
-      <c r="C47" s="74"/>
-      <c r="D47" s="74"/>
-      <c r="E47" s="27">
+    <row r="48" spans="1:9" ht="30">
+      <c r="A48" s="86"/>
+      <c r="B48" s="79"/>
+      <c r="C48" s="79"/>
+      <c r="D48" s="79"/>
+      <c r="E48" s="27">
         <v>2</v>
       </c>
-      <c r="F47" s="24" t="s">
+      <c r="F48" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="G47" s="24" t="s">
+      <c r="G48" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="H47" s="24" t="s">
+      <c r="H48" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="I47" s="24" t="s">
+      <c r="I48" s="24" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="48" spans="1:9">
-      <c r="A48" s="25"/>
-      <c r="B48" s="25"/>
-      <c r="C48" s="25"/>
-      <c r="D48" s="25"/>
-      <c r="E48" s="26"/>
-      <c r="F48" s="25"/>
-      <c r="G48" s="25"/>
-      <c r="H48" s="25"/>
-      <c r="I48" s="25"/>
-    </row>
-    <row r="49" spans="1:9" ht="30">
-      <c r="A49" s="79" t="s">
+    <row r="49" spans="1:9">
+      <c r="A49" s="25"/>
+      <c r="B49" s="25"/>
+      <c r="C49" s="25"/>
+      <c r="D49" s="25"/>
+      <c r="E49" s="26"/>
+      <c r="F49" s="25"/>
+      <c r="G49" s="25"/>
+      <c r="H49" s="25"/>
+      <c r="I49" s="25"/>
+    </row>
+    <row r="50" spans="1:9" ht="30">
+      <c r="A50" s="85" t="s">
         <v>41</v>
       </c>
-      <c r="B49" s="89" t="s">
+      <c r="B50" s="76" t="s">
         <v>64</v>
       </c>
-      <c r="C49" s="89" t="s">
+      <c r="C50" s="76" t="s">
         <v>89</v>
       </c>
-      <c r="D49" s="89" t="s">
+      <c r="D50" s="76" t="s">
         <v>90</v>
       </c>
-      <c r="E49" s="27">
+      <c r="E50" s="27">
         <v>1</v>
       </c>
-      <c r="F49" s="24" t="s">
+      <c r="F50" s="24" t="s">
         <v>91</v>
       </c>
-      <c r="G49" s="24" t="s">
+      <c r="G50" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="H49" s="24" t="s">
+      <c r="H50" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="I49" s="24" t="s">
+      <c r="I50" s="24" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="50" spans="1:9">
-      <c r="A50" s="80"/>
-      <c r="B50" s="74"/>
-      <c r="C50" s="74"/>
-      <c r="D50" s="74"/>
-      <c r="E50" s="27">
+    <row r="51" spans="1:9">
+      <c r="A51" s="86"/>
+      <c r="B51" s="79"/>
+      <c r="C51" s="79"/>
+      <c r="D51" s="79"/>
+      <c r="E51" s="27">
         <v>2</v>
       </c>
-      <c r="F50" s="24" t="s">
+      <c r="F51" s="24" t="s">
         <v>95</v>
       </c>
-      <c r="G50" s="24" t="s">
+      <c r="G51" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="H50" s="24" t="s">
+      <c r="H51" s="24" t="s">
         <v>97</v>
       </c>
-      <c r="I50" s="24" t="s">
+      <c r="I51" s="24" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="51" spans="1:9">
-      <c r="A51" s="25"/>
-      <c r="B51" s="25"/>
-      <c r="C51" s="25"/>
-      <c r="D51" s="25"/>
-      <c r="E51" s="26"/>
-      <c r="F51" s="25"/>
-      <c r="G51" s="25"/>
-      <c r="H51" s="25"/>
-      <c r="I51" s="25"/>
-    </row>
-    <row r="52" spans="1:9" ht="30">
-      <c r="A52" s="79" t="s">
+    <row r="52" spans="1:9">
+      <c r="A52" s="25"/>
+      <c r="B52" s="25"/>
+      <c r="C52" s="25"/>
+      <c r="D52" s="25"/>
+      <c r="E52" s="26"/>
+      <c r="F52" s="25"/>
+      <c r="G52" s="25"/>
+      <c r="H52" s="25"/>
+      <c r="I52" s="25"/>
+    </row>
+    <row r="53" spans="1:9" ht="30">
+      <c r="A53" s="85" t="s">
         <v>45</v>
       </c>
-      <c r="B52" s="89" t="s">
+      <c r="B53" s="76" t="s">
         <v>99</v>
       </c>
-      <c r="C52" s="89" t="s">
+      <c r="C53" s="76" t="s">
         <v>100</v>
       </c>
-      <c r="D52" s="89" t="s">
+      <c r="D53" s="76" t="s">
         <v>101</v>
       </c>
-      <c r="E52" s="27">
+      <c r="E53" s="27">
         <v>1</v>
       </c>
-      <c r="F52" s="24" t="s">
+      <c r="F53" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="G52" s="24" t="s">
+      <c r="G53" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="H52" s="24" t="s">
+      <c r="H53" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="I52" s="24" t="s">
+      <c r="I53" s="24" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="30">
-      <c r="A53" s="80"/>
-      <c r="B53" s="73"/>
-      <c r="C53" s="73"/>
-      <c r="D53" s="73"/>
-      <c r="E53" s="27">
+    <row r="54" spans="1:9" ht="30">
+      <c r="A54" s="86"/>
+      <c r="B54" s="78"/>
+      <c r="C54" s="78"/>
+      <c r="D54" s="78"/>
+      <c r="E54" s="27">
         <v>2</v>
       </c>
-      <c r="F53" s="24" t="s">
+      <c r="F54" s="24" t="s">
         <v>106</v>
       </c>
-      <c r="G53" s="24" t="s">
+      <c r="G54" s="24" t="s">
         <v>107</v>
       </c>
-      <c r="H53" s="24" t="s">
+      <c r="H54" s="24" t="s">
         <v>108</v>
       </c>
-      <c r="I53" s="24" t="s">
+      <c r="I54" s="24" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="54" spans="1:9">
-      <c r="A54" s="80"/>
-      <c r="B54" s="74"/>
-      <c r="C54" s="74"/>
-      <c r="D54" s="74"/>
-      <c r="E54" s="27">
+    <row r="55" spans="1:9">
+      <c r="A55" s="86"/>
+      <c r="B55" s="79"/>
+      <c r="C55" s="79"/>
+      <c r="D55" s="79"/>
+      <c r="E55" s="27">
         <v>3</v>
       </c>
-      <c r="F54" s="24" t="s">
+      <c r="F55" s="24" t="s">
         <v>110</v>
       </c>
-      <c r="G54" s="24" t="s">
+      <c r="G55" s="24" t="s">
         <v>111</v>
       </c>
-      <c r="H54" s="24" t="s">
+      <c r="H55" s="24" t="s">
         <v>112</v>
       </c>
-      <c r="I54" s="24" t="s">
+      <c r="I55" s="24" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="55" spans="1:9">
-      <c r="A55" s="25"/>
-      <c r="B55" s="25"/>
-      <c r="C55" s="25"/>
-      <c r="D55" s="25"/>
-      <c r="E55" s="26"/>
-      <c r="F55" s="25"/>
-      <c r="G55" s="25"/>
-      <c r="H55" s="25"/>
-      <c r="I55" s="25"/>
-    </row>
-    <row r="56" spans="1:9" ht="45">
-      <c r="A56" s="62" t="s">
+    <row r="56" spans="1:9">
+      <c r="A56" s="25"/>
+      <c r="B56" s="25"/>
+      <c r="C56" s="25"/>
+      <c r="D56" s="25"/>
+      <c r="E56" s="26"/>
+      <c r="F56" s="25"/>
+      <c r="G56" s="25"/>
+      <c r="H56" s="25"/>
+      <c r="I56" s="25"/>
+    </row>
+    <row r="57" spans="1:9" ht="45">
+      <c r="A57" s="62" t="s">
         <v>47</v>
       </c>
-      <c r="B56" s="24" t="s">
+      <c r="B57" s="24" t="s">
         <v>99</v>
       </c>
-      <c r="C56" s="24" t="s">
+      <c r="C57" s="24" t="s">
         <v>114</v>
       </c>
-      <c r="D56" s="24" t="s">
+      <c r="D57" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="E56" s="27">
+      <c r="E57" s="27">
         <v>1</v>
       </c>
-      <c r="F56" s="24" t="s">
+      <c r="F57" s="24" t="s">
         <v>116</v>
       </c>
-      <c r="G56" s="24" t="s">
+      <c r="G57" s="24" t="s">
         <v>117</v>
       </c>
-      <c r="H56" s="24" t="s">
+      <c r="H57" s="24" t="s">
         <v>118</v>
       </c>
-      <c r="I56" s="24" t="s">
+      <c r="I57" s="24" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="57" spans="1:9">
-      <c r="A57" s="25"/>
-      <c r="B57" s="25"/>
-      <c r="C57" s="25"/>
-      <c r="D57" s="25"/>
-      <c r="E57" s="26"/>
-      <c r="F57" s="25"/>
-      <c r="G57" s="25"/>
-      <c r="H57" s="25"/>
-      <c r="I57" s="25"/>
-    </row>
-    <row r="58" spans="1:9" s="41" customFormat="1" ht="30">
-      <c r="A58" s="91" t="s">
+    <row r="58" spans="1:9">
+      <c r="A58" s="25"/>
+      <c r="B58" s="25"/>
+      <c r="C58" s="25"/>
+      <c r="D58" s="25"/>
+      <c r="E58" s="26"/>
+      <c r="F58" s="25"/>
+      <c r="G58" s="25"/>
+      <c r="H58" s="25"/>
+      <c r="I58" s="25"/>
+    </row>
+    <row r="59" spans="1:9" s="41" customFormat="1" ht="30">
+      <c r="A59" s="74" t="s">
         <v>51</v>
       </c>
-      <c r="B58" s="89" t="s">
+      <c r="B59" s="76" t="s">
         <v>99</v>
       </c>
-      <c r="C58" s="89" t="s">
+      <c r="C59" s="76" t="s">
         <v>120</v>
       </c>
-      <c r="D58" s="89" t="s">
+      <c r="D59" s="76" t="s">
         <v>121</v>
       </c>
-      <c r="E58" s="27">
+      <c r="E59" s="27">
         <v>1</v>
       </c>
-      <c r="F58" s="24" t="s">
+      <c r="F59" s="24" t="s">
         <v>122</v>
       </c>
-      <c r="G58" s="24" t="s">
+      <c r="G59" s="24" t="s">
         <v>123</v>
       </c>
-      <c r="H58" s="24" t="s">
+      <c r="H59" s="24" t="s">
         <v>124</v>
       </c>
-      <c r="I58" s="24" t="s">
+      <c r="I59" s="24" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="30">
-      <c r="A59" s="73"/>
-      <c r="B59" s="73"/>
-      <c r="C59" s="73"/>
-      <c r="D59" s="73"/>
-      <c r="E59" s="27">
+    <row r="60" spans="1:9" ht="30">
+      <c r="A60" s="78"/>
+      <c r="B60" s="78"/>
+      <c r="C60" s="78"/>
+      <c r="D60" s="78"/>
+      <c r="E60" s="27">
         <v>2</v>
       </c>
-      <c r="F59" s="24" t="s">
+      <c r="F60" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="G59" s="24" t="s">
+      <c r="G60" s="24" t="s">
         <v>127</v>
       </c>
-      <c r="H59" s="24" t="s">
+      <c r="H60" s="24" t="s">
         <v>128</v>
       </c>
-      <c r="I59" s="24" t="s">
+      <c r="I60" s="24" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="60" spans="1:9">
-      <c r="A60" s="74"/>
-      <c r="B60" s="74"/>
-      <c r="C60" s="74"/>
-      <c r="D60" s="74"/>
-      <c r="E60" s="27">
+    <row r="61" spans="1:9">
+      <c r="A61" s="79"/>
+      <c r="B61" s="79"/>
+      <c r="C61" s="79"/>
+      <c r="D61" s="79"/>
+      <c r="E61" s="27">
         <v>3</v>
       </c>
-      <c r="F60" s="24" t="s">
+      <c r="F61" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="G60" s="24" t="s">
+      <c r="G61" s="24" t="s">
         <v>131</v>
       </c>
-      <c r="H60" s="24" t="s">
+      <c r="H61" s="24" t="s">
         <v>132</v>
       </c>
-      <c r="I60" s="24" t="s">
+      <c r="I61" s="24" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="61" spans="1:9">
-      <c r="A61" s="25"/>
-      <c r="B61" s="25"/>
-      <c r="C61" s="25"/>
-      <c r="D61" s="25"/>
-      <c r="E61" s="26"/>
-      <c r="F61" s="25"/>
-      <c r="G61" s="25"/>
-      <c r="H61" s="25"/>
-      <c r="I61" s="25"/>
-    </row>
-    <row r="62" spans="1:9" ht="30">
-      <c r="A62" s="93" t="s">
+    <row r="62" spans="1:9">
+      <c r="A62" s="25"/>
+      <c r="B62" s="25"/>
+      <c r="C62" s="25"/>
+      <c r="D62" s="25"/>
+      <c r="E62" s="26"/>
+      <c r="F62" s="25"/>
+      <c r="G62" s="25"/>
+      <c r="H62" s="25"/>
+      <c r="I62" s="25"/>
+    </row>
+    <row r="63" spans="1:9" ht="30">
+      <c r="A63" s="80" t="s">
         <v>243</v>
       </c>
-      <c r="B62" s="96" t="s">
+      <c r="B63" s="83" t="s">
         <v>99</v>
       </c>
-      <c r="C62" s="93" t="s">
+      <c r="C63" s="80" t="s">
         <v>249</v>
       </c>
-      <c r="D62" s="93" t="s">
+      <c r="D63" s="80" t="s">
         <v>250</v>
       </c>
-      <c r="E62" s="42">
+      <c r="E63" s="42">
         <v>1</v>
       </c>
-      <c r="F62" s="43" t="s">
+      <c r="F63" s="43" t="s">
         <v>285</v>
       </c>
-      <c r="G62" s="43" t="s">
+      <c r="G63" s="43" t="s">
         <v>252</v>
       </c>
-      <c r="H62" s="43" t="s">
+      <c r="H63" s="43" t="s">
         <v>300</v>
       </c>
-      <c r="I62" s="43" t="s">
+      <c r="I63" s="43" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="30">
-      <c r="A63" s="94"/>
-      <c r="B63" s="97"/>
-      <c r="C63" s="94"/>
-      <c r="D63" s="94"/>
-      <c r="E63" s="42">
+    <row r="64" spans="1:9" ht="30">
+      <c r="A64" s="81"/>
+      <c r="B64" s="84"/>
+      <c r="C64" s="81"/>
+      <c r="D64" s="81"/>
+      <c r="E64" s="42">
         <v>2</v>
       </c>
-      <c r="F63" s="43" t="s">
+      <c r="F64" s="43" t="s">
         <v>299</v>
       </c>
-      <c r="G63" s="43" t="s">
+      <c r="G64" s="43" t="s">
         <v>176</v>
       </c>
-      <c r="H63" s="43" t="s">
+      <c r="H64" s="43" t="s">
         <v>302</v>
       </c>
-      <c r="I63" s="43" t="s">
+      <c r="I64" s="43" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="30">
-      <c r="A64" s="95"/>
-      <c r="B64" s="95"/>
-      <c r="C64" s="95"/>
-      <c r="D64" s="95"/>
-      <c r="E64" s="42">
+    <row r="65" spans="1:9" ht="30">
+      <c r="A65" s="82"/>
+      <c r="B65" s="82"/>
+      <c r="C65" s="82"/>
+      <c r="D65" s="82"/>
+      <c r="E65" s="42">
         <v>3</v>
       </c>
-      <c r="F64" s="43" t="s">
+      <c r="F65" s="43" t="s">
         <v>251</v>
       </c>
-      <c r="G64" s="43" t="s">
+      <c r="G65" s="43" t="s">
         <v>254</v>
       </c>
-      <c r="H64" s="43" t="s">
+      <c r="H65" s="43" t="s">
         <v>255</v>
       </c>
-      <c r="I64" s="43" t="s">
+      <c r="I65" s="43" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="65" spans="1:9">
-      <c r="A65" s="25"/>
-      <c r="B65" s="25"/>
-      <c r="C65" s="25"/>
-      <c r="D65" s="25"/>
-      <c r="E65" s="26"/>
-      <c r="F65" s="25"/>
-      <c r="G65" s="25"/>
-      <c r="H65" s="25"/>
-      <c r="I65" s="25"/>
-    </row>
-    <row r="66" spans="1:9" ht="30">
-      <c r="A66" s="59" t="s">
+    <row r="66" spans="1:9">
+      <c r="A66" s="25"/>
+      <c r="B66" s="25"/>
+      <c r="C66" s="25"/>
+      <c r="D66" s="25"/>
+      <c r="E66" s="26"/>
+      <c r="F66" s="25"/>
+      <c r="G66" s="25"/>
+      <c r="H66" s="25"/>
+      <c r="I66" s="25"/>
+    </row>
+    <row r="67" spans="1:9" ht="30">
+      <c r="A67" s="59" t="s">
         <v>245</v>
       </c>
-      <c r="B66" s="60" t="s">
+      <c r="B67" s="60" t="s">
         <v>99</v>
       </c>
-      <c r="C66" s="59" t="s">
+      <c r="C67" s="59" t="s">
         <v>257</v>
       </c>
-      <c r="D66" s="59" t="s">
+      <c r="D67" s="59" t="s">
         <v>258</v>
       </c>
-      <c r="E66" s="42">
+      <c r="E67" s="42">
         <v>1</v>
       </c>
-      <c r="F66" s="43" t="s">
+      <c r="F67" s="43" t="s">
         <v>264</v>
       </c>
-      <c r="G66" s="43" t="s">
+      <c r="G67" s="43" t="s">
         <v>259</v>
       </c>
-      <c r="H66" s="43" t="s">
+      <c r="H67" s="43" t="s">
         <v>260</v>
       </c>
-      <c r="I66" s="43" t="s">
+      <c r="I67" s="43" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="67" spans="1:9">
-      <c r="A67" s="25"/>
-      <c r="B67" s="25"/>
-      <c r="C67" s="25"/>
-      <c r="D67" s="25"/>
-      <c r="E67" s="26"/>
-      <c r="F67" s="25"/>
-      <c r="G67" s="25"/>
-      <c r="H67" s="25"/>
-      <c r="I67" s="25"/>
-    </row>
-    <row r="68" spans="1:9" ht="30">
-      <c r="A68" s="59" t="s">
+    <row r="68" spans="1:9">
+      <c r="A68" s="25"/>
+      <c r="B68" s="25"/>
+      <c r="C68" s="25"/>
+      <c r="D68" s="25"/>
+      <c r="E68" s="26"/>
+      <c r="F68" s="25"/>
+      <c r="G68" s="25"/>
+      <c r="H68" s="25"/>
+      <c r="I68" s="25"/>
+    </row>
+    <row r="69" spans="1:9" ht="30">
+      <c r="A69" s="59" t="s">
         <v>247</v>
       </c>
-      <c r="B68" s="60" t="s">
+      <c r="B69" s="60" t="s">
         <v>99</v>
       </c>
-      <c r="C68" s="59" t="s">
+      <c r="C69" s="59" t="s">
         <v>262</v>
       </c>
-      <c r="D68" s="59" t="s">
+      <c r="D69" s="59" t="s">
         <v>263</v>
       </c>
-      <c r="E68" s="42">
+      <c r="E69" s="42">
         <v>1</v>
       </c>
-      <c r="F68" s="43" t="s">
+      <c r="F69" s="43" t="s">
         <v>265</v>
       </c>
-      <c r="G68" s="43" t="s">
+      <c r="G69" s="43" t="s">
         <v>176</v>
       </c>
-      <c r="H68" s="43" t="s">
+      <c r="H69" s="43" t="s">
         <v>266</v>
       </c>
-      <c r="I68" s="43" t="s">
+      <c r="I69" s="43" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="69" spans="1:9">
-      <c r="A69" s="25"/>
-      <c r="B69" s="25"/>
-      <c r="C69" s="25"/>
-      <c r="D69" s="25"/>
-      <c r="E69" s="26"/>
-      <c r="F69" s="25"/>
-      <c r="G69" s="25"/>
-      <c r="H69" s="25"/>
-      <c r="I69" s="25"/>
-    </row>
-    <row r="70" spans="1:9" ht="30">
-      <c r="A70" s="61" t="s">
+    <row r="70" spans="1:9">
+      <c r="A70" s="25"/>
+      <c r="B70" s="25"/>
+      <c r="C70" s="25"/>
+      <c r="D70" s="25"/>
+      <c r="E70" s="26"/>
+      <c r="F70" s="25"/>
+      <c r="G70" s="25"/>
+      <c r="H70" s="25"/>
+      <c r="I70" s="25"/>
+    </row>
+    <row r="71" spans="1:9" ht="30">
+      <c r="A71" s="61" t="s">
         <v>267</v>
       </c>
-      <c r="B70" s="58" t="s">
+      <c r="B71" s="58" t="s">
         <v>99</v>
       </c>
-      <c r="C70" s="58" t="s">
+      <c r="C71" s="58" t="s">
         <v>271</v>
       </c>
-      <c r="D70" s="58" t="s">
+      <c r="D71" s="58" t="s">
         <v>272</v>
       </c>
-      <c r="E70" s="27">
+      <c r="E71" s="27">
         <v>1</v>
       </c>
-      <c r="F70" s="24" t="s">
+      <c r="F71" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="G70" s="24" t="s">
+      <c r="G71" s="24" t="s">
         <v>273</v>
       </c>
-      <c r="H70" s="24" t="s">
+      <c r="H71" s="24" t="s">
         <v>274</v>
       </c>
-      <c r="I70" s="24" t="s">
+      <c r="I71" s="24" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="71" spans="1:9">
-      <c r="A71" s="25"/>
-      <c r="B71" s="25"/>
-      <c r="C71" s="25"/>
-      <c r="D71" s="25"/>
-      <c r="E71" s="26"/>
-      <c r="F71" s="25"/>
-      <c r="G71" s="25"/>
-      <c r="H71" s="25"/>
-      <c r="I71" s="25"/>
-    </row>
-    <row r="72" spans="1:9" ht="30">
-      <c r="A72" s="91" t="s">
+    <row r="72" spans="1:9">
+      <c r="A72" s="25"/>
+      <c r="B72" s="25"/>
+      <c r="C72" s="25"/>
+      <c r="D72" s="25"/>
+      <c r="E72" s="26"/>
+      <c r="F72" s="25"/>
+      <c r="G72" s="25"/>
+      <c r="H72" s="25"/>
+      <c r="I72" s="25"/>
+    </row>
+    <row r="73" spans="1:9" ht="30">
+      <c r="A73" s="74" t="s">
         <v>269</v>
       </c>
-      <c r="B72" s="89" t="s">
+      <c r="B73" s="76" t="s">
         <v>99</v>
       </c>
-      <c r="C72" s="89" t="s">
+      <c r="C73" s="76" t="s">
         <v>276</v>
       </c>
-      <c r="D72" s="89" t="s">
+      <c r="D73" s="76" t="s">
         <v>277</v>
       </c>
-      <c r="E72" s="27">
+      <c r="E73" s="27">
         <v>1</v>
       </c>
-      <c r="F72" s="24" t="s">
+      <c r="F73" s="24" t="s">
         <v>278</v>
       </c>
-      <c r="G72" s="24" t="s">
+      <c r="G73" s="24" t="s">
         <v>280</v>
-      </c>
-      <c r="H72" s="24" t="s">
-        <v>281</v>
-      </c>
-      <c r="I72" s="24" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" ht="30">
-      <c r="A73" s="98"/>
-      <c r="B73" s="87"/>
-      <c r="C73" s="87"/>
-      <c r="D73" s="87"/>
-      <c r="E73" s="27">
-        <v>2</v>
-      </c>
-      <c r="F73" s="24" t="s">
-        <v>279</v>
-      </c>
-      <c r="G73" s="24" t="s">
-        <v>283</v>
       </c>
       <c r="H73" s="24" t="s">
         <v>281</v>
       </c>
       <c r="I73" s="24" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" ht="30">
+      <c r="A74" s="75"/>
+      <c r="B74" s="77"/>
+      <c r="C74" s="77"/>
+      <c r="D74" s="77"/>
+      <c r="E74" s="27">
+        <v>2</v>
+      </c>
+      <c r="F74" s="24" t="s">
+        <v>279</v>
+      </c>
+      <c r="G74" s="24" t="s">
+        <v>283</v>
+      </c>
+      <c r="H74" s="24" t="s">
+        <v>281</v>
+      </c>
+      <c r="I74" s="24" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="74" spans="1:9">
-      <c r="A74" s="25"/>
-      <c r="B74" s="25"/>
-      <c r="C74" s="25"/>
-      <c r="D74" s="25"/>
-      <c r="E74" s="26"/>
-      <c r="F74" s="25"/>
-      <c r="G74" s="25"/>
-      <c r="H74" s="25"/>
-      <c r="I74" s="25"/>
-    </row>
-    <row r="75" spans="1:9" ht="14.25">
-      <c r="A75" s="28"/>
-      <c r="E75" s="28"/>
+    <row r="75" spans="1:9">
+      <c r="A75" s="25"/>
+      <c r="B75" s="25"/>
+      <c r="C75" s="25"/>
+      <c r="D75" s="25"/>
+      <c r="E75" s="26"/>
+      <c r="F75" s="25"/>
+      <c r="G75" s="25"/>
+      <c r="H75" s="25"/>
+      <c r="I75" s="25"/>
     </row>
     <row r="76" spans="1:9" ht="14.25">
       <c r="A76" s="28"/>
@@ -4717,11 +4817,11 @@
     <row r="87" spans="1:8" ht="14.25">
       <c r="A87" s="28"/>
       <c r="E87" s="28"/>
-      <c r="H87" s="63"/>
     </row>
     <row r="88" spans="1:8" ht="14.25">
       <c r="A88" s="28"/>
       <c r="E88" s="28"/>
+      <c r="H88" s="63"/>
     </row>
     <row r="89" spans="1:8" ht="14.25">
       <c r="A89" s="28"/>
@@ -4895,7 +4995,7 @@
       <c r="A131" s="28"/>
       <c r="E131" s="28"/>
     </row>
-    <row r="132" spans="1:5" ht="14.25" customHeight="1">
+    <row r="132" spans="1:5" ht="14.25">
       <c r="A132" s="28"/>
       <c r="E132" s="28"/>
     </row>
@@ -5227,7 +5327,10 @@
       <c r="A214" s="28"/>
       <c r="E214" s="28"/>
     </row>
-    <row r="215" spans="1:5" ht="14.25" customHeight="1"/>
+    <row r="215" spans="1:5" ht="14.25" customHeight="1">
+      <c r="A215" s="28"/>
+      <c r="E215" s="28"/>
+    </row>
     <row r="216" spans="1:5" ht="14.25" customHeight="1"/>
     <row r="217" spans="1:5" ht="14.25" customHeight="1"/>
     <row r="218" spans="1:5" ht="14.25" customHeight="1"/>
@@ -5246,10 +5349,7 @@
     <row r="231" spans="1:5" ht="14.25" customHeight="1"/>
     <row r="232" spans="1:5" ht="14.25" customHeight="1"/>
     <row r="233" spans="1:5" ht="14.25" customHeight="1"/>
-    <row r="234" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A234" s="28"/>
-      <c r="E234" s="28"/>
-    </row>
+    <row r="234" spans="1:5" ht="14.25" customHeight="1"/>
     <row r="235" spans="1:5" ht="14.25" customHeight="1">
       <c r="A235" s="28"/>
       <c r="E235" s="28"/>
@@ -5388,67 +5488,58 @@
     </row>
     <row r="269" spans="1:9" ht="14.25" customHeight="1">
       <c r="A269" s="28"/>
-      <c r="D269" s="29"/>
-      <c r="E269" s="76" t="s">
-        <v>53</v>
-      </c>
-      <c r="F269" s="77"/>
-      <c r="G269" s="77"/>
-      <c r="H269" s="78"/>
-      <c r="I269" s="55" t="s">
-        <v>54</v>
-      </c>
+      <c r="E269" s="28"/>
     </row>
     <row r="270" spans="1:9" ht="14.25" customHeight="1">
       <c r="A270" s="28"/>
-      <c r="D270" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="E270" s="22" t="s">
-        <v>56</v>
-      </c>
-      <c r="F270" s="22" t="s">
-        <v>57</v>
-      </c>
-      <c r="G270" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="H270" s="22" t="s">
-        <v>59</v>
-      </c>
-      <c r="I270" s="22" t="s">
-        <v>60</v>
+      <c r="D270" s="29"/>
+      <c r="E270" s="96" t="s">
+        <v>53</v>
+      </c>
+      <c r="F270" s="97"/>
+      <c r="G270" s="97"/>
+      <c r="H270" s="98"/>
+      <c r="I270" s="55" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="271" spans="1:9" ht="14.25" customHeight="1">
       <c r="A271" s="28"/>
-      <c r="D271" s="75" t="s">
-        <v>134</v>
-      </c>
-      <c r="E271" s="75" t="s">
-        <v>135</v>
-      </c>
-      <c r="F271" s="72" t="s">
-        <v>136</v>
-      </c>
-      <c r="G271" s="75" t="s">
-        <v>137</v>
-      </c>
-      <c r="H271" s="30">
-        <v>1</v>
-      </c>
-      <c r="I271" s="31" t="s">
-        <v>138</v>
+      <c r="D271" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="E271" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="F271" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="G271" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="H271" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="I271" s="22" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="272" spans="1:9" ht="14.25" customHeight="1">
       <c r="A272" s="28"/>
-      <c r="D272" s="73"/>
-      <c r="E272" s="73"/>
-      <c r="F272" s="73"/>
-      <c r="G272" s="73"/>
+      <c r="D272" s="100" t="s">
+        <v>134</v>
+      </c>
+      <c r="E272" s="100" t="s">
+        <v>135</v>
+      </c>
+      <c r="F272" s="99" t="s">
+        <v>136</v>
+      </c>
+      <c r="G272" s="100" t="s">
+        <v>137</v>
+      </c>
       <c r="H272" s="30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I272" s="31" t="s">
         <v>138</v>
@@ -5456,12 +5547,12 @@
     </row>
     <row r="273" spans="1:9" ht="14.25" customHeight="1">
       <c r="A273" s="28"/>
-      <c r="D273" s="73"/>
-      <c r="E273" s="73"/>
-      <c r="F273" s="73"/>
-      <c r="G273" s="73"/>
+      <c r="D273" s="78"/>
+      <c r="E273" s="78"/>
+      <c r="F273" s="78"/>
+      <c r="G273" s="78"/>
       <c r="H273" s="30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I273" s="31" t="s">
         <v>138</v>
@@ -5469,12 +5560,12 @@
     </row>
     <row r="274" spans="1:9" ht="14.25" customHeight="1">
       <c r="A274" s="28"/>
-      <c r="D274" s="74"/>
-      <c r="E274" s="74"/>
-      <c r="F274" s="74"/>
-      <c r="G274" s="74"/>
+      <c r="D274" s="78"/>
+      <c r="E274" s="78"/>
+      <c r="F274" s="78"/>
+      <c r="G274" s="78"/>
       <c r="H274" s="30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I274" s="31" t="s">
         <v>138</v>
@@ -5482,42 +5573,42 @@
     </row>
     <row r="275" spans="1:9" ht="14.25" customHeight="1">
       <c r="A275" s="28"/>
-      <c r="D275" s="32"/>
-      <c r="E275" s="32"/>
-      <c r="F275" s="33"/>
-      <c r="G275" s="32"/>
-      <c r="H275" s="32"/>
-      <c r="I275" s="32"/>
+      <c r="D275" s="79"/>
+      <c r="E275" s="79"/>
+      <c r="F275" s="79"/>
+      <c r="G275" s="79"/>
+      <c r="H275" s="30">
+        <v>4</v>
+      </c>
+      <c r="I275" s="31" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="276" spans="1:9" ht="14.25" customHeight="1">
       <c r="A276" s="28"/>
-      <c r="D276" s="75" t="s">
-        <v>134</v>
-      </c>
-      <c r="E276" s="75" t="s">
-        <v>135</v>
-      </c>
-      <c r="F276" s="72" t="s">
-        <v>136</v>
-      </c>
-      <c r="G276" s="75" t="s">
-        <v>137</v>
-      </c>
-      <c r="H276" s="30">
-        <v>1</v>
-      </c>
-      <c r="I276" s="31" t="s">
-        <v>138</v>
-      </c>
+      <c r="D276" s="32"/>
+      <c r="E276" s="32"/>
+      <c r="F276" s="33"/>
+      <c r="G276" s="32"/>
+      <c r="H276" s="32"/>
+      <c r="I276" s="32"/>
     </row>
     <row r="277" spans="1:9" ht="14.25" customHeight="1">
       <c r="A277" s="28"/>
-      <c r="D277" s="73"/>
-      <c r="E277" s="73"/>
-      <c r="F277" s="73"/>
-      <c r="G277" s="73"/>
+      <c r="D277" s="100" t="s">
+        <v>134</v>
+      </c>
+      <c r="E277" s="100" t="s">
+        <v>135</v>
+      </c>
+      <c r="F277" s="99" t="s">
+        <v>136</v>
+      </c>
+      <c r="G277" s="100" t="s">
+        <v>137</v>
+      </c>
       <c r="H277" s="30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I277" s="31" t="s">
         <v>138</v>
@@ -5525,12 +5616,12 @@
     </row>
     <row r="278" spans="1:9" ht="14.25" customHeight="1">
       <c r="A278" s="28"/>
-      <c r="D278" s="73"/>
-      <c r="E278" s="73"/>
-      <c r="F278" s="73"/>
-      <c r="G278" s="73"/>
+      <c r="D278" s="78"/>
+      <c r="E278" s="78"/>
+      <c r="F278" s="78"/>
+      <c r="G278" s="78"/>
       <c r="H278" s="30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I278" s="31" t="s">
         <v>138</v>
@@ -5538,12 +5629,12 @@
     </row>
     <row r="279" spans="1:9" ht="14.25" customHeight="1">
       <c r="A279" s="28"/>
-      <c r="D279" s="74"/>
-      <c r="E279" s="74"/>
-      <c r="F279" s="74"/>
-      <c r="G279" s="74"/>
+      <c r="D279" s="78"/>
+      <c r="E279" s="78"/>
+      <c r="F279" s="78"/>
+      <c r="G279" s="78"/>
       <c r="H279" s="30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I279" s="31" t="s">
         <v>138</v>
@@ -5551,42 +5642,42 @@
     </row>
     <row r="280" spans="1:9" ht="14.25" customHeight="1">
       <c r="A280" s="28"/>
-      <c r="D280" s="32"/>
-      <c r="E280" s="32"/>
-      <c r="F280" s="33"/>
-      <c r="G280" s="32"/>
-      <c r="H280" s="32"/>
-      <c r="I280" s="32"/>
+      <c r="D280" s="79"/>
+      <c r="E280" s="79"/>
+      <c r="F280" s="79"/>
+      <c r="G280" s="79"/>
+      <c r="H280" s="30">
+        <v>4</v>
+      </c>
+      <c r="I280" s="31" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="281" spans="1:9" ht="14.25" customHeight="1">
       <c r="A281" s="28"/>
-      <c r="D281" s="75" t="s">
-        <v>134</v>
-      </c>
-      <c r="E281" s="75" t="s">
-        <v>135</v>
-      </c>
-      <c r="F281" s="72" t="s">
-        <v>136</v>
-      </c>
-      <c r="G281" s="75" t="s">
-        <v>137</v>
-      </c>
-      <c r="H281" s="30">
-        <v>1</v>
-      </c>
-      <c r="I281" s="31" t="s">
-        <v>138</v>
-      </c>
+      <c r="D281" s="32"/>
+      <c r="E281" s="32"/>
+      <c r="F281" s="33"/>
+      <c r="G281" s="32"/>
+      <c r="H281" s="32"/>
+      <c r="I281" s="32"/>
     </row>
     <row r="282" spans="1:9" ht="14.25" customHeight="1">
       <c r="A282" s="28"/>
-      <c r="D282" s="73"/>
-      <c r="E282" s="73"/>
-      <c r="F282" s="73"/>
-      <c r="G282" s="73"/>
+      <c r="D282" s="100" t="s">
+        <v>134</v>
+      </c>
+      <c r="E282" s="100" t="s">
+        <v>135</v>
+      </c>
+      <c r="F282" s="99" t="s">
+        <v>136</v>
+      </c>
+      <c r="G282" s="100" t="s">
+        <v>137</v>
+      </c>
       <c r="H282" s="30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I282" s="31" t="s">
         <v>138</v>
@@ -5594,12 +5685,12 @@
     </row>
     <row r="283" spans="1:9" ht="14.25" customHeight="1">
       <c r="A283" s="28"/>
-      <c r="D283" s="73"/>
-      <c r="E283" s="73"/>
-      <c r="F283" s="73"/>
-      <c r="G283" s="73"/>
+      <c r="D283" s="78"/>
+      <c r="E283" s="78"/>
+      <c r="F283" s="78"/>
+      <c r="G283" s="78"/>
       <c r="H283" s="30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I283" s="31" t="s">
         <v>138</v>
@@ -5607,12 +5698,12 @@
     </row>
     <row r="284" spans="1:9" ht="14.25" customHeight="1">
       <c r="A284" s="28"/>
-      <c r="D284" s="74"/>
-      <c r="E284" s="74"/>
-      <c r="F284" s="74"/>
-      <c r="G284" s="74"/>
+      <c r="D284" s="78"/>
+      <c r="E284" s="78"/>
+      <c r="F284" s="78"/>
+      <c r="G284" s="78"/>
       <c r="H284" s="30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I284" s="31" t="s">
         <v>138</v>
@@ -5620,16 +5711,25 @@
     </row>
     <row r="285" spans="1:9" ht="14.25" customHeight="1">
       <c r="A285" s="28"/>
-      <c r="D285" s="32"/>
-      <c r="E285" s="32"/>
-      <c r="F285" s="33"/>
-      <c r="G285" s="32"/>
-      <c r="H285" s="32"/>
-      <c r="I285" s="32"/>
+      <c r="D285" s="79"/>
+      <c r="E285" s="79"/>
+      <c r="F285" s="79"/>
+      <c r="G285" s="79"/>
+      <c r="H285" s="30">
+        <v>4</v>
+      </c>
+      <c r="I285" s="31" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="286" spans="1:9" ht="14.25" customHeight="1">
       <c r="A286" s="28"/>
-      <c r="E286" s="28"/>
+      <c r="D286" s="32"/>
+      <c r="E286" s="32"/>
+      <c r="F286" s="33"/>
+      <c r="G286" s="32"/>
+      <c r="H286" s="32"/>
+      <c r="I286" s="32"/>
     </row>
     <row r="287" spans="1:9" ht="14.25" customHeight="1">
       <c r="A287" s="28"/>
@@ -5786,34 +5886,25 @@
     <row r="325" spans="1:12" ht="14.25" customHeight="1">
       <c r="A325" s="28"/>
       <c r="E325" s="28"/>
-      <c r="J325" s="56"/>
-      <c r="K325" s="56"/>
-      <c r="L325" s="57"/>
     </row>
     <row r="326" spans="1:12" ht="14.25" customHeight="1">
       <c r="A326" s="28"/>
       <c r="E326" s="28"/>
-      <c r="J326" s="22" t="s">
-        <v>61</v>
-      </c>
-      <c r="K326" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="L326" s="22" t="s">
-        <v>63</v>
-      </c>
+      <c r="J326" s="56"/>
+      <c r="K326" s="56"/>
+      <c r="L326" s="57"/>
     </row>
     <row r="327" spans="1:12" ht="14.25" customHeight="1">
       <c r="A327" s="28"/>
       <c r="E327" s="28"/>
-      <c r="J327" s="31" t="s">
-        <v>139</v>
-      </c>
-      <c r="K327" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="L327" s="31" t="s">
-        <v>141</v>
+      <c r="J327" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="K327" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="L327" s="22" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="328" spans="1:12" ht="14.25" customHeight="1">
@@ -5858,22 +5949,22 @@
     <row r="331" spans="1:12" ht="14.25" customHeight="1">
       <c r="A331" s="28"/>
       <c r="E331" s="28"/>
-      <c r="J331" s="32"/>
-      <c r="K331" s="32"/>
-      <c r="L331" s="32"/>
+      <c r="J331" s="31" t="s">
+        <v>139</v>
+      </c>
+      <c r="K331" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="L331" s="31" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="332" spans="1:12" ht="14.25" customHeight="1">
       <c r="A332" s="28"/>
       <c r="E332" s="28"/>
-      <c r="J332" s="31" t="s">
-        <v>139</v>
-      </c>
-      <c r="K332" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="L332" s="31" t="s">
-        <v>141</v>
-      </c>
+      <c r="J332" s="32"/>
+      <c r="K332" s="32"/>
+      <c r="L332" s="32"/>
     </row>
     <row r="333" spans="1:12" ht="14.25" customHeight="1">
       <c r="A333" s="28"/>
@@ -5917,22 +6008,22 @@
     <row r="336" spans="1:12" ht="14.25" customHeight="1">
       <c r="A336" s="28"/>
       <c r="E336" s="28"/>
-      <c r="J336" s="32"/>
-      <c r="K336" s="32"/>
-      <c r="L336" s="32"/>
+      <c r="J336" s="31" t="s">
+        <v>139</v>
+      </c>
+      <c r="K336" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="L336" s="31" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="337" spans="1:12" ht="14.25" customHeight="1">
       <c r="A337" s="28"/>
       <c r="E337" s="28"/>
-      <c r="J337" s="31" t="s">
-        <v>139</v>
-      </c>
-      <c r="K337" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="L337" s="31" t="s">
-        <v>141</v>
-      </c>
+      <c r="J337" s="32"/>
+      <c r="K337" s="32"/>
+      <c r="L337" s="32"/>
     </row>
     <row r="338" spans="1:12" ht="14.25" customHeight="1">
       <c r="A338" s="28"/>
@@ -5976,13 +6067,22 @@
     <row r="341" spans="1:12" ht="14.25" customHeight="1">
       <c r="A341" s="28"/>
       <c r="E341" s="28"/>
-      <c r="J341" s="32"/>
-      <c r="K341" s="32"/>
-      <c r="L341" s="32"/>
+      <c r="J341" s="31" t="s">
+        <v>139</v>
+      </c>
+      <c r="K341" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="L341" s="31" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="342" spans="1:12" ht="14.25" customHeight="1">
       <c r="A342" s="28"/>
       <c r="E342" s="28"/>
+      <c r="J342" s="32"/>
+      <c r="K342" s="32"/>
+      <c r="L342" s="32"/>
     </row>
     <row r="343" spans="1:12" ht="14.25" customHeight="1">
       <c r="A343" s="28"/>
@@ -8128,7 +8228,10 @@
       <c r="A878" s="28"/>
       <c r="E878" s="28"/>
     </row>
-    <row r="879" spans="1:5" ht="14.25" customHeight="1"/>
+    <row r="879" spans="1:5" ht="14.25" customHeight="1">
+      <c r="A879" s="28"/>
+      <c r="E879" s="28"/>
+    </row>
     <row r="880" spans="1:5" ht="14.25" customHeight="1"/>
     <row r="881" ht="14.25" customHeight="1"/>
     <row r="882" ht="14.25" customHeight="1"/>
@@ -8184,75 +8287,76 @@
     <row r="932" ht="14.25" customHeight="1"/>
     <row r="933" ht="14.25" customHeight="1"/>
     <row r="934" ht="14.25" customHeight="1"/>
+    <row r="935" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="67">
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="D72:D73"/>
-    <mergeCell ref="A58:A60"/>
-    <mergeCell ref="B58:B60"/>
-    <mergeCell ref="C58:C60"/>
-    <mergeCell ref="D58:D60"/>
-    <mergeCell ref="A62:A64"/>
-    <mergeCell ref="B62:B64"/>
-    <mergeCell ref="C62:C64"/>
-    <mergeCell ref="D62:D64"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="D49:D50"/>
-    <mergeCell ref="A52:A54"/>
-    <mergeCell ref="B52:B54"/>
-    <mergeCell ref="C52:C54"/>
-    <mergeCell ref="D52:D54"/>
-    <mergeCell ref="A42:A44"/>
-    <mergeCell ref="B42:B44"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="A28:A30"/>
-    <mergeCell ref="B28:B30"/>
-    <mergeCell ref="C28:C30"/>
-    <mergeCell ref="D28:D30"/>
-    <mergeCell ref="A15:A18"/>
-    <mergeCell ref="B15:B18"/>
-    <mergeCell ref="C15:C18"/>
-    <mergeCell ref="D15:D18"/>
-    <mergeCell ref="A20:A23"/>
-    <mergeCell ref="B20:B23"/>
-    <mergeCell ref="C20:C23"/>
-    <mergeCell ref="D20:D23"/>
-    <mergeCell ref="E269:H269"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="D9:D11"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="F282:F285"/>
+    <mergeCell ref="G282:G285"/>
+    <mergeCell ref="D272:D275"/>
+    <mergeCell ref="D277:D280"/>
+    <mergeCell ref="E277:E280"/>
+    <mergeCell ref="F277:F280"/>
+    <mergeCell ref="G277:G280"/>
+    <mergeCell ref="D282:D285"/>
+    <mergeCell ref="E282:E285"/>
+    <mergeCell ref="E272:E275"/>
+    <mergeCell ref="F272:F275"/>
+    <mergeCell ref="G272:G275"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="F1:I1"/>
     <mergeCell ref="A3:A7"/>
     <mergeCell ref="B3:B7"/>
     <mergeCell ref="C3:C7"/>
     <mergeCell ref="D3:D7"/>
-    <mergeCell ref="F281:F284"/>
-    <mergeCell ref="G281:G284"/>
-    <mergeCell ref="D271:D274"/>
-    <mergeCell ref="D276:D279"/>
-    <mergeCell ref="E276:E279"/>
-    <mergeCell ref="F276:F279"/>
-    <mergeCell ref="G276:G279"/>
-    <mergeCell ref="D281:D284"/>
-    <mergeCell ref="E281:E284"/>
-    <mergeCell ref="E271:E274"/>
-    <mergeCell ref="F271:F274"/>
-    <mergeCell ref="G271:G274"/>
+    <mergeCell ref="E270:H270"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="D9:D11"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="A15:A19"/>
+    <mergeCell ref="B15:B19"/>
+    <mergeCell ref="C15:C19"/>
+    <mergeCell ref="D15:D19"/>
+    <mergeCell ref="A21:A24"/>
+    <mergeCell ref="B21:B24"/>
+    <mergeCell ref="C21:C24"/>
+    <mergeCell ref="D21:D24"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="A29:A31"/>
+    <mergeCell ref="B29:B31"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="D29:D31"/>
+    <mergeCell ref="A43:A45"/>
+    <mergeCell ref="B43:B45"/>
+    <mergeCell ref="C43:C45"/>
+    <mergeCell ref="D43:D45"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="D50:D51"/>
+    <mergeCell ref="A53:A55"/>
+    <mergeCell ref="B53:B55"/>
+    <mergeCell ref="C53:C55"/>
+    <mergeCell ref="D53:D55"/>
+    <mergeCell ref="A73:A74"/>
+    <mergeCell ref="B73:B74"/>
+    <mergeCell ref="C73:C74"/>
+    <mergeCell ref="D73:D74"/>
+    <mergeCell ref="A59:A61"/>
+    <mergeCell ref="B59:B61"/>
+    <mergeCell ref="C59:C61"/>
+    <mergeCell ref="D59:D61"/>
+    <mergeCell ref="A63:A65"/>
+    <mergeCell ref="B63:B65"/>
+    <mergeCell ref="C63:C65"/>
+    <mergeCell ref="D63:D65"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
